--- a/ref/scTypeDB.xlsx
+++ b/ref/scTypeDB.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1051" uniqueCount="596">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1054" uniqueCount="600">
   <si>
     <t xml:space="preserve">tissueType</t>
   </si>
@@ -274,7 +274,7 @@
     <t xml:space="preserve">Endothelial</t>
   </si>
   <si>
-    <t xml:space="preserve">PECAM1,CD34,KDR,CDH5,PROM1,PDPN,TEK,FLT1,VCAM1,PTPRC,VWF,ENG,MCAM,ICAM1,FLT4,SELE</t>
+    <t xml:space="preserve">PECAM1,CDH5,KDR,VWF,TEK,FLT1,FLT4,CD34,EMCN,STAB2</t>
   </si>
   <si>
     <t xml:space="preserve">ECs</t>
@@ -349,31 +349,43 @@
     <t xml:space="preserve">MSCs</t>
   </si>
   <si>
-    <t xml:space="preserve">CXCL12,SPARC,IGFBP5,SERPINE2,APOE,KITL,LEPR</t>
+    <t xml:space="preserve">CXCL12,LEPR,KITL,NT5E,THY1,ENG,EBF3</t>
   </si>
   <si>
     <t xml:space="preserve">Pericytes</t>
   </si>
   <si>
-    <t xml:space="preserve">CRIP1,ACTA2,MYH11,TAGLN,MYL6,CALD1,TPM1,TPM2,MYL9,MYLK,DSTN,SPARCL1,PPP1R12A</t>
+    <t xml:space="preserve">PDGFRB,RGS5,ACTA2,TAGLN,MYH11,CRIP1,NESTIN</t>
   </si>
   <si>
     <t xml:space="preserve">Fibroblasts</t>
   </si>
   <si>
-    <t xml:space="preserve">IGFBP6,DCN,COL1A1,PDGFRA,GSN,LGALS1,TIMP2,COL3A1,LRP1,PRRX1,LUM,S100A4,S100A6,ACTA2</t>
+    <t xml:space="preserve">DCN,COL1A1,COL3A1,LUM,PDGFRA,PRRX1,LGALS1,IGFBP6,GSN,FAP,THY1,TNXB,FBLN1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fibro</t>
   </si>
   <si>
     <t xml:space="preserve">OLCs</t>
   </si>
   <si>
-    <t xml:space="preserve">COL1A1,COL5A2,IBSP,CFH,SERPINF1,BGLAP2,NUPR1,BGLAP,LOX,NRP2,COL11A2,SP7</t>
+    <t xml:space="preserve">COL1A1,COL5A2,IBSP,BGLAP,SP7,RUNX2,ALPL,LOX,IFITM5</t>
   </si>
   <si>
     <t xml:space="preserve">Chondrocytes</t>
   </si>
   <si>
-    <t xml:space="preserve">COL11A1,ACAN,HAPLN1,COMP,COL11A2,MIA,CNMD</t>
+    <t xml:space="preserve">COL2A1,COL9A1,COL11A1,COL11A2,ACAN,COMP,HAPLN1,SOX9,MIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chondro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schwann</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S100B,SOX10,MPZ,MBP,PLP1,NGFR,GFRA3,ERBB3</t>
   </si>
   <si>
     <t xml:space="preserve">Pancreas</t>
@@ -1747,7 +1759,7 @@
     <t xml:space="preserve">Exh CD4+ T</t>
   </si>
   <si>
-    <t xml:space="preserve">γδ- T cells</t>
+    <t xml:space="preserve">gammaDelta- T cells</t>
   </si>
   <si>
     <t xml:space="preserve">PTPRC,TRDV2,TRGV9,TRGC1,CD3D,CD3E,CD3G,TRDC,TRGC2,TRDV1,ZBTB16,PLZF,RORC,CD3D,CD3E,CD3G</t>
@@ -1818,7 +1830,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -1858,11 +1870,6 @@
       <name val="Helvetica Neue"/>
       <family val="0"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="0"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1920,7 +1927,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1957,10 +1964,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1978,7 +1981,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AMJ1048576"/>
+  <dimension ref="A1:E1048576"/>
   <sheetFormatPr defaultColWidth="8.8515625" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.85"/>
@@ -2565,11 +2568,9 @@
       <c r="C37" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="D37" s="3" t="s">
-        <v>78</v>
-      </c>
+      <c r="D37" s="3"/>
       <c r="E37" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2577,14 +2578,14 @@
         <v>5</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D38" s="5"/>
       <c r="E38" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2592,229 +2593,229 @@
         <v>5</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D39" s="5"/>
       <c r="E39" s="3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="B40" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="C40" s="5" t="s">
+    </row>
+    <row r="40" customFormat="false" ht="14.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B40" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="D40" s="6"/>
-      <c r="E40" s="5" t="s">
+      <c r="C40" s="7" t="s">
         <v>121</v>
+      </c>
+      <c r="D40" s="5"/>
+      <c r="E40" s="3" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D41" s="6"/>
       <c r="E41" s="5" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D42" s="6"/>
       <c r="E42" s="5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D43" s="6"/>
       <c r="E43" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D44" s="6"/>
       <c r="E44" s="5" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="5" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D45" s="6"/>
       <c r="E45" s="5" t="s">
-        <v>85</v>
+        <v>137</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D46" s="6"/>
       <c r="E46" s="5" t="s">
-        <v>138</v>
+        <v>85</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D47" s="6"/>
       <c r="E47" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="5" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D48" s="6"/>
       <c r="E48" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="5" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>63</v>
+        <v>146</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D49" s="6"/>
       <c r="E49" s="5" t="s">
-        <v>65</v>
+        <v>148</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="5" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>146</v>
+        <v>63</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D50" s="6"/>
       <c r="E50" s="5" t="s">
-        <v>148</v>
+        <v>65</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="5" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D51" s="6"/>
       <c r="E51" s="5" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="5" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D52" s="6"/>
       <c r="E52" s="5" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="5" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D53" s="6"/>
       <c r="E53" s="5" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="5" t="s">
-        <v>158</v>
+        <v>122</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>159</v>
@@ -2824,213 +2825,213 @@
       </c>
       <c r="D54" s="6"/>
       <c r="E54" s="5" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="5" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D55" s="6"/>
       <c r="E55" s="5" t="s">
-        <v>83</v>
+        <v>163</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="5" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D56" s="6"/>
       <c r="E56" s="5" t="s">
-        <v>165</v>
+        <v>83</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="5" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D57" s="6"/>
       <c r="E57" s="5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="5" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D58" s="6"/>
       <c r="E58" s="5" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="5" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D59" s="6"/>
       <c r="E59" s="5" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="5" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>142</v>
+        <v>175</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D60" s="6"/>
       <c r="E60" s="5" t="s">
-        <v>144</v>
+        <v>175</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="5" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>174</v>
+        <v>146</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D61" s="6"/>
       <c r="E61" s="5" t="s">
-        <v>176</v>
+        <v>148</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="5" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D62" s="6"/>
       <c r="E62" s="5" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="5" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>63</v>
+        <v>181</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>145</v>
+        <v>182</v>
       </c>
       <c r="D63" s="6"/>
       <c r="E63" s="5" t="s">
-        <v>65</v>
+        <v>183</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="5" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>180</v>
+        <v>63</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>181</v>
+        <v>149</v>
       </c>
       <c r="D64" s="6"/>
       <c r="E64" s="5" t="s">
-        <v>180</v>
+        <v>65</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="5" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D65" s="6"/>
       <c r="E65" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="5" t="s">
-        <v>184</v>
+        <v>162</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D66" s="6"/>
       <c r="E66" s="5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D67" s="6"/>
       <c r="E67" s="5" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D68" s="6"/>
       <c r="E68" s="5" t="s">
@@ -3039,148 +3040,148 @@
     </row>
     <row r="69" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D69" s="6"/>
       <c r="E69" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D70" s="6"/>
       <c r="E70" s="5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D71" s="6"/>
       <c r="E71" s="5" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D72" s="6"/>
       <c r="E72" s="5" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D73" s="6"/>
       <c r="E73" s="5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D74" s="6"/>
       <c r="E74" s="5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D75" s="6"/>
       <c r="E75" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D76" s="6"/>
       <c r="E76" s="5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D77" s="6"/>
       <c r="E77" s="5" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D78" s="6"/>
       <c r="E78" s="5" t="s">
@@ -3189,157 +3190,157 @@
     </row>
     <row r="79" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D79" s="6"/>
       <c r="E79" s="5" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D80" s="6"/>
       <c r="E80" s="5" t="s">
-        <v>144</v>
+        <v>228</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>112</v>
+        <v>229</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="D81" s="6"/>
       <c r="E81" s="5" t="s">
-        <v>112</v>
+        <v>148</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="D82" s="6"/>
       <c r="E82" s="5" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>110</v>
+        <v>138</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="D83" s="6"/>
       <c r="E83" s="5" t="s">
-        <v>110</v>
+        <v>83</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>230</v>
+        <v>110</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D84" s="6"/>
       <c r="E84" s="5" t="s">
-        <v>232</v>
+        <v>110</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D85" s="6"/>
       <c r="E85" s="5" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D86" s="6"/>
       <c r="E86" s="5" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D87" s="6"/>
       <c r="E87" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D88" s="6"/>
       <c r="E88" s="5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="5" t="s">
-        <v>245</v>
+        <v>188</v>
       </c>
       <c r="B89" s="5" t="s">
         <v>246</v>
@@ -3354,103 +3355,103 @@
     </row>
     <row r="90" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="5" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>225</v>
+        <v>250</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="D90" s="6"/>
       <c r="E90" s="5" t="s">
-        <v>144</v>
+        <v>252</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="5" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>250</v>
+        <v>229</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D91" s="6"/>
       <c r="E91" s="5" t="s">
-        <v>252</v>
+        <v>148</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="5" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D92" s="6"/>
       <c r="E92" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="5" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D93" s="6"/>
       <c r="E93" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="5" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D94" s="6"/>
       <c r="E94" s="5" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="5" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D95" s="6"/>
       <c r="E95" s="5" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="5" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D96" s="6"/>
       <c r="E96" s="5" t="s">
@@ -3459,418 +3460,418 @@
     </row>
     <row r="97" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="5" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D97" s="6"/>
       <c r="E97" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="5" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D98" s="6"/>
       <c r="E98" s="5" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="5" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D99" s="6"/>
       <c r="E99" s="5" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="5" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>134</v>
+        <v>276</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D100" s="6"/>
       <c r="E100" s="5" t="s">
-        <v>83</v>
+        <v>278</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="5" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>276</v>
+        <v>138</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D101" s="6"/>
       <c r="E101" s="5" t="s">
-        <v>278</v>
+        <v>83</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="5" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D102" s="6"/>
       <c r="E102" s="5" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="5" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D103" s="6"/>
       <c r="E103" s="5" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="5" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D104" s="6"/>
       <c r="E104" s="5" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="5" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D105" s="6"/>
       <c r="E105" s="5" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="5" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D106" s="6"/>
       <c r="E106" s="5" t="s">
-        <v>165</v>
+        <v>294</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="5" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D107" s="6"/>
       <c r="E107" s="5" t="s">
-        <v>295</v>
+        <v>169</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="5" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D108" s="6"/>
       <c r="E108" s="5" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="5" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>246</v>
+        <v>300</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>247</v>
+        <v>301</v>
       </c>
       <c r="D109" s="6"/>
       <c r="E109" s="5" t="s">
-        <v>248</v>
+        <v>302</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="5" t="s">
-        <v>299</v>
+        <v>249</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>188</v>
+        <v>250</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>300</v>
+        <v>251</v>
       </c>
       <c r="D110" s="6"/>
       <c r="E110" s="5" t="s">
-        <v>188</v>
+        <v>252</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="5" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>301</v>
+        <v>192</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D111" s="6"/>
       <c r="E111" s="5" t="s">
-        <v>301</v>
+        <v>192</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="5" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D112" s="6"/>
       <c r="E112" s="5" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="5" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>134</v>
+        <v>307</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="D113" s="6"/>
       <c r="E113" s="5" t="s">
-        <v>83</v>
+        <v>307</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="5" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>306</v>
+        <v>138</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D114" s="6"/>
       <c r="E114" s="5" t="s">
-        <v>306</v>
+        <v>83</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="5" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D115" s="6"/>
       <c r="E115" s="5" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="5" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D116" s="6"/>
       <c r="E116" s="5" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="5" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>142</v>
+        <v>314</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="D117" s="6"/>
       <c r="E117" s="5" t="s">
-        <v>5</v>
+        <v>314</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="5" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>313</v>
+        <v>146</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D118" s="6"/>
       <c r="E118" s="5" t="s">
-        <v>313</v>
+        <v>5</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="5" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>211</v>
+        <v>317</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="D119" s="6"/>
       <c r="E119" s="5" t="s">
-        <v>213</v>
+        <v>317</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="5" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>316</v>
+        <v>215</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D120" s="6"/>
       <c r="E120" s="5" t="s">
-        <v>318</v>
+        <v>217</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="5" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D121" s="6"/>
       <c r="E121" s="5" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="5" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D122" s="6"/>
       <c r="E122" s="5" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="5" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D123" s="6"/>
       <c r="E123" s="5" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="5" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D124" s="6"/>
       <c r="E124" s="5" t="s">
@@ -3879,58 +3880,58 @@
     </row>
     <row r="125" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="5" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D125" s="6"/>
       <c r="E125" s="5" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="5" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D126" s="6"/>
       <c r="E126" s="5" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="5" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D127" s="6"/>
       <c r="E127" s="5" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="5" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="D128" s="6"/>
       <c r="E128" s="5" t="s">
@@ -3939,148 +3940,148 @@
     </row>
     <row r="129" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="5" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D129" s="6"/>
       <c r="E129" s="5" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="5" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D130" s="6"/>
       <c r="E130" s="5" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="5" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D131" s="6"/>
       <c r="E131" s="5" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="5" t="s">
-        <v>348</v>
+        <v>303</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D132" s="6"/>
       <c r="E132" s="5" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="5" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D133" s="6"/>
       <c r="E133" s="5" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="5" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D134" s="6"/>
       <c r="E134" s="5" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="5" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>112</v>
+        <v>359</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D135" s="6"/>
       <c r="E135" s="5" t="s">
-        <v>112</v>
+        <v>361</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="5" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>359</v>
+        <v>112</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="D136" s="6"/>
       <c r="E136" s="5" t="s">
-        <v>361</v>
+        <v>112</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="5" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D137" s="6"/>
       <c r="E137" s="5" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="5" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="D138" s="6"/>
       <c r="E138" s="5" t="s">
@@ -4089,88 +4090,88 @@
     </row>
     <row r="139" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="5" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D139" s="6"/>
       <c r="E139" s="5" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="5" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>142</v>
+        <v>371</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D140" s="6"/>
       <c r="E140" s="5" t="s">
-        <v>5</v>
+        <v>373</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="5" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="D141" s="6"/>
       <c r="E141" s="5" t="s">
-        <v>161</v>
+        <v>5</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="5" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>372</v>
+        <v>165</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D142" s="6"/>
       <c r="E142" s="5" t="s">
-        <v>374</v>
+        <v>165</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="5" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D143" s="6"/>
       <c r="E143" s="5" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="5" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D144" s="6"/>
       <c r="E144" s="5" t="s">
@@ -4179,37 +4180,37 @@
     </row>
     <row r="145" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="5" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D145" s="6"/>
       <c r="E145" s="5" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="5" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D146" s="6"/>
       <c r="E146" s="5" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="5" t="s">
-        <v>386</v>
+        <v>352</v>
       </c>
       <c r="B147" s="5" t="s">
         <v>387</v>
@@ -4218,1429 +4219,1427 @@
         <v>388</v>
       </c>
       <c r="D147" s="6"/>
-      <c r="E147" s="6"/>
+      <c r="E147" s="5" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="148" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="5" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D148" s="6"/>
       <c r="E148" s="6"/>
     </row>
     <row r="149" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="5" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="D149" s="6"/>
       <c r="E149" s="6"/>
     </row>
     <row r="150" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="5" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="D150" s="6"/>
       <c r="E150" s="6"/>
     </row>
     <row r="151" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="5" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="D151" s="6"/>
       <c r="E151" s="6"/>
     </row>
     <row r="152" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A152" s="5" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="D152" s="6"/>
       <c r="E152" s="6"/>
     </row>
     <row r="153" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="5" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="D153" s="6"/>
       <c r="E153" s="6"/>
     </row>
     <row r="154" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A154" s="5" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D154" s="6"/>
       <c r="E154" s="6"/>
     </row>
     <row r="155" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A155" s="5" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="D155" s="6"/>
       <c r="E155" s="6"/>
     </row>
     <row r="156" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A156" s="5" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="D156" s="6"/>
       <c r="E156" s="6"/>
     </row>
     <row r="157" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A157" s="5" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="D157" s="6"/>
       <c r="E157" s="6"/>
     </row>
     <row r="158" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="5" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="D158" s="6"/>
       <c r="E158" s="6"/>
     </row>
     <row r="159" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="5" t="s">
-        <v>411</v>
+        <v>390</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>389</v>
+        <v>413</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="D159" s="6"/>
       <c r="E159" s="6"/>
     </row>
     <row r="160" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="5" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>413</v>
+        <v>393</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D160" s="6"/>
       <c r="E160" s="6"/>
     </row>
     <row r="161" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="5" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D161" s="6"/>
       <c r="E161" s="6"/>
     </row>
     <row r="162" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="5" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>391</v>
+        <v>419</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="D162" s="6"/>
       <c r="E162" s="6"/>
     </row>
     <row r="163" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="5" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="D163" s="6"/>
       <c r="E163" s="6"/>
     </row>
     <row r="164" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="5" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>393</v>
+        <v>409</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="D164" s="6"/>
       <c r="E164" s="6"/>
     </row>
     <row r="165" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="5" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>420</v>
+        <v>397</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D165" s="6"/>
       <c r="E165" s="6"/>
     </row>
     <row r="166" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="5" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>401</v>
+        <v>424</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="D166" s="6"/>
       <c r="E166" s="6"/>
     </row>
     <row r="167" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="5" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="D167" s="6"/>
       <c r="E167" s="6"/>
     </row>
     <row r="168" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="5" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="B168" s="5" t="s">
-        <v>424</v>
+        <v>403</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D168" s="6"/>
       <c r="E168" s="6"/>
     </row>
     <row r="169" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="5" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="B169" s="5" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="D169" s="6"/>
       <c r="E169" s="6"/>
     </row>
     <row r="170" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="5" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="B170" s="5" t="s">
-        <v>397</v>
+        <v>430</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="D170" s="6"/>
       <c r="E170" s="6"/>
     </row>
     <row r="171" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="5" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>429</v>
+        <v>401</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D171" s="6"/>
       <c r="E171" s="6"/>
     </row>
     <row r="172" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="5" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="B172" s="5" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D172" s="6"/>
       <c r="E172" s="6"/>
     </row>
     <row r="173" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="5" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D173" s="6"/>
       <c r="E173" s="6"/>
     </row>
     <row r="174" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="5" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="B174" s="5" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="D174" s="6"/>
       <c r="E174" s="6"/>
     </row>
     <row r="175" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="5" t="s">
-        <v>437</v>
+        <v>415</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>397</v>
+        <v>439</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="D175" s="6"/>
       <c r="E175" s="6"/>
     </row>
     <row r="176" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="5" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="B176" s="5" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="D176" s="6"/>
       <c r="E176" s="6"/>
     </row>
     <row r="177" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="5" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>424</v>
+        <v>407</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="D177" s="6"/>
       <c r="E177" s="6"/>
     </row>
     <row r="178" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="5" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="B178" s="5" t="s">
-        <v>393</v>
+        <v>428</v>
       </c>
       <c r="C178" s="5" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="D178" s="6"/>
       <c r="E178" s="6"/>
     </row>
     <row r="179" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="5" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="D179" s="6"/>
       <c r="E179" s="6"/>
     </row>
     <row r="180" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="5" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="B180" s="5" t="s">
-        <v>443</v>
+        <v>409</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D180" s="6"/>
       <c r="E180" s="6"/>
     </row>
     <row r="181" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="5" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D181" s="6"/>
       <c r="E181" s="6"/>
     </row>
     <row r="182" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="5" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D182" s="6"/>
       <c r="E182" s="6"/>
     </row>
     <row r="183" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="5" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>401</v>
+        <v>451</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="D183" s="6"/>
       <c r="E183" s="6"/>
     </row>
     <row r="184" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="5" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="B184" s="5" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="C184" s="5" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="D184" s="6"/>
       <c r="E184" s="6"/>
     </row>
     <row r="185" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="5" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="B185" s="5" t="s">
-        <v>355</v>
+        <v>403</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D185" s="6"/>
       <c r="E185" s="6"/>
     </row>
     <row r="186" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="5" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>415</v>
+        <v>359</v>
       </c>
       <c r="C186" s="5" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="D186" s="6"/>
       <c r="E186" s="6"/>
     </row>
     <row r="187" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="5" t="s">
-        <v>453</v>
+        <v>441</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>389</v>
+        <v>419</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="D187" s="6"/>
       <c r="E187" s="6"/>
     </row>
     <row r="188" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="5" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C188" s="5" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D188" s="6"/>
       <c r="E188" s="6"/>
     </row>
     <row r="189" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="5" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>415</v>
+        <v>395</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="D189" s="6"/>
       <c r="E189" s="6"/>
     </row>
     <row r="190" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="5" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>397</v>
+        <v>419</v>
       </c>
       <c r="C190" s="5" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="D190" s="6"/>
       <c r="E190" s="6"/>
     </row>
     <row r="191" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="5" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>458</v>
+        <v>401</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="D191" s="6"/>
       <c r="E191" s="6"/>
     </row>
     <row r="192" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="5" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>399</v>
+        <v>462</v>
       </c>
       <c r="C192" s="5" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="D192" s="6"/>
       <c r="E192" s="6"/>
     </row>
     <row r="193" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="5" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B193" s="5" t="s">
-        <v>461</v>
+        <v>403</v>
       </c>
       <c r="C193" s="5" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="D193" s="6"/>
       <c r="E193" s="6"/>
     </row>
     <row r="194" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="5" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B194" s="5" t="s">
-        <v>401</v>
+        <v>465</v>
       </c>
       <c r="C194" s="5" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="D194" s="6"/>
       <c r="E194" s="6"/>
     </row>
     <row r="195" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="5" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B195" s="5" t="s">
-        <v>424</v>
+        <v>405</v>
       </c>
       <c r="C195" s="5" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="D195" s="6"/>
       <c r="E195" s="6"/>
     </row>
     <row r="196" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A196" s="5" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B196" s="5" t="s">
-        <v>393</v>
+        <v>428</v>
       </c>
       <c r="C196" s="5" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="D196" s="6"/>
       <c r="E196" s="6"/>
     </row>
     <row r="197" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="5" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B197" s="5" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="C197" s="5" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="D197" s="6"/>
       <c r="E197" s="6"/>
     </row>
     <row r="198" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A198" s="5" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="B198" s="5" t="s">
-        <v>468</v>
+        <v>409</v>
       </c>
       <c r="C198" s="5" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D198" s="6"/>
       <c r="E198" s="6"/>
     </row>
     <row r="199" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A199" s="5" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="B199" s="5" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C199" s="5" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="D199" s="6"/>
       <c r="E199" s="6"/>
     </row>
     <row r="200" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A200" s="5" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="B200" s="5" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C200" s="5" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="D200" s="6"/>
       <c r="E200" s="6"/>
     </row>
     <row r="201" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A201" s="5" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="B201" s="5" t="s">
-        <v>405</v>
+        <v>476</v>
       </c>
       <c r="C201" s="5" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="D201" s="6"/>
       <c r="E201" s="6"/>
     </row>
     <row r="202" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A202" s="5" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="B202" s="5" t="s">
-        <v>475</v>
+        <v>409</v>
       </c>
       <c r="C202" s="5" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="D202" s="6"/>
       <c r="E202" s="6"/>
     </row>
     <row r="203" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A203" s="5" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="B203" s="5" t="s">
-        <v>424</v>
+        <v>479</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="D203" s="6"/>
       <c r="E203" s="6"/>
     </row>
     <row r="204" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A204" s="5" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="B204" s="5" t="s">
-        <v>478</v>
+        <v>428</v>
       </c>
       <c r="C204" s="5" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="D204" s="6"/>
       <c r="E204" s="6"/>
     </row>
     <row r="205" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A205" s="5" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="B205" s="5" t="s">
-        <v>399</v>
+        <v>482</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="D205" s="6"/>
       <c r="E205" s="6"/>
     </row>
     <row r="206" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A206" s="5" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="B206" s="5" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C206" s="5" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="D206" s="6"/>
       <c r="E206" s="6"/>
     </row>
     <row r="207" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A207" s="5" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="B207" s="5" t="s">
-        <v>482</v>
+        <v>405</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="D207" s="6"/>
       <c r="E207" s="6"/>
     </row>
     <row r="208" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A208" s="5" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="B208" s="5" t="s">
-        <v>393</v>
+        <v>486</v>
       </c>
       <c r="C208" s="5" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="D208" s="6"/>
       <c r="E208" s="6"/>
     </row>
     <row r="209" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A209" s="5" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="B209" s="5" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="C209" s="5" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="D209" s="6"/>
       <c r="E209" s="6"/>
     </row>
     <row r="210" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A210" s="5" t="s">
-        <v>486</v>
+        <v>471</v>
       </c>
       <c r="B210" s="5" t="s">
-        <v>470</v>
+        <v>393</v>
       </c>
       <c r="C210" s="5" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="D210" s="6"/>
       <c r="E210" s="6"/>
     </row>
     <row r="211" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A211" s="5" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="B211" s="5" t="s">
-        <v>405</v>
+        <v>474</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="D211" s="6"/>
       <c r="E211" s="6"/>
     </row>
     <row r="212" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="5" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="B212" s="5" t="s">
-        <v>393</v>
+        <v>409</v>
       </c>
       <c r="C212" s="5" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="D212" s="6"/>
       <c r="E212" s="6"/>
     </row>
     <row r="213" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A213" s="5" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="B213" s="5" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="D213" s="6"/>
       <c r="E213" s="6"/>
     </row>
     <row r="214" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A214" s="5" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="B214" s="5" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="C214" s="5" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="D214" s="6"/>
       <c r="E214" s="6"/>
     </row>
     <row r="215" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A215" s="5" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="B215" s="5" t="s">
-        <v>492</v>
+        <v>403</v>
       </c>
       <c r="C215" s="5" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="D215" s="6"/>
       <c r="E215" s="6"/>
     </row>
     <row r="216" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A216" s="5" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="B216" s="5" t="s">
-        <v>389</v>
+        <v>496</v>
       </c>
       <c r="C216" s="5" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="D216" s="6"/>
       <c r="E216" s="6"/>
     </row>
     <row r="217" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A217" s="5" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="B217" s="5" t="s">
-        <v>355</v>
+        <v>393</v>
       </c>
       <c r="C217" s="5" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="D217" s="6"/>
       <c r="E217" s="6"/>
     </row>
     <row r="218" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A218" s="5" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="B218" s="5" t="s">
-        <v>397</v>
+        <v>359</v>
       </c>
       <c r="C218" s="5" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="D218" s="6"/>
       <c r="E218" s="6"/>
     </row>
     <row r="219" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A219" s="5" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="B219" s="5" t="s">
-        <v>498</v>
+        <v>401</v>
       </c>
       <c r="C219" s="5" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D219" s="6"/>
       <c r="E219" s="6"/>
     </row>
     <row r="220" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A220" s="5" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="B220" s="5" t="s">
-        <v>397</v>
+        <v>502</v>
       </c>
       <c r="C220" s="5" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="D220" s="6"/>
       <c r="E220" s="6"/>
     </row>
     <row r="221" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A221" s="5" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="B221" s="5" t="s">
-        <v>501</v>
+        <v>401</v>
       </c>
       <c r="C221" s="5" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="D221" s="6"/>
       <c r="E221" s="6"/>
     </row>
     <row r="222" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A222" s="5" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="B222" s="5" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C222" s="5" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="D222" s="6"/>
       <c r="E222" s="6"/>
     </row>
     <row r="223" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A223" s="5" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="B223" s="5" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C223" s="5" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="D223" s="6"/>
       <c r="E223" s="6"/>
     </row>
     <row r="224" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A224" s="5" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="B224" s="5" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C224" s="5" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="D224" s="6"/>
       <c r="E224" s="6"/>
     </row>
     <row r="225" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A225" s="5" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="B225" s="5" t="s">
-        <v>393</v>
+        <v>511</v>
       </c>
       <c r="C225" s="5" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="D225" s="6"/>
       <c r="E225" s="6"/>
     </row>
     <row r="226" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A226" s="5" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="B226" s="5" t="s">
-        <v>510</v>
+        <v>397</v>
       </c>
       <c r="C226" s="5" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="D226" s="6"/>
       <c r="E226" s="6"/>
     </row>
     <row r="227" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A227" s="5" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="B227" s="5" t="s">
-        <v>399</v>
+        <v>514</v>
       </c>
       <c r="C227" s="5" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="D227" s="6"/>
       <c r="E227" s="6"/>
     </row>
     <row r="228" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A228" s="5" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="B228" s="5" t="s">
-        <v>447</v>
+        <v>403</v>
       </c>
       <c r="C228" s="5" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="D228" s="6"/>
       <c r="E228" s="6"/>
     </row>
     <row r="229" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A229" s="5" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="B229" s="5" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="C229" s="5" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="D229" s="6"/>
       <c r="E229" s="6"/>
     </row>
     <row r="230" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A230" s="5" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="B230" s="5" t="s">
-        <v>401</v>
+        <v>449</v>
       </c>
       <c r="C230" s="5" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="D230" s="6"/>
       <c r="E230" s="6"/>
     </row>
     <row r="231" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A231" s="5" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="B231" s="5" t="s">
-        <v>415</v>
+        <v>405</v>
       </c>
       <c r="C231" s="5" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="D231" s="6"/>
       <c r="E231" s="6"/>
     </row>
     <row r="232" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A232" s="5" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="B232" s="5" t="s">
-        <v>355</v>
+        <v>419</v>
       </c>
       <c r="C232" s="5" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="D232" s="6"/>
       <c r="E232" s="6"/>
     </row>
     <row r="233" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A233" s="5" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="B233" s="5" t="s">
-        <v>405</v>
+        <v>359</v>
       </c>
       <c r="C233" s="5" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="D233" s="6"/>
       <c r="E233" s="6"/>
     </row>
     <row r="234" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A234" s="5" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="B234" s="5" t="s">
-        <v>519</v>
+        <v>409</v>
       </c>
       <c r="C234" s="5" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="D234" s="6"/>
       <c r="E234" s="6"/>
     </row>
     <row r="235" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A235" s="5" t="s">
-        <v>521</v>
+        <v>501</v>
       </c>
       <c r="B235" s="5" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C235" s="5" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D235" s="6"/>
       <c r="E235" s="6"/>
     </row>
     <row r="236" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A236" s="5" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="B236" s="5" t="s">
-        <v>399</v>
+        <v>526</v>
       </c>
       <c r="C236" s="5" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="D236" s="6"/>
       <c r="E236" s="6"/>
     </row>
     <row r="237" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A237" s="5" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="B237" s="5" t="s">
-        <v>525</v>
+        <v>403</v>
       </c>
       <c r="C237" s="5" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="D237" s="6"/>
       <c r="E237" s="6"/>
     </row>
     <row r="238" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A238" s="5" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="B238" s="5" t="s">
-        <v>401</v>
+        <v>529</v>
       </c>
       <c r="C238" s="5" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="D238" s="6"/>
       <c r="E238" s="6"/>
     </row>
     <row r="239" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A239" s="5" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="B239" s="5" t="s">
-        <v>528</v>
+        <v>405</v>
       </c>
       <c r="C239" s="5" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="D239" s="6"/>
       <c r="E239" s="6"/>
     </row>
     <row r="240" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A240" s="5" t="s">
-        <v>5</v>
+        <v>525</v>
       </c>
       <c r="B240" s="5" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C240" s="5" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="D240" s="6"/>
-      <c r="E240" s="5" t="s">
-        <v>532</v>
-      </c>
+      <c r="E240" s="6"/>
     </row>
     <row r="241" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A241" s="5" t="s">
-        <v>118</v>
+        <v>5</v>
       </c>
       <c r="B241" s="5" t="s">
-        <v>246</v>
+        <v>534</v>
       </c>
       <c r="C241" s="5" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="D241" s="6"/>
       <c r="E241" s="5" t="s">
-        <v>248</v>
+        <v>536</v>
       </c>
     </row>
     <row r="242" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A242" s="5" t="s">
-        <v>158</v>
+        <v>122</v>
       </c>
       <c r="B242" s="5" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="C242" s="5" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="D242" s="6"/>
       <c r="E242" s="5" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
     </row>
     <row r="243" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A243" s="5" t="s">
-        <v>184</v>
+        <v>162</v>
       </c>
       <c r="B243" s="5" t="s">
-        <v>530</v>
+        <v>250</v>
       </c>
       <c r="C243" s="5" t="s">
-        <v>247</v>
+        <v>538</v>
       </c>
       <c r="D243" s="6"/>
       <c r="E243" s="5" t="s">
-        <v>532</v>
+        <v>252</v>
       </c>
     </row>
     <row r="244" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A244" s="5" t="s">
-        <v>348</v>
+        <v>188</v>
       </c>
       <c r="B244" s="5" t="s">
-        <v>246</v>
+        <v>534</v>
       </c>
       <c r="C244" s="5" t="s">
-        <v>535</v>
+        <v>251</v>
       </c>
       <c r="D244" s="6"/>
       <c r="E244" s="5" t="s">
-        <v>248</v>
+        <v>536</v>
       </c>
     </row>
     <row r="245" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A245" s="5" t="s">
-        <v>299</v>
+        <v>352</v>
       </c>
       <c r="B245" s="5" t="s">
-        <v>530</v>
+        <v>250</v>
       </c>
       <c r="C245" s="5" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="D245" s="6"/>
       <c r="E245" s="5" t="s">
-        <v>532</v>
+        <v>252</v>
       </c>
     </row>
     <row r="246" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A246" s="5" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B246" s="5" t="s">
-        <v>246</v>
+        <v>534</v>
       </c>
       <c r="C246" s="5" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="D246" s="6"/>
       <c r="E246" s="5" t="s">
-        <v>248</v>
+        <v>536</v>
       </c>
     </row>
     <row r="247" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A247" s="5" t="s">
-        <v>245</v>
+        <v>303</v>
       </c>
       <c r="B247" s="5" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="C247" s="5" t="s">
-        <v>247</v>
+        <v>541</v>
       </c>
       <c r="D247" s="6"/>
       <c r="E247" s="5" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="248" customFormat="false" ht="13.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A248" s="3" t="s">
-        <v>538</v>
-      </c>
-      <c r="B248" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C248" s="8" t="s">
-        <v>539</v>
-      </c>
-      <c r="D248" s="4" t="s">
-        <v>540</v>
-      </c>
-      <c r="E248" s="3" t="s">
-        <v>8</v>
+        <v>252</v>
+      </c>
+    </row>
+    <row r="248" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A248" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="B248" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="C248" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="D248" s="6"/>
+      <c r="E248" s="5" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="249" customFormat="false" ht="13.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A249" s="3" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B249" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C249" s="8" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="D249" s="4" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="E249" s="3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="250" customFormat="false" ht="13.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A250" s="3" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B250" s="3" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C250" s="8" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D250" s="4" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="E250" s="3" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="251" customFormat="false" ht="13.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A251" s="3" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B251" s="3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C251" s="8" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="D251" s="4" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="E251" s="3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="252" customFormat="false" ht="13.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A252" s="3" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B252" s="3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C252" s="8" t="s">
-        <v>547</v>
-      </c>
-      <c r="D252" s="3" t="s">
-        <v>548</v>
+        <v>549</v>
+      </c>
+      <c r="D252" s="4" t="s">
+        <v>550</v>
       </c>
       <c r="E252" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="253" customFormat="false" ht="13.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A253" s="3" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B253" s="3" t="s">
-        <v>549</v>
+        <v>18</v>
       </c>
       <c r="C253" s="8" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D253" s="3" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="E253" s="3" t="s">
-        <v>552</v>
+        <v>21</v>
       </c>
     </row>
     <row r="254" customFormat="false" ht="13.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A254" s="3" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B254" s="3" t="s">
         <v>553</v>
@@ -5657,1252 +5656,233 @@
     </row>
     <row r="255" customFormat="false" ht="13.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A255" s="3" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B255" s="3" t="s">
-        <v>22</v>
+        <v>557</v>
       </c>
       <c r="C255" s="8" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D255" s="3" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="E255" s="3" t="s">
-        <v>25</v>
+        <v>560</v>
       </c>
     </row>
     <row r="256" customFormat="false" ht="13.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A256" s="3" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B256" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C256" s="3" t="s">
-        <v>559</v>
+        <v>22</v>
+      </c>
+      <c r="C256" s="8" t="s">
+        <v>561</v>
       </c>
       <c r="D256" s="3" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="E256" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="257" customFormat="false" ht="13.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A257" s="3" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B257" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C257" s="8" t="s">
-        <v>561</v>
-      </c>
-      <c r="D257" s="4" t="s">
-        <v>562</v>
+        <v>26</v>
+      </c>
+      <c r="C257" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="D257" s="3" t="s">
+        <v>564</v>
       </c>
       <c r="E257" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="258" customFormat="false" ht="13.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A258" s="3" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B258" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C258" s="8" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="D258" s="4" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="E258" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="259" customFormat="false" ht="13.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A259" s="3" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B259" s="3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C259" s="8" t="s">
-        <v>565</v>
-      </c>
-      <c r="D259" s="3" t="s">
-        <v>566</v>
+        <v>567</v>
+      </c>
+      <c r="D259" s="4" t="s">
+        <v>568</v>
       </c>
       <c r="E259" s="3" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="260" customFormat="false" ht="13.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A260" s="3" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B260" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C260" s="3" t="s">
-        <v>567</v>
+        <v>35</v>
+      </c>
+      <c r="C260" s="8" t="s">
+        <v>569</v>
       </c>
       <c r="D260" s="3" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="E260" s="3" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="261" customFormat="false" ht="13.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A261" s="3" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B261" s="3" t="s">
-        <v>569</v>
-      </c>
-      <c r="C261" s="5" t="s">
-        <v>570</v>
+        <v>39</v>
+      </c>
+      <c r="C261" s="3" t="s">
+        <v>571</v>
       </c>
       <c r="D261" s="3" t="s">
-        <v>551</v>
+        <v>572</v>
       </c>
       <c r="E261" s="3" t="s">
-        <v>571</v>
+        <v>41</v>
       </c>
     </row>
     <row r="262" customFormat="false" ht="13.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A262" s="3" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B262" s="3" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C262" s="5" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="D262" s="3" t="s">
         <v>555</v>
       </c>
       <c r="E262" s="3" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="263" customFormat="false" ht="13.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A263" s="3" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B263" s="3" t="s">
-        <v>575</v>
-      </c>
-      <c r="C263" s="8" t="s">
         <v>576</v>
       </c>
+      <c r="C263" s="5" t="s">
+        <v>577</v>
+      </c>
       <c r="D263" s="3" t="s">
-        <v>577</v>
+        <v>559</v>
       </c>
       <c r="E263" s="3" t="s">
-        <v>44</v>
+        <v>578</v>
       </c>
     </row>
     <row r="264" customFormat="false" ht="13.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A264" s="3" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B264" s="3" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C264" s="8" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="D264" s="3" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="E264" s="3" t="s">
-        <v>581</v>
+        <v>44</v>
       </c>
     </row>
     <row r="265" customFormat="false" ht="13.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A265" s="3" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B265" s="3" t="s">
-        <v>47</v>
+        <v>582</v>
       </c>
       <c r="C265" s="8" t="s">
-        <v>582</v>
-      </c>
-      <c r="D265" s="4" t="s">
         <v>583</v>
       </c>
+      <c r="D265" s="3" t="s">
+        <v>584</v>
+      </c>
       <c r="E265" s="3" t="s">
-        <v>49</v>
+        <v>585</v>
       </c>
     </row>
     <row r="266" customFormat="false" ht="13.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A266" s="3" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B266" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C266" s="8" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="D266" s="4" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="E266" s="3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="267" customFormat="false" ht="13.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A267" s="3" t="s">
-        <v>538</v>
-      </c>
-      <c r="B267" s="0" t="s">
-        <v>586</v>
-      </c>
-      <c r="C267" s="9" t="s">
-        <v>587</v>
-      </c>
-      <c r="D267" s="0" t="s">
+        <v>542</v>
+      </c>
+      <c r="B267" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C267" s="8" t="s">
         <v>588</v>
       </c>
-      <c r="E267" s="0" t="s">
+      <c r="D267" s="4" t="s">
         <v>589</v>
       </c>
-      <c r="F267" s="0"/>
-      <c r="G267" s="0"/>
-      <c r="H267" s="0"/>
-      <c r="I267" s="0"/>
-      <c r="J267" s="0"/>
-      <c r="K267" s="0"/>
-      <c r="L267" s="0"/>
-      <c r="M267" s="0"/>
-      <c r="N267" s="0"/>
-      <c r="O267" s="0"/>
-      <c r="P267" s="0"/>
-      <c r="Q267" s="0"/>
-      <c r="R267" s="0"/>
-      <c r="S267" s="0"/>
-      <c r="T267" s="0"/>
-      <c r="U267" s="0"/>
-      <c r="V267" s="0"/>
-      <c r="W267" s="0"/>
-      <c r="X267" s="0"/>
-      <c r="Y267" s="0"/>
-      <c r="Z267" s="0"/>
-      <c r="AA267" s="0"/>
-      <c r="AB267" s="0"/>
-      <c r="AC267" s="0"/>
-      <c r="AD267" s="0"/>
-      <c r="AE267" s="0"/>
-      <c r="AF267" s="0"/>
-      <c r="AG267" s="0"/>
-      <c r="AH267" s="0"/>
-      <c r="AI267" s="0"/>
-      <c r="AJ267" s="0"/>
-      <c r="AK267" s="0"/>
-      <c r="AL267" s="0"/>
-      <c r="AM267" s="0"/>
-      <c r="AN267" s="0"/>
-      <c r="AO267" s="0"/>
-      <c r="AP267" s="0"/>
-      <c r="AQ267" s="0"/>
-      <c r="AR267" s="0"/>
-      <c r="AS267" s="0"/>
-      <c r="AT267" s="0"/>
-      <c r="AU267" s="0"/>
-      <c r="AV267" s="0"/>
-      <c r="AW267" s="0"/>
-      <c r="AX267" s="0"/>
-      <c r="AY267" s="0"/>
-      <c r="AZ267" s="0"/>
-      <c r="BA267" s="0"/>
-      <c r="BB267" s="0"/>
-      <c r="BC267" s="0"/>
-      <c r="BD267" s="0"/>
-      <c r="BE267" s="0"/>
-      <c r="BF267" s="0"/>
-      <c r="BG267" s="0"/>
-      <c r="BH267" s="0"/>
-      <c r="BI267" s="0"/>
-      <c r="BJ267" s="0"/>
-      <c r="BK267" s="0"/>
-      <c r="BL267" s="0"/>
-      <c r="BM267" s="0"/>
-      <c r="BN267" s="0"/>
-      <c r="BO267" s="0"/>
-      <c r="BP267" s="0"/>
-      <c r="BQ267" s="0"/>
-      <c r="BR267" s="0"/>
-      <c r="BS267" s="0"/>
-      <c r="BT267" s="0"/>
-      <c r="BU267" s="0"/>
-      <c r="BV267" s="0"/>
-      <c r="BW267" s="0"/>
-      <c r="BX267" s="0"/>
-      <c r="BY267" s="0"/>
-      <c r="BZ267" s="0"/>
-      <c r="CA267" s="0"/>
-      <c r="CB267" s="0"/>
-      <c r="CC267" s="0"/>
-      <c r="CD267" s="0"/>
-      <c r="CE267" s="0"/>
-      <c r="CF267" s="0"/>
-      <c r="CG267" s="0"/>
-      <c r="CH267" s="0"/>
-      <c r="CI267" s="0"/>
-      <c r="CJ267" s="0"/>
-      <c r="CK267" s="0"/>
-      <c r="CL267" s="0"/>
-      <c r="CM267" s="0"/>
-      <c r="CN267" s="0"/>
-      <c r="CO267" s="0"/>
-      <c r="CP267" s="0"/>
-      <c r="CQ267" s="0"/>
-      <c r="CR267" s="0"/>
-      <c r="CS267" s="0"/>
-      <c r="CT267" s="0"/>
-      <c r="CU267" s="0"/>
-      <c r="CV267" s="0"/>
-      <c r="CW267" s="0"/>
-      <c r="CX267" s="0"/>
-      <c r="CY267" s="0"/>
-      <c r="CZ267" s="0"/>
-      <c r="DA267" s="0"/>
-      <c r="DB267" s="0"/>
-      <c r="DC267" s="0"/>
-      <c r="DD267" s="0"/>
-      <c r="DE267" s="0"/>
-      <c r="DF267" s="0"/>
-      <c r="DG267" s="0"/>
-      <c r="DH267" s="0"/>
-      <c r="DI267" s="0"/>
-      <c r="DJ267" s="0"/>
-      <c r="DK267" s="0"/>
-      <c r="DL267" s="0"/>
-      <c r="DM267" s="0"/>
-      <c r="DN267" s="0"/>
-      <c r="DO267" s="0"/>
-      <c r="DP267" s="0"/>
-      <c r="DQ267" s="0"/>
-      <c r="DR267" s="0"/>
-      <c r="DS267" s="0"/>
-      <c r="DT267" s="0"/>
-      <c r="DU267" s="0"/>
-      <c r="DV267" s="0"/>
-      <c r="DW267" s="0"/>
-      <c r="DX267" s="0"/>
-      <c r="DY267" s="0"/>
-      <c r="DZ267" s="0"/>
-      <c r="EA267" s="0"/>
-      <c r="EB267" s="0"/>
-      <c r="EC267" s="0"/>
-      <c r="ED267" s="0"/>
-      <c r="EE267" s="0"/>
-      <c r="EF267" s="0"/>
-      <c r="EG267" s="0"/>
-      <c r="EH267" s="0"/>
-      <c r="EI267" s="0"/>
-      <c r="EJ267" s="0"/>
-      <c r="EK267" s="0"/>
-      <c r="EL267" s="0"/>
-      <c r="EM267" s="0"/>
-      <c r="EN267" s="0"/>
-      <c r="EO267" s="0"/>
-      <c r="EP267" s="0"/>
-      <c r="EQ267" s="0"/>
-      <c r="ER267" s="0"/>
-      <c r="ES267" s="0"/>
-      <c r="ET267" s="0"/>
-      <c r="EU267" s="0"/>
-      <c r="EV267" s="0"/>
-      <c r="EW267" s="0"/>
-      <c r="EX267" s="0"/>
-      <c r="EY267" s="0"/>
-      <c r="EZ267" s="0"/>
-      <c r="FA267" s="0"/>
-      <c r="FB267" s="0"/>
-      <c r="FC267" s="0"/>
-      <c r="FD267" s="0"/>
-      <c r="FE267" s="0"/>
-      <c r="FF267" s="0"/>
-      <c r="FG267" s="0"/>
-      <c r="FH267" s="0"/>
-      <c r="FI267" s="0"/>
-      <c r="FJ267" s="0"/>
-      <c r="FK267" s="0"/>
-      <c r="FL267" s="0"/>
-      <c r="FM267" s="0"/>
-      <c r="FN267" s="0"/>
-      <c r="FO267" s="0"/>
-      <c r="FP267" s="0"/>
-      <c r="FQ267" s="0"/>
-      <c r="FR267" s="0"/>
-      <c r="FS267" s="0"/>
-      <c r="FT267" s="0"/>
-      <c r="FU267" s="0"/>
-      <c r="FV267" s="0"/>
-      <c r="FW267" s="0"/>
-      <c r="FX267" s="0"/>
-      <c r="FY267" s="0"/>
-      <c r="FZ267" s="0"/>
-      <c r="GA267" s="0"/>
-      <c r="GB267" s="0"/>
-      <c r="GC267" s="0"/>
-      <c r="GD267" s="0"/>
-      <c r="GE267" s="0"/>
-      <c r="GF267" s="0"/>
-      <c r="GG267" s="0"/>
-      <c r="GH267" s="0"/>
-      <c r="GI267" s="0"/>
-      <c r="GJ267" s="0"/>
-      <c r="GK267" s="0"/>
-      <c r="GL267" s="0"/>
-      <c r="GM267" s="0"/>
-      <c r="GN267" s="0"/>
-      <c r="GO267" s="0"/>
-      <c r="GP267" s="0"/>
-      <c r="GQ267" s="0"/>
-      <c r="GR267" s="0"/>
-      <c r="GS267" s="0"/>
-      <c r="GT267" s="0"/>
-      <c r="GU267" s="0"/>
-      <c r="GV267" s="0"/>
-      <c r="GW267" s="0"/>
-      <c r="GX267" s="0"/>
-      <c r="GY267" s="0"/>
-      <c r="GZ267" s="0"/>
-      <c r="HA267" s="0"/>
-      <c r="HB267" s="0"/>
-      <c r="HC267" s="0"/>
-      <c r="HD267" s="0"/>
-      <c r="HE267" s="0"/>
-      <c r="HF267" s="0"/>
-      <c r="HG267" s="0"/>
-      <c r="HH267" s="0"/>
-      <c r="HI267" s="0"/>
-      <c r="HJ267" s="0"/>
-      <c r="HK267" s="0"/>
-      <c r="HL267" s="0"/>
-      <c r="HM267" s="0"/>
-      <c r="HN267" s="0"/>
-      <c r="HO267" s="0"/>
-      <c r="HP267" s="0"/>
-      <c r="HQ267" s="0"/>
-      <c r="HR267" s="0"/>
-      <c r="HS267" s="0"/>
-      <c r="HT267" s="0"/>
-      <c r="HU267" s="0"/>
-      <c r="HV267" s="0"/>
-      <c r="HW267" s="0"/>
-      <c r="HX267" s="0"/>
-      <c r="HY267" s="0"/>
-      <c r="HZ267" s="0"/>
-      <c r="IA267" s="0"/>
-      <c r="IB267" s="0"/>
-      <c r="IC267" s="0"/>
-      <c r="ID267" s="0"/>
-      <c r="IE267" s="0"/>
-      <c r="IF267" s="0"/>
-      <c r="IG267" s="0"/>
-      <c r="IH267" s="0"/>
-      <c r="II267" s="0"/>
-      <c r="IJ267" s="0"/>
-      <c r="IK267" s="0"/>
-      <c r="IL267" s="0"/>
-      <c r="IM267" s="0"/>
-      <c r="IN267" s="0"/>
-      <c r="IO267" s="0"/>
-      <c r="IP267" s="0"/>
-      <c r="IQ267" s="0"/>
-      <c r="IR267" s="0"/>
-      <c r="IS267" s="0"/>
-      <c r="IT267" s="0"/>
-      <c r="IU267" s="0"/>
-      <c r="IV267" s="0"/>
-      <c r="IW267" s="0"/>
-      <c r="IX267" s="0"/>
-      <c r="IY267" s="0"/>
-      <c r="IZ267" s="0"/>
-      <c r="JA267" s="0"/>
-      <c r="JB267" s="0"/>
-      <c r="JC267" s="0"/>
-      <c r="JD267" s="0"/>
-      <c r="JE267" s="0"/>
-      <c r="JF267" s="0"/>
-      <c r="JG267" s="0"/>
-      <c r="JH267" s="0"/>
-      <c r="JI267" s="0"/>
-      <c r="JJ267" s="0"/>
-      <c r="JK267" s="0"/>
-      <c r="JL267" s="0"/>
-      <c r="JM267" s="0"/>
-      <c r="JN267" s="0"/>
-      <c r="JO267" s="0"/>
-      <c r="JP267" s="0"/>
-      <c r="JQ267" s="0"/>
-      <c r="JR267" s="0"/>
-      <c r="JS267" s="0"/>
-      <c r="JT267" s="0"/>
-      <c r="JU267" s="0"/>
-      <c r="JV267" s="0"/>
-      <c r="JW267" s="0"/>
-      <c r="JX267" s="0"/>
-      <c r="JY267" s="0"/>
-      <c r="JZ267" s="0"/>
-      <c r="KA267" s="0"/>
-      <c r="KB267" s="0"/>
-      <c r="KC267" s="0"/>
-      <c r="KD267" s="0"/>
-      <c r="KE267" s="0"/>
-      <c r="KF267" s="0"/>
-      <c r="KG267" s="0"/>
-      <c r="KH267" s="0"/>
-      <c r="KI267" s="0"/>
-      <c r="KJ267" s="0"/>
-      <c r="KK267" s="0"/>
-      <c r="KL267" s="0"/>
-      <c r="KM267" s="0"/>
-      <c r="KN267" s="0"/>
-      <c r="KO267" s="0"/>
-      <c r="KP267" s="0"/>
-      <c r="KQ267" s="0"/>
-      <c r="KR267" s="0"/>
-      <c r="KS267" s="0"/>
-      <c r="KT267" s="0"/>
-      <c r="KU267" s="0"/>
-      <c r="KV267" s="0"/>
-      <c r="KW267" s="0"/>
-      <c r="KX267" s="0"/>
-      <c r="KY267" s="0"/>
-      <c r="KZ267" s="0"/>
-      <c r="LA267" s="0"/>
-      <c r="LB267" s="0"/>
-      <c r="LC267" s="0"/>
-      <c r="LD267" s="0"/>
-      <c r="LE267" s="0"/>
-      <c r="LF267" s="0"/>
-      <c r="LG267" s="0"/>
-      <c r="LH267" s="0"/>
-      <c r="LI267" s="0"/>
-      <c r="LJ267" s="0"/>
-      <c r="LK267" s="0"/>
-      <c r="LL267" s="0"/>
-      <c r="LM267" s="0"/>
-      <c r="LN267" s="0"/>
-      <c r="LO267" s="0"/>
-      <c r="LP267" s="0"/>
-      <c r="LQ267" s="0"/>
-      <c r="LR267" s="0"/>
-      <c r="LS267" s="0"/>
-      <c r="LT267" s="0"/>
-      <c r="LU267" s="0"/>
-      <c r="LV267" s="0"/>
-      <c r="LW267" s="0"/>
-      <c r="LX267" s="0"/>
-      <c r="LY267" s="0"/>
-      <c r="LZ267" s="0"/>
-      <c r="MA267" s="0"/>
-      <c r="MB267" s="0"/>
-      <c r="MC267" s="0"/>
-      <c r="MD267" s="0"/>
-      <c r="ME267" s="0"/>
-      <c r="MF267" s="0"/>
-      <c r="MG267" s="0"/>
-      <c r="MH267" s="0"/>
-      <c r="MI267" s="0"/>
-      <c r="MJ267" s="0"/>
-      <c r="MK267" s="0"/>
-      <c r="ML267" s="0"/>
-      <c r="MM267" s="0"/>
-      <c r="MN267" s="0"/>
-      <c r="MO267" s="0"/>
-      <c r="MP267" s="0"/>
-      <c r="MQ267" s="0"/>
-      <c r="MR267" s="0"/>
-      <c r="MS267" s="0"/>
-      <c r="MT267" s="0"/>
-      <c r="MU267" s="0"/>
-      <c r="MV267" s="0"/>
-      <c r="MW267" s="0"/>
-      <c r="MX267" s="0"/>
-      <c r="MY267" s="0"/>
-      <c r="MZ267" s="0"/>
-      <c r="NA267" s="0"/>
-      <c r="NB267" s="0"/>
-      <c r="NC267" s="0"/>
-      <c r="ND267" s="0"/>
-      <c r="NE267" s="0"/>
-      <c r="NF267" s="0"/>
-      <c r="NG267" s="0"/>
-      <c r="NH267" s="0"/>
-      <c r="NI267" s="0"/>
-      <c r="NJ267" s="0"/>
-      <c r="NK267" s="0"/>
-      <c r="NL267" s="0"/>
-      <c r="NM267" s="0"/>
-      <c r="NN267" s="0"/>
-      <c r="NO267" s="0"/>
-      <c r="NP267" s="0"/>
-      <c r="NQ267" s="0"/>
-      <c r="NR267" s="0"/>
-      <c r="NS267" s="0"/>
-      <c r="NT267" s="0"/>
-      <c r="NU267" s="0"/>
-      <c r="NV267" s="0"/>
-      <c r="NW267" s="0"/>
-      <c r="NX267" s="0"/>
-      <c r="NY267" s="0"/>
-      <c r="NZ267" s="0"/>
-      <c r="OA267" s="0"/>
-      <c r="OB267" s="0"/>
-      <c r="OC267" s="0"/>
-      <c r="OD267" s="0"/>
-      <c r="OE267" s="0"/>
-      <c r="OF267" s="0"/>
-      <c r="OG267" s="0"/>
-      <c r="OH267" s="0"/>
-      <c r="OI267" s="0"/>
-      <c r="OJ267" s="0"/>
-      <c r="OK267" s="0"/>
-      <c r="OL267" s="0"/>
-      <c r="OM267" s="0"/>
-      <c r="ON267" s="0"/>
-      <c r="OO267" s="0"/>
-      <c r="OP267" s="0"/>
-      <c r="OQ267" s="0"/>
-      <c r="OR267" s="0"/>
-      <c r="OS267" s="0"/>
-      <c r="OT267" s="0"/>
-      <c r="OU267" s="0"/>
-      <c r="OV267" s="0"/>
-      <c r="OW267" s="0"/>
-      <c r="OX267" s="0"/>
-      <c r="OY267" s="0"/>
-      <c r="OZ267" s="0"/>
-      <c r="PA267" s="0"/>
-      <c r="PB267" s="0"/>
-      <c r="PC267" s="0"/>
-      <c r="PD267" s="0"/>
-      <c r="PE267" s="0"/>
-      <c r="PF267" s="0"/>
-      <c r="PG267" s="0"/>
-      <c r="PH267" s="0"/>
-      <c r="PI267" s="0"/>
-      <c r="PJ267" s="0"/>
-      <c r="PK267" s="0"/>
-      <c r="PL267" s="0"/>
-      <c r="PM267" s="0"/>
-      <c r="PN267" s="0"/>
-      <c r="PO267" s="0"/>
-      <c r="PP267" s="0"/>
-      <c r="PQ267" s="0"/>
-      <c r="PR267" s="0"/>
-      <c r="PS267" s="0"/>
-      <c r="PT267" s="0"/>
-      <c r="PU267" s="0"/>
-      <c r="PV267" s="0"/>
-      <c r="PW267" s="0"/>
-      <c r="PX267" s="0"/>
-      <c r="PY267" s="0"/>
-      <c r="PZ267" s="0"/>
-      <c r="QA267" s="0"/>
-      <c r="QB267" s="0"/>
-      <c r="QC267" s="0"/>
-      <c r="QD267" s="0"/>
-      <c r="QE267" s="0"/>
-      <c r="QF267" s="0"/>
-      <c r="QG267" s="0"/>
-      <c r="QH267" s="0"/>
-      <c r="QI267" s="0"/>
-      <c r="QJ267" s="0"/>
-      <c r="QK267" s="0"/>
-      <c r="QL267" s="0"/>
-      <c r="QM267" s="0"/>
-      <c r="QN267" s="0"/>
-      <c r="QO267" s="0"/>
-      <c r="QP267" s="0"/>
-      <c r="QQ267" s="0"/>
-      <c r="QR267" s="0"/>
-      <c r="QS267" s="0"/>
-      <c r="QT267" s="0"/>
-      <c r="QU267" s="0"/>
-      <c r="QV267" s="0"/>
-      <c r="QW267" s="0"/>
-      <c r="QX267" s="0"/>
-      <c r="QY267" s="0"/>
-      <c r="QZ267" s="0"/>
-      <c r="RA267" s="0"/>
-      <c r="RB267" s="0"/>
-      <c r="RC267" s="0"/>
-      <c r="RD267" s="0"/>
-      <c r="RE267" s="0"/>
-      <c r="RF267" s="0"/>
-      <c r="RG267" s="0"/>
-      <c r="RH267" s="0"/>
-      <c r="RI267" s="0"/>
-      <c r="RJ267" s="0"/>
-      <c r="RK267" s="0"/>
-      <c r="RL267" s="0"/>
-      <c r="RM267" s="0"/>
-      <c r="RN267" s="0"/>
-      <c r="RO267" s="0"/>
-      <c r="RP267" s="0"/>
-      <c r="RQ267" s="0"/>
-      <c r="RR267" s="0"/>
-      <c r="RS267" s="0"/>
-      <c r="RT267" s="0"/>
-      <c r="RU267" s="0"/>
-      <c r="RV267" s="0"/>
-      <c r="RW267" s="0"/>
-      <c r="RX267" s="0"/>
-      <c r="RY267" s="0"/>
-      <c r="RZ267" s="0"/>
-      <c r="SA267" s="0"/>
-      <c r="SB267" s="0"/>
-      <c r="SC267" s="0"/>
-      <c r="SD267" s="0"/>
-      <c r="SE267" s="0"/>
-      <c r="SF267" s="0"/>
-      <c r="SG267" s="0"/>
-      <c r="SH267" s="0"/>
-      <c r="SI267" s="0"/>
-      <c r="SJ267" s="0"/>
-      <c r="SK267" s="0"/>
-      <c r="SL267" s="0"/>
-      <c r="SM267" s="0"/>
-      <c r="SN267" s="0"/>
-      <c r="SO267" s="0"/>
-      <c r="SP267" s="0"/>
-      <c r="SQ267" s="0"/>
-      <c r="SR267" s="0"/>
-      <c r="SS267" s="0"/>
-      <c r="ST267" s="0"/>
-      <c r="SU267" s="0"/>
-      <c r="SV267" s="0"/>
-      <c r="SW267" s="0"/>
-      <c r="SX267" s="0"/>
-      <c r="SY267" s="0"/>
-      <c r="SZ267" s="0"/>
-      <c r="TA267" s="0"/>
-      <c r="TB267" s="0"/>
-      <c r="TC267" s="0"/>
-      <c r="TD267" s="0"/>
-      <c r="TE267" s="0"/>
-      <c r="TF267" s="0"/>
-      <c r="TG267" s="0"/>
-      <c r="TH267" s="0"/>
-      <c r="TI267" s="0"/>
-      <c r="TJ267" s="0"/>
-      <c r="TK267" s="0"/>
-      <c r="TL267" s="0"/>
-      <c r="TM267" s="0"/>
-      <c r="TN267" s="0"/>
-      <c r="TO267" s="0"/>
-      <c r="TP267" s="0"/>
-      <c r="TQ267" s="0"/>
-      <c r="TR267" s="0"/>
-      <c r="TS267" s="0"/>
-      <c r="TT267" s="0"/>
-      <c r="TU267" s="0"/>
-      <c r="TV267" s="0"/>
-      <c r="TW267" s="0"/>
-      <c r="TX267" s="0"/>
-      <c r="TY267" s="0"/>
-      <c r="TZ267" s="0"/>
-      <c r="UA267" s="0"/>
-      <c r="UB267" s="0"/>
-      <c r="UC267" s="0"/>
-      <c r="UD267" s="0"/>
-      <c r="UE267" s="0"/>
-      <c r="UF267" s="0"/>
-      <c r="UG267" s="0"/>
-      <c r="UH267" s="0"/>
-      <c r="UI267" s="0"/>
-      <c r="UJ267" s="0"/>
-      <c r="UK267" s="0"/>
-      <c r="UL267" s="0"/>
-      <c r="UM267" s="0"/>
-      <c r="UN267" s="0"/>
-      <c r="UO267" s="0"/>
-      <c r="UP267" s="0"/>
-      <c r="UQ267" s="0"/>
-      <c r="UR267" s="0"/>
-      <c r="US267" s="0"/>
-      <c r="UT267" s="0"/>
-      <c r="UU267" s="0"/>
-      <c r="UV267" s="0"/>
-      <c r="UW267" s="0"/>
-      <c r="UX267" s="0"/>
-      <c r="UY267" s="0"/>
-      <c r="UZ267" s="0"/>
-      <c r="VA267" s="0"/>
-      <c r="VB267" s="0"/>
-      <c r="VC267" s="0"/>
-      <c r="VD267" s="0"/>
-      <c r="VE267" s="0"/>
-      <c r="VF267" s="0"/>
-      <c r="VG267" s="0"/>
-      <c r="VH267" s="0"/>
-      <c r="VI267" s="0"/>
-      <c r="VJ267" s="0"/>
-      <c r="VK267" s="0"/>
-      <c r="VL267" s="0"/>
-      <c r="VM267" s="0"/>
-      <c r="VN267" s="0"/>
-      <c r="VO267" s="0"/>
-      <c r="VP267" s="0"/>
-      <c r="VQ267" s="0"/>
-      <c r="VR267" s="0"/>
-      <c r="VS267" s="0"/>
-      <c r="VT267" s="0"/>
-      <c r="VU267" s="0"/>
-      <c r="VV267" s="0"/>
-      <c r="VW267" s="0"/>
-      <c r="VX267" s="0"/>
-      <c r="VY267" s="0"/>
-      <c r="VZ267" s="0"/>
-      <c r="WA267" s="0"/>
-      <c r="WB267" s="0"/>
-      <c r="WC267" s="0"/>
-      <c r="WD267" s="0"/>
-      <c r="WE267" s="0"/>
-      <c r="WF267" s="0"/>
-      <c r="WG267" s="0"/>
-      <c r="WH267" s="0"/>
-      <c r="WI267" s="0"/>
-      <c r="WJ267" s="0"/>
-      <c r="WK267" s="0"/>
-      <c r="WL267" s="0"/>
-      <c r="WM267" s="0"/>
-      <c r="WN267" s="0"/>
-      <c r="WO267" s="0"/>
-      <c r="WP267" s="0"/>
-      <c r="WQ267" s="0"/>
-      <c r="WR267" s="0"/>
-      <c r="WS267" s="0"/>
-      <c r="WT267" s="0"/>
-      <c r="WU267" s="0"/>
-      <c r="WV267" s="0"/>
-      <c r="WW267" s="0"/>
-      <c r="WX267" s="0"/>
-      <c r="WY267" s="0"/>
-      <c r="WZ267" s="0"/>
-      <c r="XA267" s="0"/>
-      <c r="XB267" s="0"/>
-      <c r="XC267" s="0"/>
-      <c r="XD267" s="0"/>
-      <c r="XE267" s="0"/>
-      <c r="XF267" s="0"/>
-      <c r="XG267" s="0"/>
-      <c r="XH267" s="0"/>
-      <c r="XI267" s="0"/>
-      <c r="XJ267" s="0"/>
-      <c r="XK267" s="0"/>
-      <c r="XL267" s="0"/>
-      <c r="XM267" s="0"/>
-      <c r="XN267" s="0"/>
-      <c r="XO267" s="0"/>
-      <c r="XP267" s="0"/>
-      <c r="XQ267" s="0"/>
-      <c r="XR267" s="0"/>
-      <c r="XS267" s="0"/>
-      <c r="XT267" s="0"/>
-      <c r="XU267" s="0"/>
-      <c r="XV267" s="0"/>
-      <c r="XW267" s="0"/>
-      <c r="XX267" s="0"/>
-      <c r="XY267" s="0"/>
-      <c r="XZ267" s="0"/>
-      <c r="YA267" s="0"/>
-      <c r="YB267" s="0"/>
-      <c r="YC267" s="0"/>
-      <c r="YD267" s="0"/>
-      <c r="YE267" s="0"/>
-      <c r="YF267" s="0"/>
-      <c r="YG267" s="0"/>
-      <c r="YH267" s="0"/>
-      <c r="YI267" s="0"/>
-      <c r="YJ267" s="0"/>
-      <c r="YK267" s="0"/>
-      <c r="YL267" s="0"/>
-      <c r="YM267" s="0"/>
-      <c r="YN267" s="0"/>
-      <c r="YO267" s="0"/>
-      <c r="YP267" s="0"/>
-      <c r="YQ267" s="0"/>
-      <c r="YR267" s="0"/>
-      <c r="YS267" s="0"/>
-      <c r="YT267" s="0"/>
-      <c r="YU267" s="0"/>
-      <c r="YV267" s="0"/>
-      <c r="YW267" s="0"/>
-      <c r="YX267" s="0"/>
-      <c r="YY267" s="0"/>
-      <c r="YZ267" s="0"/>
-      <c r="ZA267" s="0"/>
-      <c r="ZB267" s="0"/>
-      <c r="ZC267" s="0"/>
-      <c r="ZD267" s="0"/>
-      <c r="ZE267" s="0"/>
-      <c r="ZF267" s="0"/>
-      <c r="ZG267" s="0"/>
-      <c r="ZH267" s="0"/>
-      <c r="ZI267" s="0"/>
-      <c r="ZJ267" s="0"/>
-      <c r="ZK267" s="0"/>
-      <c r="ZL267" s="0"/>
-      <c r="ZM267" s="0"/>
-      <c r="ZN267" s="0"/>
-      <c r="ZO267" s="0"/>
-      <c r="ZP267" s="0"/>
-      <c r="ZQ267" s="0"/>
-      <c r="ZR267" s="0"/>
-      <c r="ZS267" s="0"/>
-      <c r="ZT267" s="0"/>
-      <c r="ZU267" s="0"/>
-      <c r="ZV267" s="0"/>
-      <c r="ZW267" s="0"/>
-      <c r="ZX267" s="0"/>
-      <c r="ZY267" s="0"/>
-      <c r="ZZ267" s="0"/>
-      <c r="AAA267" s="0"/>
-      <c r="AAB267" s="0"/>
-      <c r="AAC267" s="0"/>
-      <c r="AAD267" s="0"/>
-      <c r="AAE267" s="0"/>
-      <c r="AAF267" s="0"/>
-      <c r="AAG267" s="0"/>
-      <c r="AAH267" s="0"/>
-      <c r="AAI267" s="0"/>
-      <c r="AAJ267" s="0"/>
-      <c r="AAK267" s="0"/>
-      <c r="AAL267" s="0"/>
-      <c r="AAM267" s="0"/>
-      <c r="AAN267" s="0"/>
-      <c r="AAO267" s="0"/>
-      <c r="AAP267" s="0"/>
-      <c r="AAQ267" s="0"/>
-      <c r="AAR267" s="0"/>
-      <c r="AAS267" s="0"/>
-      <c r="AAT267" s="0"/>
-      <c r="AAU267" s="0"/>
-      <c r="AAV267" s="0"/>
-      <c r="AAW267" s="0"/>
-      <c r="AAX267" s="0"/>
-      <c r="AAY267" s="0"/>
-      <c r="AAZ267" s="0"/>
-      <c r="ABA267" s="0"/>
-      <c r="ABB267" s="0"/>
-      <c r="ABC267" s="0"/>
-      <c r="ABD267" s="0"/>
-      <c r="ABE267" s="0"/>
-      <c r="ABF267" s="0"/>
-      <c r="ABG267" s="0"/>
-      <c r="ABH267" s="0"/>
-      <c r="ABI267" s="0"/>
-      <c r="ABJ267" s="0"/>
-      <c r="ABK267" s="0"/>
-      <c r="ABL267" s="0"/>
-      <c r="ABM267" s="0"/>
-      <c r="ABN267" s="0"/>
-      <c r="ABO267" s="0"/>
-      <c r="ABP267" s="0"/>
-      <c r="ABQ267" s="0"/>
-      <c r="ABR267" s="0"/>
-      <c r="ABS267" s="0"/>
-      <c r="ABT267" s="0"/>
-      <c r="ABU267" s="0"/>
-      <c r="ABV267" s="0"/>
-      <c r="ABW267" s="0"/>
-      <c r="ABX267" s="0"/>
-      <c r="ABY267" s="0"/>
-      <c r="ABZ267" s="0"/>
-      <c r="ACA267" s="0"/>
-      <c r="ACB267" s="0"/>
-      <c r="ACC267" s="0"/>
-      <c r="ACD267" s="0"/>
-      <c r="ACE267" s="0"/>
-      <c r="ACF267" s="0"/>
-      <c r="ACG267" s="0"/>
-      <c r="ACH267" s="0"/>
-      <c r="ACI267" s="0"/>
-      <c r="ACJ267" s="0"/>
-      <c r="ACK267" s="0"/>
-      <c r="ACL267" s="0"/>
-      <c r="ACM267" s="0"/>
-      <c r="ACN267" s="0"/>
-      <c r="ACO267" s="0"/>
-      <c r="ACP267" s="0"/>
-      <c r="ACQ267" s="0"/>
-      <c r="ACR267" s="0"/>
-      <c r="ACS267" s="0"/>
-      <c r="ACT267" s="0"/>
-      <c r="ACU267" s="0"/>
-      <c r="ACV267" s="0"/>
-      <c r="ACW267" s="0"/>
-      <c r="ACX267" s="0"/>
-      <c r="ACY267" s="0"/>
-      <c r="ACZ267" s="0"/>
-      <c r="ADA267" s="0"/>
-      <c r="ADB267" s="0"/>
-      <c r="ADC267" s="0"/>
-      <c r="ADD267" s="0"/>
-      <c r="ADE267" s="0"/>
-      <c r="ADF267" s="0"/>
-      <c r="ADG267" s="0"/>
-      <c r="ADH267" s="0"/>
-      <c r="ADI267" s="0"/>
-      <c r="ADJ267" s="0"/>
-      <c r="ADK267" s="0"/>
-      <c r="ADL267" s="0"/>
-      <c r="ADM267" s="0"/>
-      <c r="ADN267" s="0"/>
-      <c r="ADO267" s="0"/>
-      <c r="ADP267" s="0"/>
-      <c r="ADQ267" s="0"/>
-      <c r="ADR267" s="0"/>
-      <c r="ADS267" s="0"/>
-      <c r="ADT267" s="0"/>
-      <c r="ADU267" s="0"/>
-      <c r="ADV267" s="0"/>
-      <c r="ADW267" s="0"/>
-      <c r="ADX267" s="0"/>
-      <c r="ADY267" s="0"/>
-      <c r="ADZ267" s="0"/>
-      <c r="AEA267" s="0"/>
-      <c r="AEB267" s="0"/>
-      <c r="AEC267" s="0"/>
-      <c r="AED267" s="0"/>
-      <c r="AEE267" s="0"/>
-      <c r="AEF267" s="0"/>
-      <c r="AEG267" s="0"/>
-      <c r="AEH267" s="0"/>
-      <c r="AEI267" s="0"/>
-      <c r="AEJ267" s="0"/>
-      <c r="AEK267" s="0"/>
-      <c r="AEL267" s="0"/>
-      <c r="AEM267" s="0"/>
-      <c r="AEN267" s="0"/>
-      <c r="AEO267" s="0"/>
-      <c r="AEP267" s="0"/>
-      <c r="AEQ267" s="0"/>
-      <c r="AER267" s="0"/>
-      <c r="AES267" s="0"/>
-      <c r="AET267" s="0"/>
-      <c r="AEU267" s="0"/>
-      <c r="AEV267" s="0"/>
-      <c r="AEW267" s="0"/>
-      <c r="AEX267" s="0"/>
-      <c r="AEY267" s="0"/>
-      <c r="AEZ267" s="0"/>
-      <c r="AFA267" s="0"/>
-      <c r="AFB267" s="0"/>
-      <c r="AFC267" s="0"/>
-      <c r="AFD267" s="0"/>
-      <c r="AFE267" s="0"/>
-      <c r="AFF267" s="0"/>
-      <c r="AFG267" s="0"/>
-      <c r="AFH267" s="0"/>
-      <c r="AFI267" s="0"/>
-      <c r="AFJ267" s="0"/>
-      <c r="AFK267" s="0"/>
-      <c r="AFL267" s="0"/>
-      <c r="AFM267" s="0"/>
-      <c r="AFN267" s="0"/>
-      <c r="AFO267" s="0"/>
-      <c r="AFP267" s="0"/>
-      <c r="AFQ267" s="0"/>
-      <c r="AFR267" s="0"/>
-      <c r="AFS267" s="0"/>
-      <c r="AFT267" s="0"/>
-      <c r="AFU267" s="0"/>
-      <c r="AFV267" s="0"/>
-      <c r="AFW267" s="0"/>
-      <c r="AFX267" s="0"/>
-      <c r="AFY267" s="0"/>
-      <c r="AFZ267" s="0"/>
-      <c r="AGA267" s="0"/>
-      <c r="AGB267" s="0"/>
-      <c r="AGC267" s="0"/>
-      <c r="AGD267" s="0"/>
-      <c r="AGE267" s="0"/>
-      <c r="AGF267" s="0"/>
-      <c r="AGG267" s="0"/>
-      <c r="AGH267" s="0"/>
-      <c r="AGI267" s="0"/>
-      <c r="AGJ267" s="0"/>
-      <c r="AGK267" s="0"/>
-      <c r="AGL267" s="0"/>
-      <c r="AGM267" s="0"/>
-      <c r="AGN267" s="0"/>
-      <c r="AGO267" s="0"/>
-      <c r="AGP267" s="0"/>
-      <c r="AGQ267" s="0"/>
-      <c r="AGR267" s="0"/>
-      <c r="AGS267" s="0"/>
-      <c r="AGT267" s="0"/>
-      <c r="AGU267" s="0"/>
-      <c r="AGV267" s="0"/>
-      <c r="AGW267" s="0"/>
-      <c r="AGX267" s="0"/>
-      <c r="AGY267" s="0"/>
-      <c r="AGZ267" s="0"/>
-      <c r="AHA267" s="0"/>
-      <c r="AHB267" s="0"/>
-      <c r="AHC267" s="0"/>
-      <c r="AHD267" s="0"/>
-      <c r="AHE267" s="0"/>
-      <c r="AHF267" s="0"/>
-      <c r="AHG267" s="0"/>
-      <c r="AHH267" s="0"/>
-      <c r="AHI267" s="0"/>
-      <c r="AHJ267" s="0"/>
-      <c r="AHK267" s="0"/>
-      <c r="AHL267" s="0"/>
-      <c r="AHM267" s="0"/>
-      <c r="AHN267" s="0"/>
-      <c r="AHO267" s="0"/>
-      <c r="AHP267" s="0"/>
-      <c r="AHQ267" s="0"/>
-      <c r="AHR267" s="0"/>
-      <c r="AHS267" s="0"/>
-      <c r="AHT267" s="0"/>
-      <c r="AHU267" s="0"/>
-      <c r="AHV267" s="0"/>
-      <c r="AHW267" s="0"/>
-      <c r="AHX267" s="0"/>
-      <c r="AHY267" s="0"/>
-      <c r="AHZ267" s="0"/>
-      <c r="AIA267" s="0"/>
-      <c r="AIB267" s="0"/>
-      <c r="AIC267" s="0"/>
-      <c r="AID267" s="0"/>
-      <c r="AIE267" s="0"/>
-      <c r="AIF267" s="0"/>
-      <c r="AIG267" s="0"/>
-      <c r="AIH267" s="0"/>
-      <c r="AII267" s="0"/>
-      <c r="AIJ267" s="0"/>
-      <c r="AIK267" s="0"/>
-      <c r="AIL267" s="0"/>
-      <c r="AIM267" s="0"/>
-      <c r="AIN267" s="0"/>
-      <c r="AIO267" s="0"/>
-      <c r="AIP267" s="0"/>
-      <c r="AIQ267" s="0"/>
-      <c r="AIR267" s="0"/>
-      <c r="AIS267" s="0"/>
-      <c r="AIT267" s="0"/>
-      <c r="AIU267" s="0"/>
-      <c r="AIV267" s="0"/>
-      <c r="AIW267" s="0"/>
-      <c r="AIX267" s="0"/>
-      <c r="AIY267" s="0"/>
-      <c r="AIZ267" s="0"/>
-      <c r="AJA267" s="0"/>
-      <c r="AJB267" s="0"/>
-      <c r="AJC267" s="0"/>
-      <c r="AJD267" s="0"/>
-      <c r="AJE267" s="0"/>
-      <c r="AJF267" s="0"/>
-      <c r="AJG267" s="0"/>
-      <c r="AJH267" s="0"/>
-      <c r="AJI267" s="0"/>
-      <c r="AJJ267" s="0"/>
-      <c r="AJK267" s="0"/>
-      <c r="AJL267" s="0"/>
-      <c r="AJM267" s="0"/>
-      <c r="AJN267" s="0"/>
-      <c r="AJO267" s="0"/>
-      <c r="AJP267" s="0"/>
-      <c r="AJQ267" s="0"/>
-      <c r="AJR267" s="0"/>
-      <c r="AJS267" s="0"/>
-      <c r="AJT267" s="0"/>
-      <c r="AJU267" s="0"/>
-      <c r="AJV267" s="0"/>
-      <c r="AJW267" s="0"/>
-      <c r="AJX267" s="0"/>
-      <c r="AJY267" s="0"/>
-      <c r="AJZ267" s="0"/>
-      <c r="AKA267" s="0"/>
-      <c r="AKB267" s="0"/>
-      <c r="AKC267" s="0"/>
-      <c r="AKD267" s="0"/>
-      <c r="AKE267" s="0"/>
-      <c r="AKF267" s="0"/>
-      <c r="AKG267" s="0"/>
-      <c r="AKH267" s="0"/>
-      <c r="AKI267" s="0"/>
-      <c r="AKJ267" s="0"/>
-      <c r="AKK267" s="0"/>
-      <c r="AKL267" s="0"/>
-      <c r="AKM267" s="0"/>
-      <c r="AKN267" s="0"/>
-      <c r="AKO267" s="0"/>
-      <c r="AKP267" s="0"/>
-      <c r="AKQ267" s="0"/>
-      <c r="AKR267" s="0"/>
-      <c r="AKS267" s="0"/>
-      <c r="AKT267" s="0"/>
-      <c r="AKU267" s="0"/>
-      <c r="AKV267" s="0"/>
-      <c r="AKW267" s="0"/>
-      <c r="AKX267" s="0"/>
-      <c r="AKY267" s="0"/>
-      <c r="AKZ267" s="0"/>
-      <c r="ALA267" s="0"/>
-      <c r="ALB267" s="0"/>
-      <c r="ALC267" s="0"/>
-      <c r="ALD267" s="0"/>
-      <c r="ALE267" s="0"/>
-      <c r="ALF267" s="0"/>
-      <c r="ALG267" s="0"/>
-      <c r="ALH267" s="0"/>
-      <c r="ALI267" s="0"/>
-      <c r="ALJ267" s="0"/>
-      <c r="ALK267" s="0"/>
-      <c r="ALL267" s="0"/>
-      <c r="ALM267" s="0"/>
-      <c r="ALN267" s="0"/>
-      <c r="ALO267" s="0"/>
-      <c r="ALP267" s="0"/>
-      <c r="ALQ267" s="0"/>
-      <c r="ALR267" s="0"/>
-      <c r="ALS267" s="0"/>
-      <c r="ALT267" s="0"/>
-      <c r="ALU267" s="0"/>
-      <c r="ALV267" s="0"/>
-      <c r="ALW267" s="0"/>
-      <c r="ALX267" s="0"/>
-      <c r="ALY267" s="0"/>
-      <c r="ALZ267" s="0"/>
-      <c r="AMA267" s="0"/>
-      <c r="AMB267" s="0"/>
-      <c r="AMC267" s="0"/>
-      <c r="AMD267" s="0"/>
-      <c r="AME267" s="0"/>
-      <c r="AMF267" s="0"/>
-      <c r="AMG267" s="0"/>
-      <c r="AMH267" s="0"/>
-      <c r="AMI267" s="0"/>
-      <c r="AMJ267" s="0"/>
+      <c r="E267" s="3" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="268" s="8" customFormat="true" ht="13.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A268" s="3" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B268" s="8" t="s">
         <v>590</v>
       </c>
-      <c r="C268" s="9" t="s">
+      <c r="C268" s="8" t="s">
         <v>591</v>
       </c>
       <c r="D268" s="8" t="s">
@@ -6912,137 +5892,153 @@
         <v>593</v>
       </c>
     </row>
-    <row r="269" customFormat="false" ht="13.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="269" s="8" customFormat="true" ht="13.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A269" s="3" t="s">
-        <v>538</v>
-      </c>
-      <c r="B269" s="3" t="s">
-        <v>53</v>
+        <v>542</v>
+      </c>
+      <c r="B269" s="8" t="s">
+        <v>594</v>
       </c>
       <c r="C269" s="8" t="s">
-        <v>594</v>
-      </c>
-      <c r="D269" s="3" t="s">
         <v>595</v>
       </c>
-      <c r="E269" s="3" t="s">
-        <v>56</v>
+      <c r="D269" s="8" t="s">
+        <v>596</v>
+      </c>
+      <c r="E269" s="8" t="s">
+        <v>597</v>
       </c>
     </row>
     <row r="270" customFormat="false" ht="13.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A270" s="3" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B270" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C270" s="3" t="s">
-        <v>67</v>
+        <v>53</v>
+      </c>
+      <c r="C270" s="8" t="s">
+        <v>598</v>
       </c>
       <c r="D270" s="3" t="s">
-        <v>68</v>
+        <v>599</v>
       </c>
       <c r="E270" s="3" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
     </row>
     <row r="271" customFormat="false" ht="13.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A271" s="3" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B271" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C271" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D271" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E271" s="3" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="272" customFormat="false" ht="13.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A272" s="3" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B272" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C272" s="3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D272" s="3" t="s">
         <v>72</v>
       </c>
       <c r="E272" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="273" customFormat="false" ht="13.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A273" s="3" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B273" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C273" s="3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D273" s="3" t="s">
         <v>72</v>
       </c>
       <c r="E273" s="3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="274" customFormat="false" ht="13.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A274" s="3" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B274" s="3" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="C274" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D274" s="4"/>
+        <v>78</v>
+      </c>
+      <c r="D274" s="3" t="s">
+        <v>72</v>
+      </c>
       <c r="E274" s="3" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="275" customFormat="false" ht="13.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A275" s="3" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B275" s="3" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="C275" s="3" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="D275" s="4"/>
       <c r="E275" s="3" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
     </row>
     <row r="276" customFormat="false" ht="13.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A276" s="3" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B276" s="3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C276" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D276" s="4"/>
       <c r="E276" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="277" customFormat="false" ht="13.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A277" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="B277" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C277" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D277" s="4"/>
+      <c r="E277" s="3" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>

--- a/ref/scTypeDB.xlsx
+++ b/ref/scTypeDB.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1193" uniqueCount="602">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1189" uniqueCount="602">
   <si>
     <t xml:space="preserve">tissueType</t>
   </si>
@@ -287,7 +287,7 @@
     <t xml:space="preserve">PTPRC,GYPA,RUVBL1,TFRC,FOLR1,CD36,ITGA4,HBB,CD235a,HBD,CA1</t>
   </si>
   <si>
-    <t xml:space="preserve">Es</t>
+    <t xml:space="preserve">Eryth</t>
   </si>
   <si>
     <t xml:space="preserve">HSC/MPP cells</t>
@@ -2221,7 +2221,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E290"/>
+  <dimension ref="A1:E1048576"/>
   <sheetFormatPr defaultColWidth="8.8515625" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.85"/>
@@ -6344,14 +6344,16 @@
         <v>542</v>
       </c>
       <c r="B282" s="22" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C282" s="22" t="s">
-        <v>87</v>
-      </c>
-      <c r="D282" s="25"/>
+        <v>90</v>
+      </c>
+      <c r="D282" s="22" t="s">
+        <v>91</v>
+      </c>
       <c r="E282" s="24" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="283" customFormat="false" ht="13.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6359,16 +6361,14 @@
         <v>542</v>
       </c>
       <c r="B283" s="22" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C283" s="22" t="s">
-        <v>90</v>
-      </c>
-      <c r="D283" s="22" t="s">
-        <v>91</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="D283" s="25"/>
       <c r="E283" s="24" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="284" customFormat="false" ht="13.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6376,14 +6376,14 @@
         <v>542</v>
       </c>
       <c r="B284" s="22" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="C284" s="22" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="D284" s="25"/>
       <c r="E284" s="24" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
     </row>
     <row r="285" customFormat="false" ht="13.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6391,14 +6391,14 @@
         <v>542</v>
       </c>
       <c r="B285" s="22" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C285" s="22" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D285" s="25"/>
       <c r="E285" s="24" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="286" customFormat="false" ht="13.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6406,14 +6406,14 @@
         <v>542</v>
       </c>
       <c r="B286" s="22" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C286" s="22" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D286" s="25"/>
       <c r="E286" s="24" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="287" customFormat="false" ht="13.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6421,61 +6421,47 @@
         <v>542</v>
       </c>
       <c r="B287" s="22" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C287" s="22" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D287" s="25"/>
       <c r="E287" s="24" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="288" customFormat="false" ht="13.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A288" s="21" t="s">
+      <c r="A288" s="26" t="s">
         <v>542</v>
       </c>
       <c r="B288" s="22" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C288" s="22" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D288" s="25"/>
       <c r="E288" s="24" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="289" customFormat="false" ht="13.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A289" s="26" t="s">
+      <c r="A289" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="B289" s="22" t="s">
-        <v>117</v>
-      </c>
-      <c r="C289" s="22" t="s">
-        <v>118</v>
-      </c>
-      <c r="D289" s="25"/>
-      <c r="E289" s="24" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="290" customFormat="false" ht="13.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A290" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="B290" s="26" t="s">
+      <c r="B289" s="26" t="s">
         <v>120</v>
       </c>
-      <c r="C290" s="27" t="s">
+      <c r="C289" s="27" t="s">
         <v>121</v>
       </c>
-      <c r="D290" s="28"/>
-      <c r="E290" s="29" t="s">
+      <c r="D289" s="28"/>
+      <c r="E289" s="29" t="s">
         <v>120</v>
       </c>
     </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.3"/>

--- a/ref/scTypeDB.xlsx
+++ b/ref/scTypeDB.xlsx
@@ -9,7 +9,6 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="Hoja 1" sheetId="2" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -21,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1189" uniqueCount="602">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1103" uniqueCount="603">
   <si>
     <t xml:space="preserve">tissueType</t>
   </si>
@@ -293,1540 +292,1543 @@
     <t xml:space="preserve">HSC/MPP cells</t>
   </si>
   <si>
+    <t xml:space="preserve">CD105,CD34,CD44,CD73,CD45,PTPRC,CD29,STRO-1,NANOG,SOX2,CD133,CD166,CD146,CD31,Nestin,OCT4,CD117,KDR,CXCL8,AVP,CRHBP,ALDH1A1,CD49,CD90,CD69,CD24,CD38,CD45RA,Keratin-19,ASPM,CD10,CD123,ABCG2,CD135,CD49f,EpCAM,Keratin-7,SCA-1,CD14,CD150,CD271,HLA-DR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PTPRC,CD38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSC/MPP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Progenitor cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CD105,CD34,CD44,CD73,CD45,CD29,STRO-1,NANOG,SOX2,CD133,CD166,CD146,CD31,Nestin,OCT4,CD117,KDR,AVP,CRHBP,ALDH1A1,STMN1,CD38,PTPRC,CD135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PCs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Myeloid Dendritic cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITGAX,CD83,CD1C,NRP1,CLEC4C,CD86,IL3RA,CD80,CD1A,ITGAX,CD40,HLA-DQA1,CD11c,HLA-DR,HLA-DPB1,HLA-DPA1,CLEC10A,CST3,GPR31,ODF3L1,PRB2,CD207,ARSE,CLEC141,MRC,EBLN1,CRIP3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mDCs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plasmacytoid Dendritic cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITGAX,CD83,CD1C,NRP1,CLEC4C,CD86,IL3RA,CD80,CD1A,ITGAX,CD40,HLA-DQA1,CD11c,HLA-DR,HLA-DPB1,HLA-DPA1,CLEC10A,CST3,TPM2,LRRC26,ASIP,GPM6B,KRT5,NTM,SCT,SHD,KCNA5,SCARA5,EPHA2,MYMX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pDCs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Granulocytes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CD203c,CD15,CD11b,CD63,CD66b,CD123,CD16,CD33,CD117,CD45,Fc-epsilon RI-alpha,CD125,CD13,CD14,CD25,CD44,CD69,CD9,HLA-DR,CCR3,CD116,CD11c,CD193,CD24,CD32,CD43,CXCL8,FCGR3B,MNDA,SIGLEC8,AZU1,MPO,CTSG,LYZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISG expressing immune cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IFIT1,IFIT2,IFIT3,IFIT5,ISG15,CCL3,CCL4,CCL3L3,RSAD2,OASL,CXCL10,IFI15,ISG20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISG+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSCs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CXCL12,LEPR,KITL,NT5E,THY1,ENG,EBF3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pericytes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDGFRB,RGS5,ACTA2,TAGLN,MYH11,CRIP1,NESTIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fibroblasts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DCN,COL1A1,COL3A1,LUM,PDGFRA,PRRX1,LGALS1,IGFBP6,GSN,FAP,THY1,TNXB,FBLN1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fibro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OLCs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COL1A1,COL5A2,IBSP,BGLAP,SP7,RUNX2,ALPL,LOX,IFITM5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chondrocytes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COL2A1,COL9A1,COL11A1,COL11A2,ACAN,COMP,HAPLN1,SOX9,MIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chondro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schwann</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S100B,SOX10,MPZ,MBP,PLP1,NGFR,GFRA3,ERBB3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pancreas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acinar cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CTRB1,KLK1,RBPJL,PTF1A,CELA3A,PRSS1,SPINK1,ZG16,CEL,CELA2A,CPB1,CELA1,RNASE1,AMY2B,CPA2,CPA1,CELA3B,PNLIP,CTRB2,PLA2G1B,PRSS2,CLPS,REG1A,SYCN,PNLIPRP1,CTRC,REG3A,PRSS3,REG1B,CFB,GDF15,MUC1,C15orf48,AKR1C3,OLFM4,GSTA1,LGALS2,PDZK1IP1,RARRES2,CXCL17,GSTA2,ANPEP,LYZ,ANGPTL4,ALDOB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acinar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alpha cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCG,TTR,ARX,POU3F4,NKX2-2,RESP18,PYY,PCSK2,SLC38A5,TM4SF4,CRYBA2,NKX6-1,KCNK16,PCSK1,PRRG2,IRX2,ALDH1A1,PEMT,CHGA,SMIM24,F10,SCGN,SLC30A8,SH3GL2,SCGB2A1,FAP,DPP4,MAFB,PAX6,NEUROD1,PLCE1,GC,KLHL41,FEV,PTGER3,RFX6,SMARCA1,PGR,LDB2,IRX1,UCP2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alpha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beta cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FXYD2,PDX1,INS,GCGR,JPH3,CD40,HAMP,EZH1,NTRK1,SLC2A2,NKX6-2,NPY,RIMS1,MAFA,EFNA5,LMX1A,NKX2-2,NKX6-1,PAX4,IAPP,PCSK2,G6PC2,SLC30A8,PCSK1,GJD2,SCGN,IGF2,SYT13,FFAR2,NPTX2,PFKFB2,EDARADD,HOPX,SH3GL2,ADCYAP1,SCGB2A1,CASR,MAFB,PAX6,NEUROD1,ISL1,TGFBR3,SMAD9,SIX3,SIX2,BMP5,PIR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delta cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SST,PDX1,FFAR4,PCSK9,RBP4,PAX4,RESP18,HHEX,ISL1,SCGN,KCNK16,IAPP,FXYD2,NPTX2,GPC5-AS1,UCP2,LEPR,BAIAP3,MS4A8,CASR,BCHE,GABRB3,UNC5B,EDN3,PRG4,FRZB,PCSK1,GABRG2,POU3F1,BHLHE41,EHF,LCORL,ETV1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ductal cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CFTR,HNF1B,KRT20,MUC1,ONECUT1,AMBP,HHEX,ANXA4,SPP1,PDX1,CFB,GDF15,AKR1C3,MMP7,DEFB1,SERPING1,TSPAN8,CLDN10,SLPI,SERPINA5,PIGR,CLDN1,LGALS4,PERP,PDLIM3,WFDC2,AQP1,ALDH1A3,KRT19,TFF1,TFF2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ductal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Endothelial cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PECAM1,CD34,MCAM,CDH5,VWF,ENG,KDR,PDPN,SELE,A2M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Epsilon cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GHRL,ANXA13,PHGR1,BMP4,HMGCS2,TM4SF5,OLFML3,ASGR1,COX6A2,NPY1R,SLC7A9,BHMT,OPRK1,PTGER4,ITGA4,EYA4,XYLB,ELOVL2,AFF3,CORIN,MYO1A,HRH2,SLC6A16,PCSK6,ADAMTS6,COL22A1,FAM124A,COL12A1,CD109,THSD4,ARX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Epsilon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gamma (PP) cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPY,SCGN,FXYD2,SCGB2A1,GPC5-AS1,CMTM8,ARX,ETV1,PXK,SERTM1,SLITRK6,SEMA3E,APOBEC2,ABCC9,NEUROD1,PAX6,ISL1,CARTPT,THSD7A,AQP3,ENTPD2,PTGFR,CHN2,EGR3,LMO3,MEIS1,ZNF503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gamma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Immune system cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS4A1,CD19,CD4,CD8A,CD7,CTLA4,CD27,CCR7,CYTIP,IGHD,CD38,IL2RA,ISG20,SELL,IL7R,FOXP3,IGKC,IGLC3,IGLC2,CD79A,CD68,CD163,CD14,ITGAM,MRC1,MS4A7,CD3D,CD3E,CD3G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Immune</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT,ENPP3,IL2RA,ISG20,SLC18A2,CD9,FCER1A,TPSB2,FCER2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mesenchymal cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITGB1,NT5E,THY1,ENG,KIT,ALCAM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MCs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pancreatic progenitor cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ONECUT1,PDX1,PTF1A,CXCR4,ISL1,NKX2-2,EPAS1,ARX,NEUROG3,SOX9,RPL23A,CTNNB1,YAP1,RGS16,MFNG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPCs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pancreatic stellate cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TIMP1,RGS5,SPON2,GEM,DYNLT1,PDGFRB,KRT10,CYGB,CCN2,MMP14,NDUFA4L2,PDGFRA,INHBA,TGFB1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSCs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peri-islet Schwann cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MPZ,EGFL8,GFRA1,OLFML2A,GULP1,SLITRK6,VGLL3,GFRA3,INSC,SLITRK2,FIGN,LRRTM1,SEMA3B,NGFR,PNLIPRP1,GFRA2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Islet Schwann</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cholangiocytes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSTR2,SLC4A2,KRT7,KCNN2,ITGB4,GGT6,CFTR,AQP4,AQP1,PIGR,GGT1,JAG1,GPBAR1,GGT7,KRT19,ONECUT2,ALPL,HNF1B,ALB,AGR2,TFF3,TFF1,SOX9,EPCAM,CLDN4,MMP7,TFF2,SCGB3A1,FXYD2,DEFB1,CD24,LCN2,CXCL1,CXCL6,LGALS2,TACSTD2,ELF3,SPP1,MUC5B,LGALS4,KRT8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Endothelial cell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLT1,APPBP2,ARGLU1,ATP10D,BNIP1,BST2,BTNL9,C11orf96,CCDC85B,CCL14,CD4,CDC73,CDKL1,CHD4,CLEC1B,CLEC2B,CLEC4G,CLEC4M,CRBN,CRHBP,CTSL,DCLRE1C,DIPK2A,DLC1,DLG1,DLK1,DNASE1L3,DOCK1,DUSP5,EFNB2,ENG,F8,FCN2,FCN3,FILIP1,FOSB,FXYD6,GBP4,GGA2,GNG11,HES1,HYI,IL1R1,IL33,KDR,KIF1B,KLHL28,LDB2,MCAM,MCM3AP,MEF2C,MFN1,MGAT5,MPZL3,MRC1,OIT3,PIK3C2A,PPWD1,PTPRC,RASGEF1B,RASGRP3,RELN,RIN2,SECISBP2L,STAB1,STRN3,TCF12,TEX264,TFRC,TRAPPC11,TSPAN7,USP48,VWF,ZNF286B,STAB2,CD34,PECAM1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hematopoietic cell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CD34,PTPRC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HCs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hepatic stellate cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CYGB,PPARG,PDGFRA,RGS5,PPARA,FOXF1,ALB,NR1H4,CCN2,SEMA7A,WT1,FGF10,GFAP,NGFR,VEGFA,ACTA2,MYB,DES,FAP,SLC8A1,RELN,SYP,VCL,TIMP1,COL1A1,TAGLN,COL1A2,COL3A1,SPARC,RBP1,DCN,MYL9,TPM2,MEG3,BGN,IGFBP7,IGFBP3,CCN1,OLFML3,IGFBP6,CCL2,COLEC11,HGF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSCs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hepatoblasts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AFP,ALB,CEBPA,KRT14,DLK1,CDH1,FOXM1,GGT1,HNF4A,PROX1,MAP2K4,SMAD5,KRT18,KRT8,HNF1B,HHEX,MET</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hepatocytes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AFP,HNF4A,KRT8,ALB,KRT18,FOSL1,EPPK1,UCP2,GCK,LRP5,SLC10A1,NOS2,ATP7B,GJB2,FGFR4,PROX1,CRP,SLC2A2,TFR2,KIF13B,LIPC,VDR,ASGR1,ARG1,G6PC,OTC,SERPINA1,ZHX2,HHEX,FOXA3,FOXA2,FOXA1,CYP2E1,CYP1A2,CEBPA,CDH1,GPC3,AHR,CPS1,GLS2,PCK1,TAT,WT1,PRRG4,SULT1A1,APOH,CTNNB1,ABCC3,FGB,AQP3,PLSCR1,FGA,APOB,ANG,ANXA13,SAT2,SFRP5,A1CF,APOA1,BNIP3,FGL1,PAH,SERPINA6,APOA2,AZGP1,FGG,APOC3,DEFB1,TM4SF4,GC,AMBP,ORM1,TTR,HAL,ASS1,SCD,HMGCS1,ACSS2,TM7SF2,SEC16B,SLBP,RND3,BCHE,GHR,ALDH6A1,MASP2,AKR1C1,HAMP,GLUL,ACLY,ASL,TMEM97,CP,SLPI,ACAT2,TM4SF5,MSMO1,LEPR,RCAN1,AR,RPP25L,HSD11B1,APOM,TKFC,G0S2,PON3,C1orf53,TTC36,FST,MCC,AQP9,GSTA2,NNT,SAA4,MRPS18C,OCIAD1,APOA5,ENTPD5,C4B,EID2,TP53INP2,ATIC,SERPINH1,SAMD5,GRB14,CD3G,RHOB,EPB41L4B,GPAT4,SPTBN1,SDC2,PHLDA1,WTAP,ACADM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CD19,MS4A1,IL2RA,PTPRC,CD4,CD8A,CD3D,CD3E,CD3G,CD11c,CD14,CD16,CD56,CD16,CD42b,CD7,CD8,IgD,CD38,CD24,CD20,CD14,CD16,HLA-DR,CD11b,CD11c,CD123,CD15,CD33,CD66b,CD38,CD27,CD94,CD45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kupffer cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CD14,CD68,TNF,LYZ,MPO,VSIG4,PROK2,STARD5,MSR1,PPARA,TREM1,SLC11A1,MMP13,VDR,CHIT1,OSM,PPARD,CLEC4F,ADGRE1,IL1B,SLC40A1,G6PD,TIMD4,MNDA,SLC15A3,DNASE1L3,MARCO,HFE,CD38,CD163,CCR5,CLEC1B,CLEC4G,GPIHBP1,FOLR2,PLTP,FTL,IRF7,SPIC,CSF1R,C1QC,C1QA,C1QB,CLEC4E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kupffer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liver progenitor cell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KRT7,KRT19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Progenitor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mesenchymal stem cell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CD44,ENG,NT5E,ITGB1,THY1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monocytes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FCGR3A,FCGR3B,CD14,Elane1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Muller cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apoe,Glul,Rlbp1,Abca8a,Vim,Aldh1a1,RLBP1,GLUL,PAX6,CA8,EDN2,KCNJ2,PRSS56,RGR,ApoE,Aqp4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Muller</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Astrocytes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRDX6,SLC1a3,PAX2,Rlbp1,GFAP,S100B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retinal ganglion cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BMP4,GRIA4,GRM3,KCNJ2,MED1,NMT,POU6F2,ZIC2,SLC17a6,Pax6,THY1,Nefl,Pou4f2,SNCG,NRN1,Cerkl </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RGCs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retinal progenitor cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAX6,CALB2,SIX6,RHO,SIX3,NEFH,LGR5,SAG,RAX,NOTCH1,HES1,MSI1,SOX9,KIT,PDGFRA,Og9x,Sfrp2,Fgf15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPCs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rod bipolar cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRKCA,PCP4,RCVRN,SLC1A2,Car8,Sebox,Vsx2,Otx2,GRM3,KCNA4,KCNMA1,RORB,Cabp5,Og9x,Vstm2b, Casp7, Rpa1,GABRA1,LHX4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RBCs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cone bipolar cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PCP4,RCVRN,SLC1A2,Car8,Scgn,Vsx2,Otx2,MIP,GNAS,ISL1,SLC1A7,GJD2,GNB3,GRIA4,TJP2,LRIT2,Cabp5,Scgn,Vsx1,GABRA1,LHX4,LHX3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CBCs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GABAergic amacrine cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pax6,Tfap2a,Gad2,Fut4,Calb2,Pvalb,Pcp4,Vip,Thy1,STX1A,MIP, GNAS, ISL1,Gad1,ZEB2,TJP2,SEMA3D,POU6F2,KCNMA1,KCNA4,GRM3,GJD2,FRMPD2,Prox1,Nr4a2,Ngn2,C1ql2,Reln</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GABAergic ACs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rod photoreceptor cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rho,Pdc,NRL,ROM1,CRX,ARR3,CABP4,CACNA1D,DYNLRB2,EDN2,FRMPD2,GJD2,KCNQ5,KCNA4,LRIT1,LRIT2,MAF,MED1,RORB,RP1L1,TSPAN10,TTC8,Gcap2,Samd7 ,Cerkl ,SAMD11,SLC24A1,RP1,PDE6B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rod</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cone photoreceptor cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arr3,Opn1sw,NRL,ROM1,CRX,ARR3,OPN1LW,OPN1MW,CABP4,CACNA1D,EDN2,GJD2,GNB3,KCNQ5,LRIT1,MED1,RP1L1,THRB,TSPAN10,TTC8,Opmw,SLC24A1,RP1,PDE6B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microglial cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P2RY12,ITGAM,CD40,PTPRC,CD68,AIF1,CX3CR1,TMEM119,ADGRE1,C1QA,NOS2,TNF,ISYNA1,CCL4,ADORA3,ADRB2,BHLHE41,BIN1,KLF2,NAV3,RHOB,SALL1,SIGLEC8,SLC1A3,SPRY1,TAL1,CX3CR1,CX3CL1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microglial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Horizontal cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rcvrn,Prox1,Ntrk1,Lhx1,Lim2,Calb2,CALB1,LIM1,DLG2,TFAP2B,ZEB2,Lim1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Horizontal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Synapses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SYP,DLG4,HOMER1,SLC32A1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retinal pigment epithelial cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EZR,RPE65,BEST1,ANO2,BMP2,BMP4,CLU,EFEMP1,IL4,KCNJ5,MED1,RDH5,RGR,SBSPON,TGFBR1,TMEM98,TTC8,TRAF1,Cerkl </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cornea epithelial cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KRT3,KLF6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CEP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Immune cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CD25,CD69,CD4,CD3,ITGAM,C1qa,Fcer1g,CD19,CD20,Trac,Ltb,Cd52,Trbc2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAX6,COL1A1,TGFB1,ACTA2,ICAM1,FBLN1,CRHBP,FN1,PDGFRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PECAM1,VWF,CDH5,BMP2,BMP4,CD34,CD55,FLT1,MED1,TGFBR1,TMEM98,TNFSF12,CD93,SLCO1A4,CLDN5,ICAM1,GNG11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kcnj8, Rgs5, Dlk1,  Abcc9,SUR2B,DLK1,VCAM1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extracellular matrix cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANTXR2,COL10A1,EFEMP1,LAMA2,SNTB1,TCF7L2,TGFBR1,TMEM98,VIPR2,ZIC2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECMs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glycinergic amacrine cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pax6,Tfap2a,Fut4,Calb2,Pvalb,Slc6a9,Pcp4,Vip,Thy1,STX1A,MIP, GNAS,ZEB2,TJP2,SEMA3D,POU6F2,KCNMA1,KCNA4,GRM3,GJD2,FRMPD2,Prox1,GlyT1,TgfB2,BE996002,Camkv,TCF4,Efna5,Dab1,Slc6a9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glycinergic ACs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cholinergic GABAergic amacrine cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pax6,Tfap2a,Gad2,Fut4,Calb2,Pvalb,Pcp4,Vip,Thy1,STX1A,MIP, GNAS, ISL1,Gad1,ZEB2,TJP2,SEMA3D,POU6F2,KCNMA1,KCNA4,GRM3,GJD2,FRMPD2,Prox1,Nr4a2,Ngn2,C1ql2,Reln,VAChT,Tac1,Scube2,Cpne4,Sox2,Slit,SCGN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cholinergic GABAergic ACs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tachykinin GABAergic amacrine cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pax6,Tfap2a,Gad2,Fut4,Calb2,Pvalb,Pcp4,Vip,Thy1,STX1A,MIP, GNAS, ISL1,Gad1,ZEB2,TJP2,SEMA3D,POU6F2,KCNMA1,KCNA4,GRM3,GJD2,FRMPD2,Prox1,Nr4a2,Ngn2,C1ql2,Reln,ZPF58,Cdh4,Grik4,Grm8,Slit2,SCGN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tachykinin GABAergic ACs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Starburst amacrine cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pax6,Tfap2a,Fut4,Calb2,Pvalb,Pcp4,Vip,Thy1,STX1A,MIP, GNAS,ZEB2,TJP2,SEMA3D,POU6F2,KCNMA1,KCNA4,GRM3,GJD2,FRMPD2,Prox1,GAD1,CHAT,SLC5A7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Starburst ACs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kidney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cancer stem cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EPCAM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSCs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CD19,IGHA2,IGHG3,IGHM,IGKC,JCHAIN,CD40,CD79A,CPNE5,FCRL5,HLA-DRA,IGHA1,IGHG1,IGHG2,IGKV1-12,IGLC2,IGLC3,IGLC7,IGLL5,MS4A1,MZB1,PKHD1L1,PNOC,POU2AF1,TNFRSF13C,CD3D,TRAC,IL7R,CD3E,CD8A,TRBC2,CD52,FCGR3A,IL32,KLRD1,CD68,CXCL8,FCGR3B,MNDA,KIT,PTGS2,SLC18A2,Trac,Ltb,Cd52,Trbc2,Shisa5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">α-intercalated cells (Collecting duct system)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FOXI1,OXGR1,ATP6V1G3,AQP6,CA2,NR1I4,SLC4A1,RHCG,ATP6V1B1,AVPR1A,P2RY14,FXYD2,TMEM213,CA2,DMRT2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">α-intercalated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">β-intercalated cells (Collecting duct system)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FOXI1,OXGR1,ATP6V1G3,SLC26A4,CA2,NR1I4,RHCG,ATP6V1B1,AVPR1A,INSRR,FXYD2,TMEM213,CA2,AP1S3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">β-intercalated cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loop of Henle cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UMOD,AQP1,IRX1,IRX2,IRX3,MECOM,POU3F3,TBC1D4,SLC12A1,DEFB1,GEM,RGS5,CYP4B1,DRAM1,NEK6,CDKN1C,CALCRL,CLCNKA,CRYAB,SPP1,PPP1R1B,LRRC66,IGF1,CLDN1,CLDN10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Henle loop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mesangial cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDGFRB,PDGFB,LAMA4,ITGA8,LGALS1,ARID5B,CCR7,FN1,GATA3,PAWR,SERPINE2,TBX18,TEK,THY1,REN,ZEB2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Podocytes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NPHS1,NPHS2,EZR,TDRD5,SEMA3G,SEMA5A,SEMA3E,PLA2R1,COL4A4,ARHGAP24,WT1,COL4A3,RHPN1,MAFB,PODXL,CLIC5,CD2AP,NOTCH2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal cells (Collecting duct system)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KCNE1,APELA,AQP2,AQP3,GATA3,ELF5,STC1,TBX3,CLDN4,KCNJ1,AVPR2,FXYD4,HSD11B2,SCNN1G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inner Medullary cells (Collecting duct system)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S100A4,PLEKHB1,ALDH1A3,TM6SF1,SLC14A2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proximal tubule cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FXYD2,ATP1B1,SLC3A1,CUBN,PDZK1,LRP2,POU3F3,AGXT2,GSTA2,CYP2E1,CRYL1,GLYAT,SORD,UPB1,SOD3,HNF4A,CDKN3,NAPSA,SLC7A13,SLC17A3,HGD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cap mesenchyme cells (Mesenchymal cells)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SIX2,ITGA8,NR2F2,EYA1,MEIS2,CITED1,MUC1,NOTCH2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cap mesenchyme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TGFBR2,NOTCH4,ADGRL4,EMCN,ENG,PECAM1,PLAC8,PLVAP,TEK,KDR,VWF,MMRN1,CD93</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stromal cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEIS1,TCF21,COL1A2,COL3A1,TNC,COL6A3,LGALS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stromal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juxtaglomerular cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REN,CRIP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juxtaglomerular</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Renal interstitium (Mesenchymal cells)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SFRP1,MEIS1,PDGFRA,C7,MGP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Renal interstitium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connecting tubule cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CALB1,TRPV5,FXYD2,ATP6V1B1,SLC8A1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connecting tubule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distal tubule cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KLK1,KCNJ1,KL,EGF,TMEM213,TMEM52B,SOSTDC1,SLC12A3,EMX1,CLDN3,CLDN8,UMOD,PCOLCE,CDC42EP3,CLCNKB,FXYD2,POU3F3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distal tubule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hematopoietic cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CORO1A,MNDA,SRGN,HLA-DPA1,LST1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ureteric Bud cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GFRA1,RET,WNT9B,CLDN6,LAMA1,NMU,Wnt11 ,Etv4, WNT7B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Renal Vesicle cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NCAM1,EMX2,LHX1,BMP2,DKK1,DLL1,GREB1,PAPSS2,PCSK9,POU3F3,TMEM100,WT1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GFAP,SLC1A3,SLC1A2,GLUL,S100B,ALDH1L1,AQP4,IGFBP3,ATP13A4,CBS,SOX9,CD40,CD80,CD86,C5AR1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cholinergic neurons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHAT,SLC18A3,ACHE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dopaminergic neurons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TH,SLC6A3,FOXA2,KCNJ6,NR4A2,LMX1B,DBH,SLC6A2,PPP1R1B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PECAM1,VWF,A2M,APOLD1,FLT1,TM4SF1,CD34,MCAM,ENG,PTPRC,VCAM1,CDH5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GABAergic neurons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLC6A1,GABBR1,GABBR2,GAD2,GAD1,SLC32A1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glutamatergic neurons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLC17A7,SLC17A6,GRIN1,GRIN2B,GLS,GLUL,GRIN2A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Immature neurons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DCX,NEUROD1,TBR1,STMN1,NCAM1,TUBB3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS4A1,CCR6,CXCR3,CD4,IL2RA,ISG20,TNFRSF8,Trac,Ltb,Cd52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mature neurons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RBFOX3,MAP2,SYP,DLG4,TUBB3,MAPT,INA,GAP43,NRP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P2RY12,ITGAM,CD40,PTPRC,CD68,AIF1,CX3CR1,TMEM119,ADGRE1,C1QA,NOS2,TNF,ISYNA1,CCL4,ADORA3,ADRB2,BHLHE41,BIN1,KLF2,NAV3,RHOB,SALL1,SIGLEC8,SLC1A3,SPRY1,TAL1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Myelinating Schwann cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOX10,EGR2,MBP,MPZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Myelinating Schwann</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neural Progenitor cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSPG4,RNF5,EOMES,SOX2,SOX1,NES,PAX3,PAX6,OTX2,CNTNAP1,ASCL1,SMARCA4,MSI1,MSI2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neural Progenitor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neural stem cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOX2,PROM1,NES,SOX9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neural stem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neuroblasts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEUROD1,DCX,DLX2,PROX1,EOMES,TUBB3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neuroepithelial cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NES,SOX2,NOTCH1,HES1,HES3,CDH1,OCLN,SOX10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neuroepithelial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non myelinating Schwann cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOX10,GAP43,NCAM1,NGFR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non myelinating Schwann</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oligodendrocyte precursor cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LHFPL3,MEGF11,PCDH15,PDGFRA,CSPG4,RNF5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oligodendrocyte precursor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oligodendrocytes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OLIG1,OLIG2,OLIG3,CLDN11,MBP,MOG,MAG,GALC,CNP,SOX10,FA2H,UGT8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radial glial cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VIM,NES,PAX6,HES1,HES5,GFAP,SLC1A3,FABP7,TNC,CDH2,SOX2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radial glial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schwann precursor cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOX10,GAP43,FABP7,MPZ,DHH,NGFR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schwann precursor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Serotonergic neurons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TPH1,SLC6A4,FEV,HTR1A,HTR1B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tanycytes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GPR50,COL23A1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airway epithelial cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADH7,AQP1,CDH1,SEC14L3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airway epithelial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airway goblet cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGR2,AQP5,CEACAM1,DMBT1,DUSP4,FXYD3,GALNT5,GALNT6,GGH,GOLPH3,GP2,IL19,LIPF,LTF,LYNX1,MSLN,MUC16,MUC4,MUC5B,NOS2,PIGR,QSOX1,SCGB3A1,SEC23B,SPDEF,TFF2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airway goblet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mesothelial cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C2,CALB2,CD44,CDH1,DES,EFEMP1,EPCAM,GSTA3,KRT5,KRT7,KRT72,LGALS7,LRRN4,ME1,ME2,MSLN,MUC16,OSR1,RSPO1,THBD,UPK3B,WT1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mesothelial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COL3A1,COL5A2,DPT,FN1,GSN,LRP1,PDGFRA,TCF21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Basal cells (Airway progenitor cells)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABI3BP,AQP3,DAPL1,GSTM2,HPGD,ICAM1,KRT14,KRT15,KRT5,PHLDA3,RPS18,SDC1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Basal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alveolar macrophages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABCG1,CCL3,CD36,CLEC7A,CSF2RB,CXCL2,G0S2,GAL,GDA,GNGT2,GPNMB,IL18,IL1B,ITGAX,KLHDC4,MARCO,MCEMP1,MPP1,MRC1,OLR1,PLET1,S100A4,TLR2,TNFAIP2,TRIM25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ciliated cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APPL2,ATP5MD,CCDC153,CCDC17,CCDC181,CCDC39,CYP2S1,FAM161A,FOXJ1,LRRC23,ODF3B,SCGB1A1,SEC14L3,SNTN,STK11,TMEM212,TSPAN19,TUBB4B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ciliated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clara cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AHR,ALDH1A1,BPIFA1,CTSE,CYP2E1,CYP4B1,ERN1,FOXM1,LEPR,MUC1,MUC4,MUC5B,RAB3D,SCGB1A1,SCGB3A1,SCGB3A2,SFTPA1,SFTPC,SFTPD,SYT2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADGRE1,ARG1,BIRC5,CCL17,CCL18,CD14,CD163,CD19,CD22,CD3D,CD3E,CD3G,CD4,CD44,CD5,CD68,CD74,CD80,CD83,CD86,CD8A,CD8B,CDCA3,CDK1,CEBPE,CR2,CSF1R,EAF2,FCER2,FCGR3A,FLT3,GIMAP3P,HLA-DRA,HMMR,IGHM,IL2RA,ITGAE,ITGAM,ITGAX,LAX1,MS4A14,MZB1,NRP1,NUSAP1,PAX5,PRG2,PTPRC,SLPI,THBD,TNFRSF17,TRBC1,XCR1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CD34,EGFL7,EMCN,ESAM,FLT1,KDR,MCAM,PECAM1,RAMP2,TEK,VWF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Epithelial cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANPEP,EPCAM,IL10,IL6R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Epithelial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ionocytes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CFTR,CLCNKB,FOXI1,KCNMA1,SCGB1A1,SLC12A2,TFCP2L1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pulmonary alveolar type I cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGER,AKAP5,AQP3,AQP5,CCN2,CLDN18,CLIC5,COL4A3,COL4A4,CRLF1,CYP4B1,EGFL6,EMP2,FSTL3,GPRC5A,HOPX,ICAM1,IGFBP6,KRT7,MEX3B,MMP11,P2RX7,PDPN,PXDC1,RTKN2,SCNN1A,SCNN1B,SCNN1G,SEC14L3,SEMA3B,SEMA3E,SMARCA1,VEGFA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AT1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pulmonary alveolar type II cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABCA3,ADGRF5,AGER,CD36,CD3G,CEBPA,CLDN18,CRLF1,CTNND1,CXCL2,CXCR2,DDX3Y,EGFL6,ETV5,GRK2,IL1B,INMT,IRX1,LAMP3,LPCAT1,LRG1,MUC1,NAPSA,NKX2-1,NRN1,PGC,PIGR,PPBP,PPP1R14C,RUNX3,S100G,SDC1,SFTA2,SFTPA1,SFTPB,SFTPC,SFTPD,SLC34A2,SOAT1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AT2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Secretory cell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MUC5B,PIGR,SCGB1A1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Secretory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adrenal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSH1_CSH2 positive cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CGB,GH2,PSG5,CGA,CSH1,ERVW-1,CSH2,PSG7,PSG11,HSD3B1,PSG9,PSG1,PSG6,PLAC4,PSG4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Megakaryocytes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C15orf54,GP9,PF4,PPBP,GP1BA,MEGT1,LY6G6F,GP6,ITGA2B,C6orf25,ALOX12,FCER1A,ELOVL7,NRGN,RP11-930O11.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schwann cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WNT16,MPZ,FOXD3,SOX10,CDH19,GPR17,PMP2,COL20A1,INSC,RP4-792G4.2,TTYH1,SOX2,LAMP5,OLFML2A,ATP1A2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Myeloid cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS4A14,LILRA1,RP11-554D14.6,AC007040.8,MS4A7,RP11-489O18.1,CLEC10A,MS4A4A,RN7SL138P,CD163,CD14,SIGLEC1,VSIG4,CLEC7A,LILRA2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sympathoblasts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NPAS4,SLC24A2,RP11-542G1.2,PENK,LINC00890,KLK4,RP11-17A4.2,RP5-1096J16.1,C18orf42,TTC40,ARC,FAM19A3,VWA5B1,PPP1R17,RP4-718N17.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erythroblasts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TPSAB1,CTD-2008P7.9,RP11-85G21.3,CTSE,CTA-392E5.1,EIF5AP2,CTA-363E6.6,C17orf99,SLC4A1,TRIM10,MIR144,ART4,AHSP,GYPA,HBM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stromal cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIR1245A,NPY5R,RP11-60A8.1,RP11-254F19.2,RP11-494K3.2,RP11-758M4.4,RP11-142A23.1,RP11-752L20.5,OSR1,RP11-867G23.13,SULT1E1,HHIP,MGP,PRELP,TWIST2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vascular endothelial cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCL23,FGF23,SMIM9,RP13-1016M1.2,RP11-100L22.1,RP11-327L3.3,RP1-149A16.12,GPR182,DLL4,GALNT15,CALCRL,CD300LG,FLT4,FCN3,GPIHBP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chromaffin cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NRG1-IT3,RNU6-457P,LINC00594,AC018643.4,RP11-159N11.3,CTC-537E7.1,Y_RNA,snoU13,CTD-2006K23.2,RP5-955M13.4,INSRR,KCNK10,PHEX-AS1,RP11-958J22.1,FLJ30594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lymphoid cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GZMH,XCL1,KLRC3,RP11-94L15.2,GZMA,IL2RB,TRAT1,SH2D1A,DTHD1,CD3E,ZNF831,GNLY,PRF1,IGHD,THEMIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adrenocortical cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RP1-145M24.1,RP11-238I10.1,AC005392.13,RP11-316I3.2,RP11-501O2.4,SDIM1,RP11-258O13.1,AJ006998.2,CTD-2517O10.5,RNU6-944P,CTB-43E15.4,RP11-34F13.3,RP11-536K7.5,RP11-183M13.1,RNU6-56P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLC26A4_PAEP positive cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IL1A,SLC26A4,SNX25P1,VMO1,CTD-2210P15.2,CTC-360P9.4,ULK4P1,SNORA14A,RNU6-518P,RP11-431N15.2,RP11-26J3.3,RP11-378A12.1,SPINK8,HSD3B2,KIRREL-IT1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEGT1,LY6G6F,TUBB1,PPBP,PF4,GP9,TPSB2,HBD,AC137932.6,ITGA2B,GP1BA,CLEC1B,PTCRA,BEND2,RP11-179A10.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Epicardial fat cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RP11-89M22.3,CTD-3012A18.1,PRG4,KRT7,SPRR2F,KLK11,MKRN9P,UPK1B,EPGN,NPHS1,ITLN1,LRRN4,CST6,GSDMA,RAET1E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lymphatic endothelial cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GPR182,GPR97,STAB2,HOXD9,TBX1,CCL21,HOXD10,TSPEAR,ABCA4,PGM5-AS1,TFF3,LINC00636,RP11-341G23.4,HOXD4,RP11-451M19.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GFRA3,SOX10,MPZ,LINC00466,COL20A1,MIA,ASPA,ERBB3,TFAP2A,INSC,ARTN,PMP2,S100B,FOXD3,AP000797.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GZMB,FCRL2,KLRC2,XCL1,LINC00861,PRF1,CD3G,SH2D1B,ANTXRLP1,VPREB3,SH2D1A,CRTAM,CXCR6,RP11-94L15.2,GZMK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XCR1,TMPRSS4-AS1,TIMD4,PRTN3,MMP9,CD86,CLEC5A,SIGLEC1,CLEC7A,C1QC,P2RY13,FCN1,CSTA,CD300LF,MS4A6A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Endocardial cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANGPTL5,APCDD1L,NPPC,SLC6A4,SALL1,LEPR,C3orf36,AC004562.1,FAM3D,HAPLN1,APCDD1,LYPD2,FOXC1,MPZL2,RP11-849I19.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESM1,SLC9C1,OPN5,QRFPR,MIR4454,AC007743.1,PKD1L1,TM4SF18,APLNR,CLRN1-AS1,CD300LG,C1QTNF9,AC019100.3,MADCAM1,RP11-298O21.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RP11-60A8.1,SCARA5,DPT,CILP,ZCCHC5,AGTR2,MFAP5,RP11-71N10.1,LUM,ABCA10,RP11-31K23.2,CCL11,NRK,PDGFRA,LPAR4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Smooth muscle cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDE4C,RP11-112H10.4,RP11-598F7.5,RP11-626H12.1,HCG22,CTD-3064M3.3,RP11-231I13.2,GPR20,RP11-267N12.1,OR51E1,THBS4,MIR143HG,PDGFRB,AOC3,ENPEP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SATB2_LRRC7 positive cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEUROD2,FEZF2,NEUROD6,TBR1,MPPED1,SATB2,FOXG1,PCDH11Y,CAMKV,BHLHE22,SLIT1,C14orf23,RP11-562L8.1,LINC00966,DRAXIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RP5-857K21.7,CENPW,SLC46A1,GSPT2,RHCE,SLC7A11,P2RX6,SKA1,FARSA,ZNF90,TMCC2,RP11-225B17.2,TMEM161A,ZNF583,ENPP4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visceral neurons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GATA3-AS1,GAL,CHRNA3,PRPH,PHOX2A,GALR1,NXPH1,TMC3,DDC,SST,OPRM1,PIRT,NECAB2,ECEL1,SLC10A4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cardiomyocytes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RP11-439H8.4,RNA5SP327,CTD-2552K11.2,Y_RNA,AC018464.3,HHATL,BMP10,RP11-461A8.4,UGT2B4,PRSS42,WI2-1896O14.1,FABP2,EPN3,RP11-406O23.2,AC009878.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELF3_AGBL2 positive cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1orf194,ZMYND10,MS4A8,IL20RA,ELF3,SCGB3A2,EFCAB1,SFTPB,WDR65,CP,PIH1D2,AGBL2,SFTPC,DNAH9,MUC1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLC_IL5RA positive cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAM209A,CERKL,CLC,PRG2,MS4A3,IL5RA,ZC2HC1C,CTD-2620I22.1,CTD-3032H12.2,RP11-252E2.1,AC011524.1,S100A1,Y_RNA,LINC00407,RP11-516C1.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intestine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AHSP,SPTA1,HBG2,HBA2,HBM,HBG1,HBA1,SLC4A1,HBB,GYPA,HEMGN,HBZ,ALAS2,MIR144,MYL4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARX,NKX2-2,CCK,CRYBA2,NEUROD1,FEV,MLN,ASIC5,ONECUT3,SST,RP11-788H18.1,PAX4,KCNH6,SSTR5,PCSK1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACTG2,GREM2,CNN1,RP11-467I20.6,WIF1,TACR2,OVCH2,FRMD6-AS2,DES,MYH11,RP11-626H12.1,ANO1,CHRDL2,TAGLN,FBXL22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VSIG4,RPL32P1,CD207,AP000439.1,HCAR3,C5orf20,AC010492.4,P2RY13,LILRB2,LILRB5,IL1B,C1QB,CD163,C1QC,DNASE1L3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IL17A,ICOS,SH2D1A,GZMK,RP11-553L6.2,TRGC1,RP11-104L21.3,TRDC,GZMA,VPREB1,CCR4,LTA,NCR2,CD247,RP11-94L15.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intestinal epithelial cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNC5CL,C1orf177,TRIM31,LINC00955,RP3-417L20.4,HMGN1P20,ALPI,RP11-395B7.2,EGFR-AS1,RP11-462G2.1,DEFB1,CA7,RP11-468N14.13,ARL14,AC024592.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENS glia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SERPINA3,RLBP1,GPR12,RP4-792G4.2,CDH19,COL20A1,SOX10,PLP1,SOX2,FOXD3,MPZ,BCAN,TFAP2A,SOX2-OT,PTPRZ1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENS neurons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDIA2,RP11-672L10.2,GRP,DRGX,GCGR,SLC18A3,PHOX2A,HECW1-IT1,RP11-202H2.1,IQCJ,STMN4,TTC9B,GAL,CEND1,NEFL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOX17,GPIHBP1,PRND,CLEC3B,FLT1,MMRN2,BTNL9,APLNR,LHX6,NOTCH4,RP11-3K16.2,ESAM,RP11-328D5.1,ESM1,GJA5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RP11-13P5.2,MSC,RP1-283K11.3,RP5-1077H22.1,CTD-2541J13.1,AC002511.2,AC002511.3,MMP27,CTD-2334D19.1,CXCL14,FZD10,PDGFRA,AC003090.1,RP1-288H2.4,ITGA11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AP000705.7,HAS1,TNNT1,BNC1,DSC3,WT1,WNT10A,C21orf62,PTPRQ,CEMP1,C3,CRB2,KLK11,PHYHIP,TGM1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RP11-474N8.5,TBX1,STAB2,CCL21,LINC00636,TSPEAR,ART5,CTC-236F12.4,GPR1,RP11-322E11.5,MPP7,Y_RNA,ABCA4,PLIN5,TP63</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Muscle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PF4,ITGA2B,LIPH,ELOVL7,GP6,ITGB3,PTGS1,RP11-480G7.1,RP11-170N16.2,C3orf55,RP4-655J12.4,TUBB1,DCLRE1A,TMEM40,GNAZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UGT8,POU3F1,PMP2,GFRA3,KCNC2,MPZ,SOX10,PTPRZ1,COL20A1,LINC01037,BCAN,C2orf72,C10orf82,RP11-946L20.2,MAG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NTS,TFF3,CCL21,STAB2,PTX3,PCLO,IL7,P4HA3,C6orf141,PIK3C2G,ASGR2,ANKRD36BP2,NALCN,FAM26F,NHLRC1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RHAG,GYPA,AHSP,GYPB,HBZ,ALAS2,SLC4A1,SLC14A1,EIF5AP2,HBM,HBA1,EPB42,RP11-57H12.2,ALS2CR12,SLC25A37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skeletal muscle cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RP11-755O11.2,ASB15,RP11-456H18.2,RPL7P3,PVALB,RN7SL365P,RP11-432J24.5,C8orf22,ASB10,RP5-921G16.2,CLDN9,RP5-1039K5.13,AC137723.5,RP11-255G21.1,AC093063.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WSCD2,C13orf45,LINC00645,RP1-300G12.2,RP11-217C7.1,RP11-332E3.2,RP11-473E2.4,CTD-2555C10.3,RP11-342A23.1,WNT10B,ACKR4,DIO3,CCDC129,ZCCHC5,RP11-38H17.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Satellite cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AC004014.3,MYEOV,TACR3,GDPD4,USP44,RGR,RP11-320P7.2,FAM132B,GPR123,CTB-175P5.4,ENPP7P10,CHRDL2,PAX7,RP11-706J10.1,MAPK15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIR4454,SLC5A4,AL118508.1,CA4,RP11-206M11.7,PRSS51,NOS3,GRIN2A,GFRAL,CD300LG,MADCAM1,RP11-327L3.3,C1QTNF9,ANO2,AP001597.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OR51E2,AC131025.8,ADORA2B,MYH11,SLC38A11,MIR143HG,MIR145,RP11-1101K5.1,P2RX3,GPR176,ANO1,OR51E1,CORIN,CACNA1C-IT3,TMC4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FCN1,MS4A4E,TMPRSS4-AS1,CD86,FLT3,P2RY13,IL10RA,FOLR2,MNDA,HLA-DQB1,MS4A4A,AMICA1,CYTH4,MS4A6A,CFP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IL7R,CD8A,NKG7,CD247,NCR1,RP11-61O1.1,TRAC,CD3E,ITK,CD2,MATK,RP11-444A22.1,SYTL1,IL2RB,GZMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Placenta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAEP_MECOM positive cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RP11-98L5.2,AC104654.1,PAEP,RP11-274B18.4,PIGR,TSPAN1,AC012593.1,RP11-510D19.1,POU5F1,UGT2B7,DEFB1,RP11-697E22.2,SLC18A2,PAX8,SLPI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AFP_ALB positive cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLC2A2,ALB,APOB,AFP,ITIH2,F2,MAT1A,APOC3,SERPINC1,FABP1,APOA2,AHSG,SERPINA10,SLC38A3,SERPINA4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extravillous trophoblasts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AC022596.6,GKN1,CILP2,LINC00330,PDE6H,PRG2,RP11-872D17.8,HLA-G,ASCL2,NOTUM,AC006262.5,DAW1,NOG,TAC3,RP11-420L9.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IGJ,IGHM,KLRC3,GZMH,PTGDR,IGHGP,IKZF3,IFNG-AS1,TIGIT,KLRC2,LCK,ANKRD36BP2,TNFRSF18,IGHG3,LINC00861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trophoblast giant cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCK,CTA-833B7.2,PSG1,CGB,CSH2,PSG6,KISS1,INHBA,GH2,PSG9,CRH,PSG8,RP11-76E12.1,PSG4,TREML3P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RP11-162G9.1,FAM162B,WNT3A,AFF2,CDH19,SCN11A,GPR20,COX4I2,AGTR1,ADAMTS20,RP11-123O22.1,HIGD1B,AC020571.3,COLEC10,KCNK17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IGFBP1_DKK1 positive cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RP3-404K8.2,RP11-486P11.1,FOXL2,WT1,RP11-171A24.3,SCARA5,LRRN4CL,S100A3,WT1-AS,PRL,WNT4,AC012065.7,APOD,BRINP2,RORB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AP006285.6,AC002451.1,RP11-99L13.2,RP1-79C4.4,MMP23B,RP11-248N22.2,LA16c-380H5.4,MIR218-1,C8orf87,SNORD113,RP11-74M11.2,HSD3BP2,AP001605.4,LINC00314,AC007394.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RP11-1028N23.4,RP11-297H3.3,AC007743.1,RP11-327L3.3,CD34,ARHGEF15,CXorf36,LRRC36,SOX7,RP11-328D5.1,NTS,CDRT1,LINC01049,ROBO4,HS3ST3A1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Syncytiotrophoblasts and villous cytotrophoblasts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CTD-2050E21.1,POTEKP,RP11-344B2.3,RP11-366M4.3,RP11-2A4.4,RP11-483F11.7,FTLP14,RP11-718G2.5,RP11-18D7.3,CLCA2,KB-1440D3.13,CTBP2P8,RP11-359P18.1,HSPD1P6,AC124861.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SIGLEC10,RP11-1143G9.4,LYZ,ADAMDEC1,LILRB2,HLA-DRB5,SDS,HLA-DOA,SIGLEC1,MMP9,LILRB4,C1QB,TLR2,TLR7,S100A8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EGF,TUBB1,PPBP,ITGA2B,RP11-930O11.1,RP11-152K4.2,LINC00989,PF4,C6orf25,LINC00534,PKHD1L1,NRGN,DNM3,RP11-466L17.1,RP11-142C4.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spleen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SERPINA6,PLG,AMBP,SERPINC1,BHMT2,LBP,PRAP1,APOB,SERPINA1,FGB,VTN,SLC2A2,FGG,MT1G,ITIH1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RN7SL337P,KLRC4-KLRK1,RP11-553L6.2,RP11-861A13.4,RP11-38J22.6,ZNF860,RP11-693J15.5,RP11-61O1.1,FCRL3,CTD-2215E18.1,RP5-1028K7.2,IKZF3,LINC00861,IL9RP3,VAV3-AS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLEC9A,RP11-489O18.1,RP3-522P13.3,RP11-807H22.7,RP11-1080G15.1,FCN1,EMR4P,TMPRSS4-AS1,RP11-157G21.2,CSF2RA,OSCAR,RP3-522D1.1,CD163L1,RUFY4,DLEU7-AS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RP11-189E14.5,ODF3L2,RP4-765C7.2,AC019100.3,RP11-172F10.1,CTD-2207L17.2,RP1-154K9.2,AC010084.1,SLC5A4,OR5G5P,HOXD3,SNTG1,EEF1A1P31,ADAMTSL1,MYRIP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CTD-2270F17.1,ENPP7P4,AC105053.3,RP11-388K12.1,SCTR,KBTBD11-OT1,ADRA1B,NPM1P10,NPY5R,TPH2,CTC-535M15.2,MIR143HG,KLHL29,AC023481.1,CADPS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STC2_TLX1 positive cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAMK2N2,CLVS2,RP11-384O8.1,FBXL16,GABRG2,HRK,EBF3,TRH,AC018730.1,CTD-3193O13.9,CPLX2,ATP1A3,TMEM119,IFI27L2,PET117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAB27B,RP11-556I14.2,EGF,GP6,RP11-930O11.1,LINC00989,SELP,GP1BA,HPSE,RP11-152K4.2,LINC00504,MMRN1,ITGB3,ELOVL7,LY6G6F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QRFPR,SLPI,LHX9,PLA2G2A,CGN,NPHS1,KRT5,LRRN4,KLK11,OLR1,PTPRQ,COL8A1,PDZK1IP1,HAS1,SFRP2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HDC,PRSS57,EIF5AP2,PPAPDC1A,MTL5,CTA-392E5.1,ACSBG1,RP5-964N17.1,GYPA,SLC25A21,RP11-146I2.1,MIR144,SLC2A14,CTA-363E6.6,SLC4A1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stomach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neuroendocrine cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLC18A1,GHRL,GAST,FEV,NKX2-2,CRYBA2,MBOAT4,CDK5R2,RFX6,HAP1,RP11-82C23.2,RBPJL,PTF1A,PAX6,CACNA1A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KLF1,SLC4A1,HBM,NFE2,HBZ,GYPB,HBG2,HBB,ALAS2,SPTA1,HBA1,HEMGN,RNF224,HBG1,HBA2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ciliated epithelial cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCDC37,C11orf88,FAM216B,LDLRAD1,TUBA4B,KIF19,DYDC2,ANKRD66,C9orf117,C10orf67,AC013264.2,LRRC71,CAPSL,TSPAN19,STOML3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Squamous epithelial cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KRT6B,CAPNS2,KRT6C,FGFBP1,KRT6A,KRT17,ADH7,SERPINB10,KRT16,S100A3,CLCA2,LY6D,KRT4,AC019349.5,GPR87</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parietal and chief cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RP11-467I20.6,ETNPPL,ATP4B,FGB,FGA,SIGLEC11,FRMD1,TRIM50,ALB,ATP4A,ANGPTL3,MFSD4,APOBEC2,CKM,PAQR5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MUC13_DMBT1 positive cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISX,GUCA2B,ENPP7,MIR194-2,BTNL3,TM4SF20,SI,SLC17A4,ALDOB,CDX1,DMBT1,CHP2,KRT20,SLC5A12,ADRA2A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1QC,HLA-DQB1,MS4A6A,CD14,C1QB,CD163L1,IGSF6,CCDC26,C1QA,NCF2,HLA-DRB1,HLA-DRB5,CLEC7A,MS4A7,HLA-DPA1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Goblet cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UGT2B15,IL17C,GKN2,SLC22A8,CXCL5,CSF3,TFF2,A4GNT,FBP2,FGF20,MUC6,GKN1,CXCL1,MUC5AC,CA9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AC002511.2,PTGER1,OSR2,AC003090.1,ACTG2,INHBA,HSPB6,AC131025.8,SHISA3,DPT,TRPA1,ACTA2,TWIST2,CXCL14,GLIS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRPH,STMN2,ATP1A3,KCNIP4,NKAIN1,INA,GAP43,ATCAY,CNGB1,TCEAL5,STAC,DCX,RP11-457K10.1,FAM163A,CNTN5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOX10,MPZ,ATP1A2,BAI1,PLP1,CDH19,COL20A1,ELOVL2,NOV,PRIMA1,RP11-308N19.1,SLC35F1,LGI4,VGLL3,EGFLAM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SELE,PRND,APLNR,ARHGEF15,PLVAP,FLT1,PCDH12,MADCAM1,GPIHBP1,GALNT15,RP4-601K24.1,MEOX1,A2M,CCM2L,CLEC14A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NTS,STAB2,CCL21,RADIL,RP11-444A22.1,TFPI,RP11-142C4.6,TNFAIP8L3,LY86-AS1,PTGS2,RP11-554D15.1,EFCC1,MMRN1,Y_RNA,NFATC1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RP11-74M11.2,AP000705.7,BNC1,SPHKAP,PTPRQ,NPHS1,TNNT1,TFPI2,BDNF,PDZRN4,LRP2,GFPT2,HAS1,WT1,COL8A1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICOS,CD27,NKG7,CD28,CD3D,CHI3L2,TRAT1,THEMIS,CD52,KLRB1,CD79B,CCL5,TRBC2,SIRPG,CD3E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDE1C_ACSM3 positive cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RP11-690G19.4,ACSM3,C1orf95,KCNE4,PDE1C,PSEN2,ERBB4,ATP6V0A4,TFCP2L1,WNK3,GABRB2,ADARB2,AMACR,SHISA2,NOX4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thymus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thymic epithelial cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RP11-81F13.2,KCNJ5,RP11-153K16.1,RP11-81F13.1,LL22NC03-75H12.2,RP11-112J1.2,RP11-114G22.1,RP6-24A23.6,C11orf16,SLC46A2,CACNA1I,PTPRT,NPFFR2,RP1-223B1.1,C12orf56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLAC9,LOX,MGP,COL1A2,COL5A3,COL1A1,ASPN,FGF18,MMP2,ISLR,DCN,SFRP2,COL3A1,SCARA5,COL6A6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antigen presenting cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IL1RN,EBI3,FGD2,MCOLN2,MMP9,TLR10,LINC00996,CD80,CXCL10,SLAMF7,P2RY13,SLC24A4,HCK,C1QB,LYZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADAMTS9,PROX1,MET,AC011526.1,MEOX2,ANO2,CTD-3179P9.1,NOVA2,AOC3,CXorf36,GPR116,PODXL,NRN1,PTPRB,LINC00472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thymocytes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RP11-104L21.3,BEST3,HKDC1,KLRC4-KLRK1,RP11-305P22.9,LTA,TMSB15B,RP11-739G5.1,UBASH3A,PLK4,FBXO41,LIN28B,SKA3,CD40LG,AC002454.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cancer cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CD44,EPCAM,ERBB2,FOLH1,KRT18,PROM1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cancer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CD24,CD44,FLOT2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANPEP,CD44,EPCAM,POU5F1,PROM1,THY1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABCG2,ALCAM,ALDH1A1,BMI1,CD24,CD44,KIT,NANOG,NES,PDPN,POU5F1,PROM1,SOX2,THY1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CD44,MBTPS2,PARP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FUT4,MSI1,NES,PROM1,SOX2,THY1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IR-Immune system</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PTPRC,CD34,FLT3,RAG1,RAG2,VPREB1,IGLL1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CD27,CD20,MS4A1,TRAC,TRBC1,TRBC2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PTPRC,CD19,VPREB1,IGLL1,RAG1,RAG2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CD27,CD34,TRAC,TRBC1,TRBC2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PTPRC,IGHM,IGHD,CD22,CD19,CD38,CD24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CD27,CD138,SDC1,CD20,TRAC,TRBC1,TRBC2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PTPRC,IGHG1,IGHG2,CD27,CD20,MS4A1,TNFRSF13B,TACI,IGHG3,IGHG4,IGHA1,IGHA2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CD34,CD138,PRDM1,TRAC,TRBC1,TRBC2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PTPRC,PRDM1,XBP1,BLIMP1,MZB1,SDC1,CD138,JCHAIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CD20,MS4A1,TRAC,TRBC1,TRBC2,CD19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCR6, CCR7, CD11B, CD127, CD2, CD27, CD30, CD3D, CD3E, CD3G, CD3Z, CD45, CD45RA, CD52, CD6, CD62L, CD8, CD8A, CD8B, CTLA4, DAPL1, FOXO1, FOXP1, FOXP3, GNLY, IL2RA, IL7R, KLF2, LCK, LEF1, LTB, PTPRC, SELL, SHISA5, TCF7, THY1, TRAC, TRBC1, TRBC2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GZMB,CD56,NCAM1,CD4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACTN1, CCR6, CCR7, CD11B, CD127, CD2, CD27, CD30, CD3D, CD3E, CD3G, CD3Z, CD4, CD45, CD45RA, CD52, CD6, CD62L, CTLA4, DAPL1, FOXP3, IL2RA, IL7R, KLF2, LCK, LEF1, LTB, PTPRC, SELL, SHISA5, TCF7, THY1, TRAC, TRBC1, TRBC2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GZMB,CD56,NCAM1,CD8A,CD8B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCR6, CCR7, CD11B, CD127, CD2, CD25, CD27, CD28, CD30, CD3D, CD3E, CD3G, CD3Z, CD45, CD45RA, CD45RO, CD52, CD6, CD62L, CD8, CD8A, CD8B, CTLA4, DAPL1, FOXP3, GNLY, GZMB, IL2RA, IL32, IL7R, LCK, LTB, S100A4, SELL, SHISA5, THY1, TRAC, TRBC1, TRBC2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCR7,SELL,CD4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCR6, CCR7, CD11B, CD127, CD2, CD25, CD27, CD28, CD30, CD3D, CD3E, CD3G, CD3Z, CD4, CD45, CD45RA, CD45RO, CD52, CD6, CD62L, CTLA4, DAPL1, FOXP3, GZMB, IL2RA, IL32, IL7R, LCK, LTB, S100A4, SELL, SHISA5, THY1, TRAC, TRBC1, TRBC2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCR7,SELL,CD8A,CD8B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCR6, CCR7, CD11B, CD127, CD2, CD25, CD27, CD30, CD3D, CD3E, CD3G, CD3Z, CD45, CD45RA, CD52, CD6, CD62L, CD8, CD8A, CD8B, CTLA4, DAPL1, FAS, FOXP3, GNLY, GZMB, GZMK, IFNG, IL2RA, JUN, JUNB, JUND, LCK, LTB, NKG7, PTPRC, SHISA5, THY1, TRAC, TRBC1, TRBC2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SELL,CCR7,CD27,CD4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCR6, CCR7, CD11B, CD127, CD2, CD25, CD27, CD30, CD3D, CD3E, CD3G, CD3Z, CD4, CD45, CD45RA, CD52, CD6, CD62L, CTLA4, DAPL1, FAS, FOS, FOXP3, GNLY, GZMB, GZMK, IFNG, IL2RA, JUN, JUNB, JUND, LCK, LTB, NKG7, PTPRC, SHISA5, THY1, TRAC, TRBC1, TRBC2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SELL,CCR7,CD27,CD8A,CD8B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCR6, CCR7, CD11B, CD127, CD2, CD25, CD27, CD30, CD3D, CD3E, CD3G, CD3Z, CD45, CD45RA, CD52, CD6, CD62L, CTLA4, DAPL1, FOXP3, GZMB, IL2RA, LCK, LTB, PLZF, PTPRC, RORC, SHISA5, THY1, TRDC, TRDV1, TRDV2, TRGC1, TRGC2, TRGV9, ZBTB16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SELL,CCR7,CD4,CD8A,CD8B,TRAC,TRBC1,TRBC2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CD11B, CD122, CD16, CD161, CD2, CD314, CD3D, CD3E, CD3G, CD3Z, CD56, CD69, CD8, CD8A, CD94, COX6A2, GNLY, GZMA, GZMB, GZMM, KIR2DL4, NCAM1, NKG2D, NKG7, NKP46, PTPRC, ZMAT4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCR7,CD27,CD4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CD11B, CD122, CD16, CD161, CD2, CD314, CD3D, CD3E, CD3G, CD3Z, CD4, CD56, CD69, CD94, COX6A2, GNLY, GZMA, GZMB, GZMM, KIR2DL4, NCAM1, NKG2D, NKG7, NKP46, PTPRC, ZMAT4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCR7,CD27,CD8A,CD8B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Natural killer cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CD11B, CD122, CD16, CD161, CD2, CD314, CD56, CD69, CD94, COX6A2, FCGR3A, GNLY, GZMA, GZMB, GZMM, KIR2DL4, KLRD1, KLRF1, NKG2D, NKG7, NKP46, ZMAT4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CD3D,CD3E,CD3G,CD3Z,CD4,CD8,TRAC,TRBC1,TRBC2,TRBC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proliferating CD8+ T cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CD3D, CD3E, CD3G, CD8A, CD8B, MCM6, MKI67, PCNA, PTPRC, TOP2A, TRAC, TRBC1, TRBC2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CD4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prolif CD8+ T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proliferating CD4+ T cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CD3D, CD3E, CD3G, CD4, MCM6, MKI67, PCNA, PTPRC, TOP2A, TRAC, TRBC1, TRBC2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CD8A,CD8B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prolif CD4+ T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exhausted CD8+ T cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CD8A, CD8B, ENTPD1, HAVCR2, LAG3, LAYN, PDCD1, PTPRC, TIGIT, TOX, TRAC, TRBC1, TRBC2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exh CD8+ T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exhausted CD4+ T cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BTLA, CD4, CTLA4, HAVCR2, PDCD1, PTPRC, TIGIT, TOX, TRAC, TRBC1, TRBC2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exh CD4+ T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Th17-proInfl T cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCR6, CD3D, CD3E, CD3G, CD4, IL17A, PDCD1, PTPRC, RORC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCR7,CD8A,CD8B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Th17_proInfl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regulatory CD8+ T cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CD8A, CD8B, CTLA4, MAF, PDCD1, PRDM1, PTPRC, TIGIT, TRAC, TRBC1, TRBC2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CD4,GZMB,PRF1,GNLY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CD8+ Treg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regulatory CD4+ T cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCR4, CD4, CTLA4, ICOS, IL2RA, PDCD1, PTPRC, TIGIT, TRAC, TRBC1, TRBC2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CD8A,CD8B,GZMB,PRF1,GNLY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CD4+ Treg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITGAX,CD83,CD1C,NRP1,CD86,CD80,CD1A,CD40,HLA-DQA1,CD11c,HLA-DR,HLA-DPB1,HLA-DPA1,CLEC10A,CST3,GPR31,ODF3L1,PRB2,CD207,ARSE,CLEC141,MRC,EBLN1,CRIP3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CD66b,CD11b,CD15,CD16,CXCL8,FCGR3B,MNDA,CXCR2,ELANE,PRTN3,MPO,AZU1,LYZ,S100A8,S100A9,PI3,CHI3L1,ANXA3,CXCL1,TGM3,BTNL3,C4BPA,MMP9,CD24,BPI,LTF,GCA,CAMP,NGP,CHIL3,LTF</t>
+  </si>
+  <si>
     <t xml:space="preserve">CD105,CD34,CD44,CD73,CD45,CD29,STRO-1,NANOG,SOX2,CD133,CD166,CD146,CD31,Nestin,OCT4,CD117,KDR,CXCL8,AVP,CRHBP,ALDH1A1,CD49,CD90,CD69,CD24,CD38,CD45RA,Keratin-19,ASPM,CD10,CD123,ABCG2,CD135,CD49f,EpCAM,Keratin-7,SCA-1,CD14,CD150,CD271,HLA-DR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PTPRC,CD38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSC/MPP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Progenitor cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CD105,CD34,CD44,CD73,CD45,CD29,STRO-1,NANOG,SOX2,CD133,CD166,CD146,CD31,Nestin,OCT4,CD117,KDR,AVP,CRHBP,ALDH1A1,STMN1,CD38,PTPRC,CD135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PCs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Myeloid Dendritic cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ITGAX,CD83,CD1C,NRP1,CLEC4C,CD86,IL3RA,CD80,CD1A,ITGAX,CD40,HLA-DQA1,CD11c,HLA-DR,HLA-DPB1,HLA-DPA1,CLEC10A,CST3,GPR31,ODF3L1,PRB2,CD207,ARSE,CLEC141,MRC,EBLN1,CRIP3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mDCs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plasmacytoid Dendritic cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ITGAX,CD83,CD1C,NRP1,CLEC4C,CD86,IL3RA,CD80,CD1A,ITGAX,CD40,HLA-DQA1,CD11c,HLA-DR,HLA-DPB1,HLA-DPA1,CLEC10A,CST3,TPM2,LRRC26,ASIP,GPM6B,KRT5,NTM,SCT,SHD,KCNA5,SCARA5,EPHA2,MYMX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pDCs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Granulocytes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CD203c,CD15,CD11b,CD63,CD66b,CD123,CD16,CD33,CD117,CD45,Fc-epsilon RI-alpha,CD125,CD13,CD14,CD25,CD44,CD69,CD9,HLA-DR,CCR3,CD116,CD11c,CD193,CD24,CD32,CD43,CXCL8,FCGR3B,MNDA,SIGLEC8,AZU1,MPO,CTSG,LYZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ISG expressing immune cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFIT1,IFIT2,IFIT3,IFIT5,ISG15,CCL3,CCL4,CCL3L3,RSAD2,OASL,CXCL10,IFI15,ISG20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ISG+</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MSCs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CXCL12,LEPR,KITL,NT5E,THY1,ENG,EBF3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pericytes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PDGFRB,RGS5,ACTA2,TAGLN,MYH11,CRIP1,NESTIN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fibroblasts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DCN,COL1A1,COL3A1,LUM,PDGFRA,PRRX1,LGALS1,IGFBP6,GSN,FAP,THY1,TNXB,FBLN1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fibro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OLCs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COL1A1,COL5A2,IBSP,BGLAP,SP7,RUNX2,ALPL,LOX,IFITM5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chondrocytes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COL2A1,COL9A1,COL11A1,COL11A2,ACAN,COMP,HAPLN1,SOX9,MIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chondro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Schwann</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S100B,SOX10,MPZ,MBP,PLP1,NGFR,GFRA3,ERBB3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pancreas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Acinar cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CTRB1,KLK1,RBPJL,PTF1A,CELA3A,PRSS1,SPINK1,ZG16,CEL,CELA2A,CPB1,CELA1,RNASE1,AMY2B,CPA2,CPA1,CELA3B,PNLIP,CTRB2,PLA2G1B,PRSS2,CLPS,REG1A,SYCN,PNLIPRP1,CTRC,REG3A,PRSS3,REG1B,CFB,GDF15,MUC1,C15orf48,AKR1C3,OLFM4,GSTA1,LGALS2,PDZK1IP1,RARRES2,CXCL17,GSTA2,ANPEP,LYZ,ANGPTL4,ALDOB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Acinar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alpha cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCG,TTR,ARX,POU3F4,NKX2-2,RESP18,PYY,PCSK2,SLC38A5,TM4SF4,CRYBA2,NKX6-1,KCNK16,PCSK1,PRRG2,IRX2,ALDH1A1,PEMT,CHGA,SMIM24,F10,SCGN,SLC30A8,SH3GL2,SCGB2A1,FAP,DPP4,MAFB,PAX6,NEUROD1,PLCE1,GC,KLHL41,FEV,PTGER3,RFX6,SMARCA1,PGR,LDB2,IRX1,UCP2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alpha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beta cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FXYD2,PDX1,INS,GCGR,JPH3,CD40,HAMP,EZH1,NTRK1,SLC2A2,NKX6-2,NPY,RIMS1,MAFA,EFNA5,LMX1A,NKX2-2,NKX6-1,PAX4,IAPP,PCSK2,G6PC2,SLC30A8,PCSK1,GJD2,SCGN,IGF2,SYT13,FFAR2,NPTX2,PFKFB2,EDARADD,HOPX,SH3GL2,ADCYAP1,SCGB2A1,CASR,MAFB,PAX6,NEUROD1,ISL1,TGFBR3,SMAD9,SIX3,SIX2,BMP5,PIR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Delta cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SST,PDX1,FFAR4,PCSK9,RBP4,PAX4,RESP18,HHEX,ISL1,SCGN,KCNK16,IAPP,FXYD2,NPTX2,GPC5-AS1,UCP2,LEPR,BAIAP3,MS4A8,CASR,BCHE,GABRB3,UNC5B,EDN3,PRG4,FRZB,PCSK1,GABRG2,POU3F1,BHLHE41,EHF,LCORL,ETV1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Delta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ductal cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CFTR,HNF1B,KRT20,MUC1,ONECUT1,AMBP,HHEX,ANXA4,SPP1,PDX1,CFB,GDF15,AKR1C3,MMP7,DEFB1,SERPING1,TSPAN8,CLDN10,SLPI,SERPINA5,PIGR,CLDN1,LGALS4,PERP,PDLIM3,WFDC2,AQP1,ALDH1A3,KRT19,TFF1,TFF2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ductal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Endothelial cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PECAM1,CD34,MCAM,CDH5,VWF,ENG,KDR,PDPN,SELE,A2M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Epsilon cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GHRL,ANXA13,PHGR1,BMP4,HMGCS2,TM4SF5,OLFML3,ASGR1,COX6A2,NPY1R,SLC7A9,BHMT,OPRK1,PTGER4,ITGA4,EYA4,XYLB,ELOVL2,AFF3,CORIN,MYO1A,HRH2,SLC6A16,PCSK6,ADAMTS6,COL22A1,FAM124A,COL12A1,CD109,THSD4,ARX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Epsilon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gamma (PP) cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPY,SCGN,FXYD2,SCGB2A1,GPC5-AS1,CMTM8,ARX,ETV1,PXK,SERTM1,SLITRK6,SEMA3E,APOBEC2,ABCC9,NEUROD1,PAX6,ISL1,CARTPT,THSD7A,AQP3,ENTPD2,PTGFR,CHN2,EGR3,LMO3,MEIS1,ZNF503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gamma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Immune system cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS4A1,CD19,CD4,CD8A,CD7,CTLA4,CD27,CCR7,CYTIP,IGHD,CD38,IL2RA,ISG20,SELL,IL7R,FOXP3,IGKC,IGLC3,IGLC2,CD79A,CD68,CD163,CD14,ITGAM,MRC1,MS4A7,CD3D,CD3E,CD3G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Immune</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT,ENPP3,IL2RA,ISG20,SLC18A2,CD9,FCER1A,TPSB2,FCER2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mesenchymal cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ITGB1,NT5E,THY1,ENG,KIT,ALCAM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MCs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pancreatic progenitor cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ONECUT1,PDX1,PTF1A,CXCR4,ISL1,NKX2-2,EPAS1,ARX,NEUROG3,SOX9,RPL23A,CTNNB1,YAP1,RGS16,MFNG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPCs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pancreatic stellate cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TIMP1,RGS5,SPON2,GEM,DYNLT1,PDGFRB,KRT10,CYGB,CCN2,MMP14,NDUFA4L2,PDGFRA,INHBA,TGFB1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSCs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peri-islet Schwann cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MPZ,EGFL8,GFRA1,OLFML2A,GULP1,SLITRK6,VGLL3,GFRA3,INSC,SLITRK2,FIGN,LRRTM1,SEMA3B,NGFR,PNLIPRP1,GFRA2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Islet Schwann</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liver</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cholangiocytes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSTR2,SLC4A2,KRT7,KCNN2,ITGB4,GGT6,CFTR,AQP4,AQP1,PIGR,GGT1,JAG1,GPBAR1,GGT7,KRT19,ONECUT2,ALPL,HNF1B,ALB,AGR2,TFF3,TFF1,SOX9,EPCAM,CLDN4,MMP7,TFF2,SCGB3A1,FXYD2,DEFB1,CD24,LCN2,CXCL1,CXCL6,LGALS2,TACSTD2,ELF3,SPP1,MUC5B,LGALS4,KRT8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Endothelial cell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FLT1,APPBP2,ARGLU1,ATP10D,BNIP1,BST2,BTNL9,C11orf96,CCDC85B,CCL14,CD4,CDC73,CDKL1,CHD4,CLEC1B,CLEC2B,CLEC4G,CLEC4M,CRBN,CRHBP,CTSL,DCLRE1C,DIPK2A,DLC1,DLG1,DLK1,DNASE1L3,DOCK1,DUSP5,EFNB2,ENG,F8,FCN2,FCN3,FILIP1,FOSB,FXYD6,GBP4,GGA2,GNG11,HES1,HYI,IL1R1,IL33,KDR,KIF1B,KLHL28,LDB2,MCAM,MCM3AP,MEF2C,MFN1,MGAT5,MPZL3,MRC1,OIT3,PIK3C2A,PPWD1,PTPRC,RASGEF1B,RASGRP3,RELN,RIN2,SECISBP2L,STAB1,STRN3,TCF12,TEX264,TFRC,TRAPPC11,TSPAN7,USP48,VWF,ZNF286B,STAB2,CD34,PECAM1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hematopoietic cell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CD34,PTPRC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HCs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hepatic stellate cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CYGB,PPARG,PDGFRA,RGS5,PPARA,FOXF1,ALB,NR1H4,CCN2,SEMA7A,WT1,FGF10,GFAP,NGFR,VEGFA,ACTA2,MYB,DES,FAP,SLC8A1,RELN,SYP,VCL,TIMP1,COL1A1,TAGLN,COL1A2,COL3A1,SPARC,RBP1,DCN,MYL9,TPM2,MEG3,BGN,IGFBP7,IGFBP3,CCN1,OLFML3,IGFBP6,CCL2,COLEC11,HGF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSCs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hepatoblasts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AFP,ALB,CEBPA,KRT14,DLK1,CDH1,FOXM1,GGT1,HNF4A,PROX1,MAP2K4,SMAD5,KRT18,KRT8,HNF1B,HHEX,MET</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hepatocytes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AFP,HNF4A,KRT8,ALB,KRT18,FOSL1,EPPK1,UCP2,GCK,LRP5,SLC10A1,NOS2,ATP7B,GJB2,FGFR4,PROX1,CRP,SLC2A2,TFR2,KIF13B,LIPC,VDR,ASGR1,ARG1,G6PC,OTC,SERPINA1,ZHX2,HHEX,FOXA3,FOXA2,FOXA1,CYP2E1,CYP1A2,CEBPA,CDH1,GPC3,AHR,CPS1,GLS2,PCK1,TAT,WT1,PRRG4,SULT1A1,APOH,CTNNB1,ABCC3,FGB,AQP3,PLSCR1,FGA,APOB,ANG,ANXA13,SAT2,SFRP5,A1CF,APOA1,BNIP3,FGL1,PAH,SERPINA6,APOA2,AZGP1,FGG,APOC3,DEFB1,TM4SF4,GC,AMBP,ORM1,TTR,HAL,ASS1,SCD,HMGCS1,ACSS2,TM7SF2,SEC16B,SLBP,RND3,BCHE,GHR,ALDH6A1,MASP2,AKR1C1,HAMP,GLUL,ACLY,ASL,TMEM97,CP,SLPI,ACAT2,TM4SF5,MSMO1,LEPR,RCAN1,AR,RPP25L,HSD11B1,APOM,TKFC,G0S2,PON3,C1orf53,TTC36,FST,MCC,AQP9,GSTA2,NNT,SAA4,MRPS18C,OCIAD1,APOA5,ENTPD5,C4B,EID2,TP53INP2,ATIC,SERPINH1,SAMD5,GRB14,CD3G,RHOB,EPB41L4B,GPAT4,SPTBN1,SDC2,PHLDA1,WTAP,ACADM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CD19,MS4A1,IL2RA,PTPRC,CD4,CD8A,CD3D,CD3E,CD3G,CD11c,CD14,CD16,CD56,CD16,CD42b,CD7,CD8,IgD,CD38,CD24,CD20,CD14,CD16,HLA-DR,CD11b,CD11c,CD123,CD15,CD33,CD66b,CD38,CD27,CD94,CD45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kupffer cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CD14,CD68,TNF,LYZ,MPO,VSIG4,PROK2,STARD5,MSR1,PPARA,TREM1,SLC11A1,MMP13,VDR,CHIT1,OSM,PPARD,CLEC4F,ADGRE1,IL1B,SLC40A1,G6PD,TIMD4,MNDA,SLC15A3,DNASE1L3,MARCO,HFE,CD38,CD163,CCR5,CLEC1B,CLEC4G,GPIHBP1,FOLR2,PLTP,FTL,IRF7,SPIC,CSF1R,C1QC,C1QA,C1QB,CLEC4E</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kupffer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liver progenitor cell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KRT7,KRT19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Progenitor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mesenchymal stem cell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CD44,ENG,NT5E,ITGB1,THY1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monocytes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FCGR3A,FCGR3B,CD14,Elane1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Muller cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apoe,Glul,Rlbp1,Abca8a,Vim,Aldh1a1,RLBP1,GLUL,PAX6,CA8,EDN2,KCNJ2,PRSS56,RGR,ApoE,Aqp4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Muller</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Astrocytes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRDX6,SLC1a3,PAX2,Rlbp1,GFAP,S100B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Retinal ganglion cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BMP4,GRIA4,GRM3,KCNJ2,MED1,NMT,POU6F2,ZIC2,SLC17a6,Pax6,THY1,Nefl,Pou4f2,SNCG,NRN1,Cerkl </t>
-  </si>
-  <si>
-    <t xml:space="preserve">RGCs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Retinal progenitor cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAX6,CALB2,SIX6,RHO,SIX3,NEFH,LGR5,SAG,RAX,NOTCH1,HES1,MSI1,SOX9,KIT,PDGFRA,Og9x,Sfrp2,Fgf15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPCs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rod bipolar cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRKCA,PCP4,RCVRN,SLC1A2,Car8,Sebox,Vsx2,Otx2,GRM3,KCNA4,KCNMA1,RORB,Cabp5,Og9x,Vstm2b, Casp7, Rpa1,GABRA1,LHX4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RBCs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cone bipolar cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PCP4,RCVRN,SLC1A2,Car8,Scgn,Vsx2,Otx2,MIP,GNAS,ISL1,SLC1A7,GJD2,GNB3,GRIA4,TJP2,LRIT2,Cabp5,Scgn,Vsx1,GABRA1,LHX4,LHX3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CBCs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GABAergic amacrine cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pax6,Tfap2a,Gad2,Fut4,Calb2,Pvalb,Pcp4,Vip,Thy1,STX1A,MIP, GNAS, ISL1,Gad1,ZEB2,TJP2,SEMA3D,POU6F2,KCNMA1,KCNA4,GRM3,GJD2,FRMPD2,Prox1,Nr4a2,Ngn2,C1ql2,Reln</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GABAergic ACs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rod photoreceptor cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rho,Pdc,NRL,ROM1,CRX,ARR3,CABP4,CACNA1D,DYNLRB2,EDN2,FRMPD2,GJD2,KCNQ5,KCNA4,LRIT1,LRIT2,MAF,MED1,RORB,RP1L1,TSPAN10,TTC8,Gcap2,Samd7 ,Cerkl ,SAMD11,SLC24A1,RP1,PDE6B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rod</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cone photoreceptor cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arr3,Opn1sw,NRL,ROM1,CRX,ARR3,OPN1LW,OPN1MW,CABP4,CACNA1D,EDN2,GJD2,GNB3,KCNQ5,LRIT1,MED1,RP1L1,THRB,TSPAN10,TTC8,Opmw,SLC24A1,RP1,PDE6B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microglial cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P2RY12,ITGAM,CD40,PTPRC,CD68,AIF1,CX3CR1,TMEM119,ADGRE1,C1QA,NOS2,TNF,ISYNA1,CCL4,ADORA3,ADRB2,BHLHE41,BIN1,KLF2,NAV3,RHOB,SALL1,SIGLEC8,SLC1A3,SPRY1,TAL1,CX3CR1,CX3CL1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microglial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Horizontal cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rcvrn,Prox1,Ntrk1,Lhx1,Lim2,Calb2,CALB1,LIM1,DLG2,TFAP2B,ZEB2,Lim1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Horizontal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Synapses</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SYP,DLG4,HOMER1,SLC32A1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Retinal pigment epithelial cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EZR,RPE65,BEST1,ANO2,BMP2,BMP4,CLU,EFEMP1,IL4,KCNJ5,MED1,RDH5,RGR,SBSPON,TGFBR1,TMEM98,TTC8,TRAF1,Cerkl </t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cornea epithelial cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KRT3,KLF6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CEP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Immune cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CD25,CD69,CD4,CD3,ITGAM,C1qa,Fcer1g,CD19,CD20,Trac,Ltb,Cd52,Trbc2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAX6,COL1A1,TGFB1,ACTA2,ICAM1,FBLN1,CRHBP,FN1,PDGFRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PECAM1,VWF,CDH5,BMP2,BMP4,CD34,CD55,FLT1,MED1,TGFBR1,TMEM98,TNFSF12,CD93,SLCO1A4,CLDN5,ICAM1,GNG11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kcnj8, Rgs5, Dlk1,  Abcc9,SUR2B,DLK1,VCAM1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extracellular matrix cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANTXR2,COL10A1,EFEMP1,LAMA2,SNTB1,TCF7L2,TGFBR1,TMEM98,VIPR2,ZIC2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ECMs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Glycinergic amacrine cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pax6,Tfap2a,Fut4,Calb2,Pvalb,Slc6a9,Pcp4,Vip,Thy1,STX1A,MIP, GNAS,ZEB2,TJP2,SEMA3D,POU6F2,KCNMA1,KCNA4,GRM3,GJD2,FRMPD2,Prox1,GlyT1,TgfB2,BE996002,Camkv,TCF4,Efna5,Dab1,Slc6a9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Glycinergic ACs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cholinergic GABAergic amacrine cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pax6,Tfap2a,Gad2,Fut4,Calb2,Pvalb,Pcp4,Vip,Thy1,STX1A,MIP, GNAS, ISL1,Gad1,ZEB2,TJP2,SEMA3D,POU6F2,KCNMA1,KCNA4,GRM3,GJD2,FRMPD2,Prox1,Nr4a2,Ngn2,C1ql2,Reln,VAChT,Tac1,Scube2,Cpne4,Sox2,Slit,SCGN </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cholinergic GABAergic ACs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tachykinin GABAergic amacrine cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pax6,Tfap2a,Gad2,Fut4,Calb2,Pvalb,Pcp4,Vip,Thy1,STX1A,MIP, GNAS, ISL1,Gad1,ZEB2,TJP2,SEMA3D,POU6F2,KCNMA1,KCNA4,GRM3,GJD2,FRMPD2,Prox1,Nr4a2,Ngn2,C1ql2,Reln,ZPF58,Cdh4,Grik4,Grm8,Slit2,SCGN </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tachykinin GABAergic ACs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Starburst amacrine cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pax6,Tfap2a,Fut4,Calb2,Pvalb,Pcp4,Vip,Thy1,STX1A,MIP, GNAS,ZEB2,TJP2,SEMA3D,POU6F2,KCNMA1,KCNA4,GRM3,GJD2,FRMPD2,Prox1,GAD1,CHAT,SLC5A7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Starburst ACs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kidney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cancer stem cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EPCAM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CSCs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CD19,IGHA2,IGHG3,IGHM,IGKC,JCHAIN,CD40,CD79A,CPNE5,FCRL5,HLA-DRA,IGHA1,IGHG1,IGHG2,IGKV1-12,IGLC2,IGLC3,IGLC7,IGLL5,MS4A1,MZB1,PKHD1L1,PNOC,POU2AF1,TNFRSF13C,CD3D,TRAC,IL7R,CD3E,CD8A,TRBC2,CD52,FCGR3A,IL32,KLRD1,CD68,CXCL8,FCGR3B,MNDA,KIT,PTGS2,SLC18A2,Trac,Ltb,Cd52,Trbc2,Shisa5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">α-intercalated cells (Collecting duct system)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FOXI1,OXGR1,ATP6V1G3,AQP6,CA2,NR1I4,SLC4A1,RHCG,ATP6V1B1,AVPR1A,P2RY14,FXYD2,TMEM213,CA2,DMRT2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">α-intercalated</t>
-  </si>
-  <si>
-    <t xml:space="preserve">β-intercalated cells (Collecting duct system)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FOXI1,OXGR1,ATP6V1G3,SLC26A4,CA2,NR1I4,RHCG,ATP6V1B1,AVPR1A,INSRR,FXYD2,TMEM213,CA2,AP1S3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">β-intercalated cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loop of Henle cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UMOD,AQP1,IRX1,IRX2,IRX3,MECOM,POU3F3,TBC1D4,SLC12A1,DEFB1,GEM,RGS5,CYP4B1,DRAM1,NEK6,CDKN1C,CALCRL,CLCNKA,CRYAB,SPP1,PPP1R1B,LRRC66,IGF1,CLDN1,CLDN10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Henle loop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mesangial cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PDGFRB,PDGFB,LAMA4,ITGA8,LGALS1,ARID5B,CCR7,FN1,GATA3,PAWR,SERPINE2,TBX18,TEK,THY1,REN,ZEB2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Podocytes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NPHS1,NPHS2,EZR,TDRD5,SEMA3G,SEMA5A,SEMA3E,PLA2R1,COL4A4,ARHGAP24,WT1,COL4A3,RHPN1,MAFB,PODXL,CLIC5,CD2AP,NOTCH2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal cells (Collecting duct system)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KCNE1,APELA,AQP2,AQP3,GATA3,ELF5,STC1,TBX3,CLDN4,KCNJ1,AVPR2,FXYD4,HSD11B2,SCNN1G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Inner Medullary cells (Collecting duct system)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S100A4,PLEKHB1,ALDH1A3,TM6SF1,SLC14A2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Proximal tubule cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FXYD2,ATP1B1,SLC3A1,CUBN,PDZK1,LRP2,POU3F3,AGXT2,GSTA2,CYP2E1,CRYL1,GLYAT,SORD,UPB1,SOD3,HNF4A,CDKN3,NAPSA,SLC7A13,SLC17A3,HGD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cap mesenchyme cells (Mesenchymal cells)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SIX2,ITGA8,NR2F2,EYA1,MEIS2,CITED1,MUC1,NOTCH2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cap mesenchyme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TGFBR2,NOTCH4,ADGRL4,EMCN,ENG,PECAM1,PLAC8,PLVAP,TEK,KDR,VWF,MMRN1,CD93</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stromal cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MEIS1,TCF21,COL1A2,COL3A1,TNC,COL6A3,LGALS1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stromal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Juxtaglomerular cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REN,CRIP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Juxtaglomerular</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Renal interstitium (Mesenchymal cells)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SFRP1,MEIS1,PDGFRA,C7,MGP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Renal interstitium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connecting tubule cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CALB1,TRPV5,FXYD2,ATP6V1B1,SLC8A1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connecting tubule</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Distal tubule cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KLK1,KCNJ1,KL,EGF,TMEM213,TMEM52B,SOSTDC1,SLC12A3,EMX1,CLDN3,CLDN8,UMOD,PCOLCE,CDC42EP3,CLCNKB,FXYD2,POU3F3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Distal tubule</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hematopoietic cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CORO1A,MNDA,SRGN,HLA-DPA1,LST1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ureteric Bud cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GFRA1,RET,WNT9B,CLDN6,LAMA1,NMU,Wnt11 ,Etv4, WNT7B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Renal Vesicle cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NCAM1,EMX2,LHX1,BMP2,DKK1,DLL1,GREB1,PAPSS2,PCSK9,POU3F3,TMEM100,WT1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GFAP,SLC1A3,SLC1A2,GLUL,S100B,ALDH1L1,AQP4,IGFBP3,ATP13A4,CBS,SOX9,CD40,CD80,CD86,C5AR1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cholinergic neurons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHAT,SLC18A3,ACHE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dopaminergic neurons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TH,SLC6A3,FOXA2,KCNJ6,NR4A2,LMX1B,DBH,SLC6A2,PPP1R1B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PECAM1,VWF,A2M,APOLD1,FLT1,TM4SF1,CD34,MCAM,ENG,PTPRC,VCAM1,CDH5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GABAergic neurons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLC6A1,GABBR1,GABBR2,GAD2,GAD1,SLC32A1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Glutamatergic neurons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLC17A7,SLC17A6,GRIN1,GRIN2B,GLS,GLUL,GRIN2A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Immature neurons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DCX,NEUROD1,TBR1,STMN1,NCAM1,TUBB3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS4A1,CCR6,CXCR3,CD4,IL2RA,ISG20,TNFRSF8,Trac,Ltb,Cd52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mature neurons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RBFOX3,MAP2,SYP,DLG4,TUBB3,MAPT,INA,GAP43,NRP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P2RY12,ITGAM,CD40,PTPRC,CD68,AIF1,CX3CR1,TMEM119,ADGRE1,C1QA,NOS2,TNF,ISYNA1,CCL4,ADORA3,ADRB2,BHLHE41,BIN1,KLF2,NAV3,RHOB,SALL1,SIGLEC8,SLC1A3,SPRY1,TAL1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Myelinating Schwann cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOX10,EGR2,MBP,MPZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Myelinating Schwann</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Neural Progenitor cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CSPG4,RNF5,EOMES,SOX2,SOX1,NES,PAX3,PAX6,OTX2,CNTNAP1,ASCL1,SMARCA4,MSI1,MSI2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Neural Progenitor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Neural stem cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOX2,PROM1,NES,SOX9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Neural stem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Neuroblasts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NEUROD1,DCX,DLX2,PROX1,EOMES,TUBB3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Neuroepithelial cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NES,SOX2,NOTCH1,HES1,HES3,CDH1,OCLN,SOX10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Neuroepithelial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non myelinating Schwann cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOX10,GAP43,NCAM1,NGFR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non myelinating Schwann</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oligodendrocyte precursor cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LHFPL3,MEGF11,PCDH15,PDGFRA,CSPG4,RNF5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oligodendrocyte precursor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oligodendrocytes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OLIG1,OLIG2,OLIG3,CLDN11,MBP,MOG,MAG,GALC,CNP,SOX10,FA2H,UGT8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radial glial cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VIM,NES,PAX6,HES1,HES5,GFAP,SLC1A3,FABP7,TNC,CDH2,SOX2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radial glial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Schwann precursor cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOX10,GAP43,FABP7,MPZ,DHH,NGFR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Schwann precursor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Serotonergic neurons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TPH1,SLC6A4,FEV,HTR1A,HTR1B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tanycytes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GPR50,COL23A1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Airway epithelial cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADH7,AQP1,CDH1,SEC14L3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Airway epithelial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Airway goblet cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AGR2,AQP5,CEACAM1,DMBT1,DUSP4,FXYD3,GALNT5,GALNT6,GGH,GOLPH3,GP2,IL19,LIPF,LTF,LYNX1,MSLN,MUC16,MUC4,MUC5B,NOS2,PIGR,QSOX1,SCGB3A1,SEC23B,SPDEF,TFF2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Airway goblet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mesothelial cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C2,CALB2,CD44,CDH1,DES,EFEMP1,EPCAM,GSTA3,KRT5,KRT7,KRT72,LGALS7,LRRN4,ME1,ME2,MSLN,MUC16,OSR1,RSPO1,THBD,UPK3B,WT1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mesothelial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COL3A1,COL5A2,DPT,FN1,GSN,LRP1,PDGFRA,TCF21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Basal cells (Airway progenitor cells)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABI3BP,AQP3,DAPL1,GSTM2,HPGD,ICAM1,KRT14,KRT15,KRT5,PHLDA3,RPS18,SDC1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Basal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alveolar macrophages</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABCG1,CCL3,CD36,CLEC7A,CSF2RB,CXCL2,G0S2,GAL,GDA,GNGT2,GPNMB,IL18,IL1B,ITGAX,KLHDC4,MARCO,MCEMP1,MPP1,MRC1,OLR1,PLET1,S100A4,TLR2,TNFAIP2,TRIM25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ciliated cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APPL2,ATP5MD,CCDC153,CCDC17,CCDC181,CCDC39,CYP2S1,FAM161A,FOXJ1,LRRC23,ODF3B,SCGB1A1,SEC14L3,SNTN,STK11,TMEM212,TSPAN19,TUBB4B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ciliated</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clara cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AHR,ALDH1A1,BPIFA1,CTSE,CYP2E1,CYP4B1,ERN1,FOXM1,LEPR,MUC1,MUC4,MUC5B,RAB3D,SCGB1A1,SCGB3A1,SCGB3A2,SFTPA1,SFTPC,SFTPD,SYT2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clara</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADGRE1,ARG1,BIRC5,CCL17,CCL18,CD14,CD163,CD19,CD22,CD3D,CD3E,CD3G,CD4,CD44,CD5,CD68,CD74,CD80,CD83,CD86,CD8A,CD8B,CDCA3,CDK1,CEBPE,CR2,CSF1R,EAF2,FCER2,FCGR3A,FLT3,GIMAP3P,HLA-DRA,HMMR,IGHM,IL2RA,ITGAE,ITGAM,ITGAX,LAX1,MS4A14,MZB1,NRP1,NUSAP1,PAX5,PRG2,PTPRC,SLPI,THBD,TNFRSF17,TRBC1,XCR1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CD34,EGFL7,EMCN,ESAM,FLT1,KDR,MCAM,PECAM1,RAMP2,TEK,VWF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Epithelial cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANPEP,EPCAM,IL10,IL6R</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Epithelial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ionocytes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CFTR,CLCNKB,FOXI1,KCNMA1,SCGB1A1,SLC12A2,TFCP2L1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pulmonary alveolar type I cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AGER,AKAP5,AQP3,AQP5,CCN2,CLDN18,CLIC5,COL4A3,COL4A4,CRLF1,CYP4B1,EGFL6,EMP2,FSTL3,GPRC5A,HOPX,ICAM1,IGFBP6,KRT7,MEX3B,MMP11,P2RX7,PDPN,PXDC1,RTKN2,SCNN1A,SCNN1B,SCNN1G,SEC14L3,SEMA3B,SEMA3E,SMARCA1,VEGFA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AT1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pulmonary alveolar type II cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABCA3,ADGRF5,AGER,CD36,CD3G,CEBPA,CLDN18,CRLF1,CTNND1,CXCL2,CXCR2,DDX3Y,EGFL6,ETV5,GRK2,IL1B,INMT,IRX1,LAMP3,LPCAT1,LRG1,MUC1,NAPSA,NKX2-1,NRN1,PGC,PIGR,PPBP,PPP1R14C,RUNX3,S100G,SDC1,SFTA2,SFTPA1,SFTPB,SFTPC,SFTPD,SLC34A2,SOAT1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AT2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Secretory cell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MUC5B,PIGR,SCGB1A1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Secretory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adrenal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CSH1_CSH2 positive cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CGB,GH2,PSG5,CGA,CSH1,ERVW-1,CSH2,PSG7,PSG11,HSD3B1,PSG9,PSG1,PSG6,PLAC4,PSG4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Megakaryocytes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C15orf54,GP9,PF4,PPBP,GP1BA,MEGT1,LY6G6F,GP6,ITGA2B,C6orf25,ALOX12,FCER1A,ELOVL7,NRGN,RP11-930O11.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Schwann cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WNT16,MPZ,FOXD3,SOX10,CDH19,GPR17,PMP2,COL20A1,INSC,RP4-792G4.2,TTYH1,SOX2,LAMP5,OLFML2A,ATP1A2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Myeloid cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS4A14,LILRA1,RP11-554D14.6,AC007040.8,MS4A7,RP11-489O18.1,CLEC10A,MS4A4A,RN7SL138P,CD163,CD14,SIGLEC1,VSIG4,CLEC7A,LILRA2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sympathoblasts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NPAS4,SLC24A2,RP11-542G1.2,PENK,LINC00890,KLK4,RP11-17A4.2,RP5-1096J16.1,C18orf42,TTC40,ARC,FAM19A3,VWA5B1,PPP1R17,RP4-718N17.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Erythroblasts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TPSAB1,CTD-2008P7.9,RP11-85G21.3,CTSE,CTA-392E5.1,EIF5AP2,CTA-363E6.6,C17orf99,SLC4A1,TRIM10,MIR144,ART4,AHSP,GYPA,HBM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stromal cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MIR1245A,NPY5R,RP11-60A8.1,RP11-254F19.2,RP11-494K3.2,RP11-758M4.4,RP11-142A23.1,RP11-752L20.5,OSR1,RP11-867G23.13,SULT1E1,HHIP,MGP,PRELP,TWIST2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vascular endothelial cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCL23,FGF23,SMIM9,RP13-1016M1.2,RP11-100L22.1,RP11-327L3.3,RP1-149A16.12,GPR182,DLL4,GALNT15,CALCRL,CD300LG,FLT4,FCN3,GPIHBP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chromaffin cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NRG1-IT3,RNU6-457P,LINC00594,AC018643.4,RP11-159N11.3,CTC-537E7.1,Y_RNA,snoU13,CTD-2006K23.2,RP5-955M13.4,INSRR,KCNK10,PHEX-AS1,RP11-958J22.1,FLJ30594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lymphoid cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GZMH,XCL1,KLRC3,RP11-94L15.2,GZMA,IL2RB,TRAT1,SH2D1A,DTHD1,CD3E,ZNF831,GNLY,PRF1,IGHD,THEMIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adrenocortical cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RP1-145M24.1,RP11-238I10.1,AC005392.13,RP11-316I3.2,RP11-501O2.4,SDIM1,RP11-258O13.1,AJ006998.2,CTD-2517O10.5,RNU6-944P,CTB-43E15.4,RP11-34F13.3,RP11-536K7.5,RP11-183M13.1,RNU6-56P</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLC26A4_PAEP positive cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IL1A,SLC26A4,SNX25P1,VMO1,CTD-2210P15.2,CTC-360P9.4,ULK4P1,SNORA14A,RNU6-518P,RP11-431N15.2,RP11-26J3.3,RP11-378A12.1,SPINK8,HSD3B2,KIRREL-IT1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MEGT1,LY6G6F,TUBB1,PPBP,PF4,GP9,TPSB2,HBD,AC137932.6,ITGA2B,GP1BA,CLEC1B,PTCRA,BEND2,RP11-179A10.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Epicardial fat cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RP11-89M22.3,CTD-3012A18.1,PRG4,KRT7,SPRR2F,KLK11,MKRN9P,UPK1B,EPGN,NPHS1,ITLN1,LRRN4,CST6,GSDMA,RAET1E</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lymphatic endothelial cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GPR182,GPR97,STAB2,HOXD9,TBX1,CCL21,HOXD10,TSPEAR,ABCA4,PGM5-AS1,TFF3,LINC00636,RP11-341G23.4,HOXD4,RP11-451M19.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GFRA3,SOX10,MPZ,LINC00466,COL20A1,MIA,ASPA,ERBB3,TFAP2A,INSC,ARTN,PMP2,S100B,FOXD3,AP000797.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GZMB,FCRL2,KLRC2,XCL1,LINC00861,PRF1,CD3G,SH2D1B,ANTXRLP1,VPREB3,SH2D1A,CRTAM,CXCR6,RP11-94L15.2,GZMK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">XCR1,TMPRSS4-AS1,TIMD4,PRTN3,MMP9,CD86,CLEC5A,SIGLEC1,CLEC7A,C1QC,P2RY13,FCN1,CSTA,CD300LF,MS4A6A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Endocardial cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANGPTL5,APCDD1L,NPPC,SLC6A4,SALL1,LEPR,C3orf36,AC004562.1,FAM3D,HAPLN1,APCDD1,LYPD2,FOXC1,MPZL2,RP11-849I19.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESM1,SLC9C1,OPN5,QRFPR,MIR4454,AC007743.1,PKD1L1,TM4SF18,APLNR,CLRN1-AS1,CD300LG,C1QTNF9,AC019100.3,MADCAM1,RP11-298O21.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RP11-60A8.1,SCARA5,DPT,CILP,ZCCHC5,AGTR2,MFAP5,RP11-71N10.1,LUM,ABCA10,RP11-31K23.2,CCL11,NRK,PDGFRA,LPAR4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Smooth muscle cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PDE4C,RP11-112H10.4,RP11-598F7.5,RP11-626H12.1,HCG22,CTD-3064M3.3,RP11-231I13.2,GPR20,RP11-267N12.1,OR51E1,THBS4,MIR143HG,PDGFRB,AOC3,ENPEP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SATB2_LRRC7 positive cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NEUROD2,FEZF2,NEUROD6,TBR1,MPPED1,SATB2,FOXG1,PCDH11Y,CAMKV,BHLHE22,SLIT1,C14orf23,RP11-562L8.1,LINC00966,DRAXIN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RP5-857K21.7,CENPW,SLC46A1,GSPT2,RHCE,SLC7A11,P2RX6,SKA1,FARSA,ZNF90,TMCC2,RP11-225B17.2,TMEM161A,ZNF583,ENPP4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Visceral neurons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GATA3-AS1,GAL,CHRNA3,PRPH,PHOX2A,GALR1,NXPH1,TMC3,DDC,SST,OPRM1,PIRT,NECAB2,ECEL1,SLC10A4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cardiomyocytes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RP11-439H8.4,RNA5SP327,CTD-2552K11.2,Y_RNA,AC018464.3,HHATL,BMP10,RP11-461A8.4,UGT2B4,PRSS42,WI2-1896O14.1,FABP2,EPN3,RP11-406O23.2,AC009878.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ELF3_AGBL2 positive cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C1orf194,ZMYND10,MS4A8,IL20RA,ELF3,SCGB3A2,EFCAB1,SFTPB,WDR65,CP,PIH1D2,AGBL2,SFTPC,DNAH9,MUC1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CLC_IL5RA positive cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FAM209A,CERKL,CLC,PRG2,MS4A3,IL5RA,ZC2HC1C,CTD-2620I22.1,CTD-3032H12.2,RP11-252E2.1,AC011524.1,S100A1,Y_RNA,LINC00407,RP11-516C1.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intestine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AHSP,SPTA1,HBG2,HBA2,HBM,HBG1,HBA1,SLC4A1,HBB,GYPA,HEMGN,HBZ,ALAS2,MIR144,MYL4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARX,NKX2-2,CCK,CRYBA2,NEUROD1,FEV,MLN,ASIC5,ONECUT3,SST,RP11-788H18.1,PAX4,KCNH6,SSTR5,PCSK1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACTG2,GREM2,CNN1,RP11-467I20.6,WIF1,TACR2,OVCH2,FRMD6-AS2,DES,MYH11,RP11-626H12.1,ANO1,CHRDL2,TAGLN,FBXL22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VSIG4,RPL32P1,CD207,AP000439.1,HCAR3,C5orf20,AC010492.4,P2RY13,LILRB2,LILRB5,IL1B,C1QB,CD163,C1QC,DNASE1L3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IL17A,ICOS,SH2D1A,GZMK,RP11-553L6.2,TRGC1,RP11-104L21.3,TRDC,GZMA,VPREB1,CCR4,LTA,NCR2,CD247,RP11-94L15.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intestinal epithelial cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNC5CL,C1orf177,TRIM31,LINC00955,RP3-417L20.4,HMGN1P20,ALPI,RP11-395B7.2,EGFR-AS1,RP11-462G2.1,DEFB1,CA7,RP11-468N14.13,ARL14,AC024592.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENS glia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SERPINA3,RLBP1,GPR12,RP4-792G4.2,CDH19,COL20A1,SOX10,PLP1,SOX2,FOXD3,MPZ,BCAN,TFAP2A,SOX2-OT,PTPRZ1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENS neurons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PDIA2,RP11-672L10.2,GRP,DRGX,GCGR,SLC18A3,PHOX2A,HECW1-IT1,RP11-202H2.1,IQCJ,STMN4,TTC9B,GAL,CEND1,NEFL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOX17,GPIHBP1,PRND,CLEC3B,FLT1,MMRN2,BTNL9,APLNR,LHX6,NOTCH4,RP11-3K16.2,ESAM,RP11-328D5.1,ESM1,GJA5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RP11-13P5.2,MSC,RP1-283K11.3,RP5-1077H22.1,CTD-2541J13.1,AC002511.2,AC002511.3,MMP27,CTD-2334D19.1,CXCL14,FZD10,PDGFRA,AC003090.1,RP1-288H2.4,ITGA11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AP000705.7,HAS1,TNNT1,BNC1,DSC3,WT1,WNT10A,C21orf62,PTPRQ,CEMP1,C3,CRB2,KLK11,PHYHIP,TGM1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RP11-474N8.5,TBX1,STAB2,CCL21,LINC00636,TSPEAR,ART5,CTC-236F12.4,GPR1,RP11-322E11.5,MPP7,Y_RNA,ABCA4,PLIN5,TP63</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Muscle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PF4,ITGA2B,LIPH,ELOVL7,GP6,ITGB3,PTGS1,RP11-480G7.1,RP11-170N16.2,C3orf55,RP4-655J12.4,TUBB1,DCLRE1A,TMEM40,GNAZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UGT8,POU3F1,PMP2,GFRA3,KCNC2,MPZ,SOX10,PTPRZ1,COL20A1,LINC01037,BCAN,C2orf72,C10orf82,RP11-946L20.2,MAG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NTS,TFF3,CCL21,STAB2,PTX3,PCLO,IL7,P4HA3,C6orf141,PIK3C2G,ASGR2,ANKRD36BP2,NALCN,FAM26F,NHLRC1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RHAG,GYPA,AHSP,GYPB,HBZ,ALAS2,SLC4A1,SLC14A1,EIF5AP2,HBM,HBA1,EPB42,RP11-57H12.2,ALS2CR12,SLC25A37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skeletal muscle cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RP11-755O11.2,ASB15,RP11-456H18.2,RPL7P3,PVALB,RN7SL365P,RP11-432J24.5,C8orf22,ASB10,RP5-921G16.2,CLDN9,RP5-1039K5.13,AC137723.5,RP11-255G21.1,AC093063.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WSCD2,C13orf45,LINC00645,RP1-300G12.2,RP11-217C7.1,RP11-332E3.2,RP11-473E2.4,CTD-2555C10.3,RP11-342A23.1,WNT10B,ACKR4,DIO3,CCDC129,ZCCHC5,RP11-38H17.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Satellite cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AC004014.3,MYEOV,TACR3,GDPD4,USP44,RGR,RP11-320P7.2,FAM132B,GPR123,CTB-175P5.4,ENPP7P10,CHRDL2,PAX7,RP11-706J10.1,MAPK15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MIR4454,SLC5A4,AL118508.1,CA4,RP11-206M11.7,PRSS51,NOS3,GRIN2A,GFRAL,CD300LG,MADCAM1,RP11-327L3.3,C1QTNF9,ANO2,AP001597.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OR51E2,AC131025.8,ADORA2B,MYH11,SLC38A11,MIR143HG,MIR145,RP11-1101K5.1,P2RX3,GPR176,ANO1,OR51E1,CORIN,CACNA1C-IT3,TMC4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FCN1,MS4A4E,TMPRSS4-AS1,CD86,FLT3,P2RY13,IL10RA,FOLR2,MNDA,HLA-DQB1,MS4A4A,AMICA1,CYTH4,MS4A6A,CFP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IL7R,CD8A,NKG7,CD247,NCR1,RP11-61O1.1,TRAC,CD3E,ITK,CD2,MATK,RP11-444A22.1,SYTL1,IL2RB,GZMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Placenta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAEP_MECOM positive cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RP11-98L5.2,AC104654.1,PAEP,RP11-274B18.4,PIGR,TSPAN1,AC012593.1,RP11-510D19.1,POU5F1,UGT2B7,DEFB1,RP11-697E22.2,SLC18A2,PAX8,SLPI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AFP_ALB positive cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLC2A2,ALB,APOB,AFP,ITIH2,F2,MAT1A,APOC3,SERPINC1,FABP1,APOA2,AHSG,SERPINA10,SLC38A3,SERPINA4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extravillous trophoblasts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AC022596.6,GKN1,CILP2,LINC00330,PDE6H,PRG2,RP11-872D17.8,HLA-G,ASCL2,NOTUM,AC006262.5,DAW1,NOG,TAC3,RP11-420L9.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IGJ,IGHM,KLRC3,GZMH,PTGDR,IGHGP,IKZF3,IFNG-AS1,TIGIT,KLRC2,LCK,ANKRD36BP2,TNFRSF18,IGHG3,LINC00861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trophoblast giant cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCK,CTA-833B7.2,PSG1,CGB,CSH2,PSG6,KISS1,INHBA,GH2,PSG9,CRH,PSG8,RP11-76E12.1,PSG4,TREML3P</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RP11-162G9.1,FAM162B,WNT3A,AFF2,CDH19,SCN11A,GPR20,COX4I2,AGTR1,ADAMTS20,RP11-123O22.1,HIGD1B,AC020571.3,COLEC10,KCNK17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IGFBP1_DKK1 positive cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RP3-404K8.2,RP11-486P11.1,FOXL2,WT1,RP11-171A24.3,SCARA5,LRRN4CL,S100A3,WT1-AS,PRL,WNT4,AC012065.7,APOD,BRINP2,RORB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AP006285.6,AC002451.1,RP11-99L13.2,RP1-79C4.4,MMP23B,RP11-248N22.2,LA16c-380H5.4,MIR218-1,C8orf87,SNORD113,RP11-74M11.2,HSD3BP2,AP001605.4,LINC00314,AC007394.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RP11-1028N23.4,RP11-297H3.3,AC007743.1,RP11-327L3.3,CD34,ARHGEF15,CXorf36,LRRC36,SOX7,RP11-328D5.1,NTS,CDRT1,LINC01049,ROBO4,HS3ST3A1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Syncytiotrophoblasts and villous cytotrophoblasts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CTD-2050E21.1,POTEKP,RP11-344B2.3,RP11-366M4.3,RP11-2A4.4,RP11-483F11.7,FTLP14,RP11-718G2.5,RP11-18D7.3,CLCA2,KB-1440D3.13,CTBP2P8,RP11-359P18.1,HSPD1P6,AC124861.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SIGLEC10,RP11-1143G9.4,LYZ,ADAMDEC1,LILRB2,HLA-DRB5,SDS,HLA-DOA,SIGLEC1,MMP9,LILRB4,C1QB,TLR2,TLR7,S100A8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EGF,TUBB1,PPBP,ITGA2B,RP11-930O11.1,RP11-152K4.2,LINC00989,PF4,C6orf25,LINC00534,PKHD1L1,NRGN,DNM3,RP11-466L17.1,RP11-142C4.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spleen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SERPINA6,PLG,AMBP,SERPINC1,BHMT2,LBP,PRAP1,APOB,SERPINA1,FGB,VTN,SLC2A2,FGG,MT1G,ITIH1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RN7SL337P,KLRC4-KLRK1,RP11-553L6.2,RP11-861A13.4,RP11-38J22.6,ZNF860,RP11-693J15.5,RP11-61O1.1,FCRL3,CTD-2215E18.1,RP5-1028K7.2,IKZF3,LINC00861,IL9RP3,VAV3-AS1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CLEC9A,RP11-489O18.1,RP3-522P13.3,RP11-807H22.7,RP11-1080G15.1,FCN1,EMR4P,TMPRSS4-AS1,RP11-157G21.2,CSF2RA,OSCAR,RP3-522D1.1,CD163L1,RUFY4,DLEU7-AS1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RP11-189E14.5,ODF3L2,RP4-765C7.2,AC019100.3,RP11-172F10.1,CTD-2207L17.2,RP1-154K9.2,AC010084.1,SLC5A4,OR5G5P,HOXD3,SNTG1,EEF1A1P31,ADAMTSL1,MYRIP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CTD-2270F17.1,ENPP7P4,AC105053.3,RP11-388K12.1,SCTR,KBTBD11-OT1,ADRA1B,NPM1P10,NPY5R,TPH2,CTC-535M15.2,MIR143HG,KLHL29,AC023481.1,CADPS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STC2_TLX1 positive cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAMK2N2,CLVS2,RP11-384O8.1,FBXL16,GABRG2,HRK,EBF3,TRH,AC018730.1,CTD-3193O13.9,CPLX2,ATP1A3,TMEM119,IFI27L2,PET117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAB27B,RP11-556I14.2,EGF,GP6,RP11-930O11.1,LINC00989,SELP,GP1BA,HPSE,RP11-152K4.2,LINC00504,MMRN1,ITGB3,ELOVL7,LY6G6F</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QRFPR,SLPI,LHX9,PLA2G2A,CGN,NPHS1,KRT5,LRRN4,KLK11,OLR1,PTPRQ,COL8A1,PDZK1IP1,HAS1,SFRP2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HDC,PRSS57,EIF5AP2,PPAPDC1A,MTL5,CTA-392E5.1,ACSBG1,RP5-964N17.1,GYPA,SLC25A21,RP11-146I2.1,MIR144,SLC2A14,CTA-363E6.6,SLC4A1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stomach</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Neuroendocrine cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLC18A1,GHRL,GAST,FEV,NKX2-2,CRYBA2,MBOAT4,CDK5R2,RFX6,HAP1,RP11-82C23.2,RBPJL,PTF1A,PAX6,CACNA1A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KLF1,SLC4A1,HBM,NFE2,HBZ,GYPB,HBG2,HBB,ALAS2,SPTA1,HBA1,HEMGN,RNF224,HBG1,HBA2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ciliated epithelial cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCDC37,C11orf88,FAM216B,LDLRAD1,TUBA4B,KIF19,DYDC2,ANKRD66,C9orf117,C10orf67,AC013264.2,LRRC71,CAPSL,TSPAN19,STOML3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Squamous epithelial cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KRT6B,CAPNS2,KRT6C,FGFBP1,KRT6A,KRT17,ADH7,SERPINB10,KRT16,S100A3,CLCA2,LY6D,KRT4,AC019349.5,GPR87</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parietal and chief cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RP11-467I20.6,ETNPPL,ATP4B,FGB,FGA,SIGLEC11,FRMD1,TRIM50,ALB,ATP4A,ANGPTL3,MFSD4,APOBEC2,CKM,PAQR5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MUC13_DMBT1 positive cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ISX,GUCA2B,ENPP7,MIR194-2,BTNL3,TM4SF20,SI,SLC17A4,ALDOB,CDX1,DMBT1,CHP2,KRT20,SLC5A12,ADRA2A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C1QC,HLA-DQB1,MS4A6A,CD14,C1QB,CD163L1,IGSF6,CCDC26,C1QA,NCF2,HLA-DRB1,HLA-DRB5,CLEC7A,MS4A7,HLA-DPA1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Goblet cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UGT2B15,IL17C,GKN2,SLC22A8,CXCL5,CSF3,TFF2,A4GNT,FBP2,FGF20,MUC6,GKN1,CXCL1,MUC5AC,CA9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AC002511.2,PTGER1,OSR2,AC003090.1,ACTG2,INHBA,HSPB6,AC131025.8,SHISA3,DPT,TRPA1,ACTA2,TWIST2,CXCL14,GLIS1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRPH,STMN2,ATP1A3,KCNIP4,NKAIN1,INA,GAP43,ATCAY,CNGB1,TCEAL5,STAC,DCX,RP11-457K10.1,FAM163A,CNTN5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOX10,MPZ,ATP1A2,BAI1,PLP1,CDH19,COL20A1,ELOVL2,NOV,PRIMA1,RP11-308N19.1,SLC35F1,LGI4,VGLL3,EGFLAM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SELE,PRND,APLNR,ARHGEF15,PLVAP,FLT1,PCDH12,MADCAM1,GPIHBP1,GALNT15,RP4-601K24.1,MEOX1,A2M,CCM2L,CLEC14A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NTS,STAB2,CCL21,RADIL,RP11-444A22.1,TFPI,RP11-142C4.6,TNFAIP8L3,LY86-AS1,PTGS2,RP11-554D15.1,EFCC1,MMRN1,Y_RNA,NFATC1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RP11-74M11.2,AP000705.7,BNC1,SPHKAP,PTPRQ,NPHS1,TNNT1,TFPI2,BDNF,PDZRN4,LRP2,GFPT2,HAS1,WT1,COL8A1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ICOS,CD27,NKG7,CD28,CD3D,CHI3L2,TRAT1,THEMIS,CD52,KLRB1,CD79B,CCL5,TRBC2,SIRPG,CD3E</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PDE1C_ACSM3 positive cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RP11-690G19.4,ACSM3,C1orf95,KCNE4,PDE1C,PSEN2,ERBB4,ATP6V0A4,TFCP2L1,WNK3,GABRB2,ADARB2,AMACR,SHISA2,NOX4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thymus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thymic epithelial cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RP11-81F13.2,KCNJ5,RP11-153K16.1,RP11-81F13.1,LL22NC03-75H12.2,RP11-112J1.2,RP11-114G22.1,RP6-24A23.6,C11orf16,SLC46A2,CACNA1I,PTPRT,NPFFR2,RP1-223B1.1,C12orf56</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PLAC9,LOX,MGP,COL1A2,COL5A3,COL1A1,ASPN,FGF18,MMP2,ISLR,DCN,SFRP2,COL3A1,SCARA5,COL6A6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Antigen presenting cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IL1RN,EBI3,FGD2,MCOLN2,MMP9,TLR10,LINC00996,CD80,CXCL10,SLAMF7,P2RY13,SLC24A4,HCK,C1QB,LYZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADAMTS9,PROX1,MET,AC011526.1,MEOX2,ANO2,CTD-3179P9.1,NOVA2,AOC3,CXorf36,GPR116,PODXL,NRN1,PTPRB,LINC00472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thymocytes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RP11-104L21.3,BEST3,HKDC1,KLRC4-KLRK1,RP11-305P22.9,LTA,TMSB15B,RP11-739G5.1,UBASH3A,PLK4,FBXO41,LIN28B,SKA3,CD40LG,AC002454.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cancer cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CD44,EPCAM,ERBB2,FOLH1,KRT18,PROM1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cancer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CD24,CD44,FLOT2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANPEP,CD44,EPCAM,POU5F1,PROM1,THY1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABCG2,ALCAM,ALDH1A1,BMI1,CD24,CD44,KIT,NANOG,NES,PDPN,POU5F1,PROM1,SOX2,THY1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CD44,MBTPS2,PARP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FUT4,MSI1,NES,PROM1,SOX2,THY1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IR-Immune system</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PTPRC,CD34,FLT3,RAG1,RAG2,VPREB1,IGLL1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CD27,CD20,MS4A1,TRAC,TRBC1,TRBC2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PTPRC,CD19,VPREB1,IGLL1,RAG1,RAG2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CD27,CD34,TRAC,TRBC1,TRBC2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PTPRC,IGHM,IGHD,CD22,CD19,CD38,CD24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CD27,CD138,SDC1,CD20,TRAC,TRBC1,TRBC2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PTPRC,IGHG1,IGHG2,CD27,CD20,MS4A1,TNFRSF13B,TACI,IGHG3,IGHG4,IGHA1,IGHA2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CD34,CD138,PRDM1,TRAC,TRBC1,TRBC2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PTPRC,PRDM1,XBP1,BLIMP1,MZB1,SDC1,CD138,JCHAIN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CD20,MS4A1,TRAC,TRBC1,TRBC2,CD19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCR6, CCR7, CD11B, CD127, CD2, CD27, CD30, CD3D, CD3E, CD3G, CD3Z, CD45, CD45RA, CD52, CD6, CD62L, CD8, CD8A, CD8B, CTLA4, DAPL1, FOXO1, FOXP1, FOXP3, GNLY, GZMB, IL2RA, IL7R, KLF2, LCK, LEF1, LTB, PTPRC, SELL, SHISA5, TCF7, THY1, TRAC, TRBC1, TRBC2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GZMB,CD56,NCAM1,CD8A,CD8B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACTN1, CCR6, CCR7, CD11B, CD127, CD2, CD27, CD30, CD3D, CD3E, CD3G, CD3Z, CD4, CD45, CD45RA, CD52, CD6, CD62L, CTLA4, DAPL1, FOXP3, GZMB, IL2RA, IL73, KLF2, LCK, LEF1, LTB, PTPRC, SELL, SHISA5, TCF7, THY1, TRAC, TRBC1, TRBC2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GZMB,CD56,NCAM1,CD4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCR6, CCR7, CD11B, CD127, CD2, CD25, CD27, CD28, CD30, CD3D, CD3E, CD3G, CD3Z, CD45, CD45RA, CD45RO, CD52, CD6, CD62L, CD8, CD8A, CD8B, CTLA4, DAPL1, FOXP3, GNLY, GZMB, IL2RA, IL32, IL7R, LCK, LTB, S100A4, SELL, SHISA5, THY1, TRAC, TRBC1, TRBC2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCR7,SELL,CD4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCR6, CCR7, CD11B, CD127, CD2, CD25, CD27, CD28, CD30, CD3D, CD3E, CD3G, CD3Z, CD4, CD45, CD45RA, CD45RO, CD52, CD6, CD62L, CTLA4, DAPL1, FOXP3, GZMB, IL2RA, IL32, IL7R, LCK, LTB, S100A4, SELL, SHISA5, THY1, TRAC, TRBC1, TRBC2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCR7,SELL,CD8A,CD8B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCR6, CCR7, CD11B, CD127, CD2, CD25, CD27, CD30, CD3D, CD3E, CD3G, CD3Z, CD45, CD45RA, CD52, CD6, CD62L, CD8, CD8A, CD8B, CTLA4, DAPL1, FAS, FOXP3, GNLY, GZMB, GZMK, IFNG, IL2RA, JUN, JUNB, JUND, LCK, LTB, NKG7, PTPRC, SHISA5, THY1, TRAC, TRBC1, TRBC2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SELL,CCR7,CD27,CD4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCR6, CCR7, CD11B, CD127, CD2, CD25, CD27, CD30, CD3D, CD3E, CD3G, CD3Z, CD4, CD45, CD45RA, CD52, CD6, CD62L, CTLA4, DAPL1, FAS, FOS, FOXP3, GNLY, GZMB, GZMK, IFNG, IL2RA, JUN, JUNB, JUND, LCK, LTB, NKG7, PTPRC, SHISA5, THY1, TRAC, TRBC1, TRBC2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SELL,CCR7,CD27,CD8A,CD8B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCR6, CCR7, CD11B, CD127, CD2, CD25, CD27, CD30, CD3D, CD3E, CD3G, CD3Z, CD45, CD45RA, CD52, CD6, CD62L, CTLA4, DAPL1, FOXP3, GZMB, IL2RA, LCK, LTB, PLZF, PTPRC, RORC, SHISA5, THY1, TRAC, TRBC2, TRDC, TRDV1, TRDV2, TRGC1, TRGC2, TRGV9, ZBTB16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SELL,CCR7,CD4,CD8A,CD8B,TRAC,TRBC1,TRBC2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CD11B, CD122, CD16, CD161, CD2, CD314, CD3D, CD3E, CD3G, CD3Z, CD56, CD69, CD8, CD8A, CD94, COX6A2, GNLY, GZMA, GZMB, GZMM, KIR2DL4, NCAM1, NKG2D, NKG7, NKP46, PTPRC, ZMAT4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCR7,CD27,CD4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CD11B, CD122, CD16, CD161, CD2, CD314, CD3D, CD3E, CD3G, CD3Z, CD4, CD56, CD69, CD94, COX6A2, GNLY, GZMA, GZMB, GZMM, KIR2DL4, NCAM1, NKG2D, NKG7, NKP46, PTPRC, ZMAT4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCR7,CD27,CD8A,CD8B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Natural killer cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CD11B, CD122, CD16, CD161, CD2, CD314, CD56, CD69, CD94, COX6A2, FCGR3A, GNLY, GZMA, GZMB, GZMM, KIR2DL4, KLRD1, KLRF1, NKG2D, NKG7, NKP46, ZMAT4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CD3D,CD3E,CD3G,CD3Z,CD4,CD8,TRAC,TRBC1,TRBC2,TRBC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Proliferating CD8+ T cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CD3D, CD3E, CD3G, CD8A, CD8B, MCM6, MKI67, PCNA, PTPRC, TOP2A, TRAC, TRBC1, TRBC2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CD4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prolif CD8+ T</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Proliferating CD4+ T cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CD3D, CD3E, CD3G, CD4, MCM6, MKI67, PCNA, PTPRC, TOP2A, TRAC, TRBC1, TRBC2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CD8A,CD8B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prolif CD4+ T</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exhausted CD8+ T cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CD8A, CD8B, ENTPD1, HAVCR2, LAG3, LAYN, PDCD1, PTPRC, TIGIT, TOX, TRAC, TRBC1, TRBC2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exh CD8+ T</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exhausted CD4+ T cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BTLA, CD4, CTLA4, HAVCR2, PDCD1, PTPRC, TIGIT, TOX, TRAC, TRBC1, TRBC2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exh CD4+ T</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Th17-proInfl T cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCR6, CD3D, CD3E, CD3G, CD4, IL17A, PDCD1, PTPRC, RORC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCR7,CD8A,CD8B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Th17_proInfl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regulatory CD8+ T cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CD8A, CD8B, CTLA4, MAF, PDCD1, PRDM1, PTPRC, TIGIT, TRAC, TRBC1, TRBC2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CD4,GZMB,PRF1,GNLY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CD8+ Treg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regulatory CD4+ T cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCR4, CD4, CTLA4, ICOS, IL2RA, PDCD1, PTPRC, TIGIT, TRAC, TRBC1, TRBC2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CD8A,CD8B,GZMB,PRF1,GNLY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CD4+ Treg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tabla 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">γδ-T cells</t>
   </si>
 </sst>
 </file>
@@ -1838,7 +1840,7 @@
     <numFmt numFmtId="165" formatCode="@"/>
     <numFmt numFmtId="166" formatCode="0"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -1863,44 +1865,6 @@
     <font>
       <sz val="11"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="15"/>
-      <name val="Calibri"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Calibri"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="12"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Times New Roman"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
@@ -2051,7 +2015,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="30">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2172,38 +2136,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5908,7 +5840,7 @@
         <v>554</v>
       </c>
       <c r="E255" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="256" customFormat="false" ht="13.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5925,7 +5857,7 @@
         <v>556</v>
       </c>
       <c r="E256" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="257" customFormat="false" ht="13.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6257,7 +6189,7 @@
         <v>96</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>97</v>
+        <v>600</v>
       </c>
       <c r="D276" s="3"/>
       <c r="E276" s="2" t="s">
@@ -6287,7 +6219,7 @@
         <v>59</v>
       </c>
       <c r="C278" s="19" t="s">
-        <v>60</v>
+        <v>601</v>
       </c>
       <c r="D278" s="3"/>
       <c r="E278" s="20" t="s">
@@ -6347,7 +6279,7 @@
         <v>89</v>
       </c>
       <c r="C282" s="22" t="s">
-        <v>90</v>
+        <v>602</v>
       </c>
       <c r="D282" s="22" t="s">
         <v>91</v>
@@ -6461,6 +6393,1666 @@
         <v>120</v>
       </c>
     </row>
+    <row r="1046916" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046917" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046918" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046919" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046920" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046921" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046922" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046923" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046924" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046925" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046926" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046927" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046928" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046929" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046930" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046931" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046932" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046933" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046934" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046935" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046936" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046937" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046938" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046939" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046940" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046941" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046942" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046943" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046944" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046945" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046946" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046947" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046948" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046949" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046950" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046951" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046952" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046953" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046954" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046955" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046956" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046957" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046958" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046959" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046960" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046961" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046962" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046963" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046964" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046965" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046966" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046967" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046968" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046969" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046970" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046971" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046972" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046973" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046974" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046975" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046976" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046977" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046978" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046979" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046980" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046981" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046982" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046983" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046984" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046985" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046986" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046987" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046988" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046989" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046990" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046991" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046992" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046993" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046994" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046995" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046996" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046997" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046998" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1046999" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047000" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047001" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047002" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047003" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047004" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047005" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047006" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047007" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047008" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047009" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047010" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047011" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047012" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047013" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047014" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047015" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047016" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047017" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047018" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047019" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047020" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047021" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047022" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047023" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047024" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047025" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047026" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047027" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047028" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047029" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047030" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047031" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047032" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047033" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047034" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047035" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047036" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047037" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047038" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047039" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047040" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047041" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047042" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047043" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047044" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047045" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047046" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047047" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047048" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047049" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047050" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047051" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047052" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047053" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047054" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047055" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047056" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047057" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047058" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047059" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047060" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047061" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047062" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047063" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047064" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047065" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047066" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047067" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047068" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047069" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047070" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047071" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047072" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047073" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047074" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047075" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047076" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047077" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047078" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047079" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047080" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047081" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047082" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047083" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047084" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047085" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047086" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047087" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047088" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047089" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047090" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047091" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047092" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047093" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047094" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047095" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047096" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047097" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047098" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047099" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047165" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047166" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047167" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047168" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047169" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047170" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047171" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047172" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047173" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047174" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047175" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047176" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047177" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047178" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047179" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047180" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047181" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047182" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047183" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047184" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047185" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047186" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047187" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047188" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047189" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047190" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047191" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047192" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047193" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047194" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047195" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047196" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047197" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047198" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047199" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047200" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047201" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047202" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047203" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047204" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047205" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047206" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047207" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047208" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047209" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047210" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047211" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047212" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047213" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047214" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047215" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047216" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047217" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047218" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047219" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047220" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047221" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047222" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047223" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047224" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047225" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047226" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047227" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047228" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047229" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047230" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047231" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047232" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047233" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047234" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047235" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047236" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047237" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047238" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047239" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047240" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047241" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047242" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047243" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047244" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047245" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047246" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047247" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047248" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047249" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047250" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047251" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047252" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047253" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047254" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047255" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047256" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047257" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047258" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047259" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047260" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047261" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047262" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047263" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047264" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047265" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047266" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047267" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047268" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047269" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047270" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047271" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047272" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047273" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047274" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047275" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047276" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047277" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047278" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047279" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047280" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047281" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047282" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047283" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047284" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047285" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047286" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047287" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047288" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047289" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047290" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047291" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047292" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047293" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047294" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047295" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047296" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047297" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047298" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047299" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047300" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047301" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047302" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047303" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047304" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047305" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047306" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047307" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047308" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047309" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047310" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047311" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047312" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047313" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047314" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047315" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047316" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047317" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047318" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047319" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047320" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047321" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047322" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047323" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047324" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047325" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047326" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047327" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047328" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047329" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047330" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047331" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047332" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047333" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047334" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047335" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047336" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047337" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047338" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047339" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047340" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047341" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047342" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047343" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047344" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047345" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047346" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047347" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047348" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047349" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047350" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047351" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047352" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047353" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047354" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047355" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047356" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047357" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047358" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047359" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047360" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047361" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047362" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047363" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047364" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047365" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047366" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047367" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047368" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047369" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047370" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047371" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047372" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047373" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047374" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047375" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047376" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047377" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047378" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047379" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047380" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047381" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047382" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047383" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047384" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047385" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047386" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047387" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047388" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047389" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047390" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047391" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047392" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047393" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047394" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047395" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047396" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047397" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047398" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047399" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047400" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047401" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047402" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047403" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047404" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047405" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047406" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047407" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047408" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047409" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047410" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047411" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047412" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047413" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047414" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047415" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047416" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047417" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047418" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047419" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047420" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047421" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047422" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047423" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047424" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047425" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047426" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047427" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047428" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047429" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047430" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047431" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047432" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047433" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047434" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047435" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047436" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047437" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047438" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047439" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047440" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047441" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047442" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047443" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047444" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047445" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047446" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047447" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047448" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047449" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047450" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047451" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047452" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047453" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047454" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047455" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047456" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047457" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047458" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047459" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047460" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047461" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047462" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047463" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047464" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047465" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047466" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047467" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047468" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047469" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047470" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047471" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047472" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047473" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047474" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047475" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047476" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047477" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047478" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047479" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047480" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047481" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047482" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047483" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047484" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047485" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047486" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047487" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047488" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047489" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047490" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047491" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047492" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047493" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047494" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047495" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047496" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047497" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047498" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047499" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047500" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047501" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047502" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047503" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047504" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047505" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047506" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047507" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047508" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047509" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047510" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047511" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047512" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047513" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047514" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047515" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047516" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047517" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047518" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047519" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047520" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047521" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047522" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047523" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047524" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047525" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047526" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047527" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047528" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047529" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047530" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047531" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047532" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047533" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047534" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047535" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047536" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047537" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047538" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047539" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047540" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047541" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047542" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047543" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047544" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047545" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047546" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047547" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047548" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047549" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047550" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047551" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047552" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047553" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047554" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047555" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047556" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047557" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047558" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047559" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047560" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047561" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047562" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047563" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047564" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047565" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047566" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047567" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047577" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047578" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047579" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047580" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047581" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047582" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047583" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047584" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047585" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047586" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047587" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047588" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047589" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047590" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047591" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047592" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047593" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047594" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047595" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047596" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047597" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047598" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047599" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047600" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047601" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047602" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047603" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047604" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047605" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047606" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047607" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047608" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047609" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047610" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047611" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047612" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047613" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047614" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047615" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047616" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047617" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047618" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047619" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047620" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047621" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047622" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047623" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047624" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047625" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047626" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047627" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047628" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047629" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047630" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047631" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047632" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047633" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047634" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047635" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047636" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047637" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047638" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047639" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047640" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047641" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047642" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047643" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047644" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047645" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047646" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047647" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047648" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047649" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047650" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047651" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047652" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047653" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047654" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047655" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047656" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047657" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047658" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047659" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047660" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047661" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047662" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047663" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047664" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047665" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047666" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047667" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047668" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047669" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047670" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047671" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047672" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047673" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047674" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047675" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047676" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047677" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047678" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047679" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047680" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047681" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047682" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047683" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047684" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047685" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047686" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047687" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047688" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047689" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047690" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047691" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047692" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047693" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047694" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047695" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047696" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047697" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047698" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047699" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047700" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047701" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047702" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047703" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047704" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047705" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047706" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047707" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047708" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047709" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047710" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047711" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047712" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047713" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047714" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047715" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047716" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047717" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047718" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047719" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047720" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047721" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047722" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047723" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047724" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047725" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047726" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047727" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047728" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047729" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047730" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047731" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047732" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047733" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047734" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047735" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047736" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047737" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047738" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047739" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047740" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047741" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047742" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047743" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047744" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047745" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047746" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047747" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047748" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047749" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047750" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047751" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047752" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047753" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047754" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047755" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047756" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047757" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047758" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047759" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047760" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047761" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047762" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047763" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047764" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047765" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047766" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047767" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047768" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047769" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047770" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047771" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047772" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047773" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047774" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047775" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047776" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047777" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047778" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047779" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047780" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047781" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047782" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047783" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047784" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047785" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047786" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047787" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047788" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047789" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047790" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047791" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047792" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047793" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047794" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047795" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047796" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047797" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047798" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047799" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047800" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047801" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047802" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047803" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047804" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047805" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047806" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047807" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047808" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047809" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047810" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047811" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047812" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047813" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047814" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047815" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047816" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047817" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047818" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047819" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047820" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047821" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047822" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047823" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047824" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047825" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047826" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047827" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047828" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047829" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047830" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047831" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047832" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047833" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047834" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047835" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047836" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047837" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047838" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047839" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047840" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047841" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047842" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047843" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047844" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047845" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047846" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047847" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047848" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047849" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047850" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047851" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047852" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047853" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047854" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047855" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047856" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047857" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047858" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047859" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047860" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047861" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047862" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047863" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047864" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047865" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047866" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047867" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047868" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047869" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047870" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047871" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047872" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047873" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047874" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047875" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047876" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047877" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047878" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047879" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047880" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047881" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047882" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047883" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047884" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047885" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047886" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047887" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047888" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047889" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047890" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047891" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047892" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047893" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047894" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047895" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047896" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047897" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047898" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047899" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047900" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047901" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047902" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047903" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047904" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047905" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047906" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047907" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047908" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047909" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047910" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047911" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047912" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047913" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047914" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047915" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047916" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047917" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047918" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047919" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047920" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047921" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047922" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047923" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047924" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047925" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047926" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047927" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047928" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047929" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047930" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047931" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047932" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047933" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047934" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047935" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047936" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047937" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047938" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047939" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047940" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047941" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047942" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047943" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047944" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047945" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047946" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047947" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047948" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047949" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047950" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047951" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047952" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047953" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047954" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047955" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047956" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047957" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047958" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047959" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047960" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047961" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047962" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047963" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047964" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047965" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047966" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047967" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047968" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047969" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047970" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047971" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047972" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047973" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047974" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047975" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047976" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047977" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047978" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047979" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047980" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047981" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047982" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047983" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047984" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047985" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047986" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047987" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047988" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047989" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047990" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047991" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047992" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047993" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047994" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047995" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047996" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047997" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047998" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047999" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048000" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048001" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048002" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048003" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048004" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048005" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048006" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048007" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048008" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048009" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048010" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048011" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048012" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048013" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048014" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048015" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048016" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048017" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048018" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048019" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048020" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048021" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048022" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048023" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048024" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048025" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048026" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048027" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048028" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048029" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048030" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048031" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048032" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048033" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048034" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048035" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048036" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048037" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048038" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048039" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048040" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048041" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048042" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048043" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048044" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048045" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048046" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048047" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048048" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048049" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048050" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048051" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048052" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048053" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048054" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048055" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048056" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048057" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048058" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048059" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048060" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048061" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048062" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048063" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048064" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048065" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048066" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048067" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048068" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048069" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048070" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048071" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048072" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048073" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048074" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048075" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048076" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048077" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048078" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048079" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048080" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048081" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048082" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048083" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048084" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048085" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048086" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048087" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048088" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048089" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048090" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048091" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048092" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048093" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048094" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048095" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048096" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048097" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048098" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048099" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048165" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048166" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048167" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048168" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048169" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048170" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048171" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048172" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048173" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048174" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048175" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048176" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048177" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048178" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048179" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048180" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048181" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048182" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048183" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048184" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048185" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048186" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048187" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048188" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048189" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048190" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048191" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048192" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048193" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048194" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048195" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048196" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048197" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048198" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048199" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048200" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048201" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048202" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048203" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048204" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048205" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048206" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048207" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048208" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048209" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048210" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048211" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048212" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048213" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048214" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048215" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048216" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048217" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048218" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048219" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048220" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048221" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048222" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048223" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048224" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048225" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048226" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048227" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048228" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048229" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048230" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048231" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048232" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048233" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048234" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048235" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048236" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048237" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048238" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048239" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048240" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048241" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048242" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048243" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048244" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048245" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048246" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048247" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048248" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048249" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048250" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048251" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048252" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048253" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048254" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048255" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048256" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048257" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048258" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048259" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048260" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048261" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048262" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048263" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048264" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048265" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048266" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048267" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048268" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048269" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048270" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048271" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048272" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048273" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048274" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048275" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048276" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048277" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048278" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048279" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048280" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048281" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048282" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048283" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048284" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048285" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048286" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048287" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048288" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048289" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048290" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048291" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048292" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048293" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048294" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048295" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048296" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048297" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048298" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048299" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048300" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048301" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048302" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048303" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048304" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048305" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048306" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048307" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048308" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048309" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048310" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048311" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048312" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048313" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048314" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048315" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048316" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048317" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048318" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048319" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048320" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048321" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048322" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048323" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048324" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048325" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048326" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048327" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048328" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048329" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048330" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048331" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048332" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048333" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048334" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048335" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048336" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048337" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048338" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048339" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048340" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048341" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048342" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048343" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048344" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048345" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048346" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048347" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048348" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048349" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048350" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048351" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048352" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048353" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048354" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048355" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048356" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048357" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048358" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048359" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048360" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048361" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048362" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048363" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048364" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048365" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048366" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048367" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048368" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048369" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048370" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048371" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048372" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048373" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048374" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048375" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048376" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048377" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048378" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048379" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048380" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048381" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048382" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048383" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048384" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048385" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048386" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048387" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048388" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048389" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048390" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048391" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048392" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048393" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048394" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048395" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048396" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048397" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048398" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048399" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048400" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048401" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048402" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048403" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048404" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048405" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048406" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048407" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048408" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048409" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048410" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048411" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048412" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048413" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048414" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048415" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048416" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048417" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048418" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048419" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048420" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048421" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048422" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048423" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048424" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048425" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048426" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048427" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048428" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048429" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048430" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048431" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048432" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048433" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048434" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048435" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048436" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048437" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048438" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048439" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048440" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048441" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048442" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048443" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048444" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048445" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048446" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048447" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048448" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048449" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048450" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048451" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048452" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048453" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048454" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048455" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048456" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048457" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048458" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048459" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048460" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048461" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048462" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048463" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048464" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048465" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048466" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048467" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048468" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048469" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048470" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048471" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048472" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048473" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048474" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048475" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048476" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048477" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048478" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048479" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048480" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048481" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048482" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048483" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048484" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048485" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048486" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048487" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048488" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048489" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048490" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048491" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048492" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048493" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048494" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048495" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048496" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048497" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048498" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048499" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048500" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048501" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048502" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048503" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048504" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048505" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048506" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048507" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048508" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048509" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048510" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048511" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048512" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048513" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048514" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048515" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048516" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048517" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048518" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048519" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048520" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048521" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048522" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048523" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048524" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048525" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048526" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048527" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048528" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048529" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048530" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048531" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048532" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048533" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048534" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048535" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048536" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048537" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048538" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048539" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048540" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048541" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048542" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048543" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048544" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048545" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048546" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048547" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048548" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048549" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048550" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048551" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048552" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048553" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048554" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048555" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048556" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048557" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048558" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048559" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048560" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048561" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048562" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048563" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048564" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048565" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048566" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048567" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -6471,357 +8063,4 @@
     <oddFooter>&amp;C&amp;"Helvetica Neue,Normal"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="true"/>
-  </sheetPr>
-  <dimension ref="A1:F19"/>
-  <sheetFormatPr defaultColWidth="16.3515625" defaultRowHeight="15.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.35"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="25.17"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16.35"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="40.17"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="5" style="1" width="16.35"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="15.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="30" t="s">
-        <v>600</v>
-      </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-    </row>
-    <row r="2" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="31" t="s">
-        <v>542</v>
-      </c>
-      <c r="B2" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" s="33" t="s">
-        <v>553</v>
-      </c>
-      <c r="D2" s="31" t="s">
-        <v>554</v>
-      </c>
-      <c r="E2" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="F2" s="31"/>
-    </row>
-    <row r="3" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="31" t="s">
-        <v>542</v>
-      </c>
-      <c r="B3" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" s="33" t="s">
-        <v>555</v>
-      </c>
-      <c r="D3" s="31" t="s">
-        <v>556</v>
-      </c>
-      <c r="E3" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" s="31"/>
-    </row>
-    <row r="4" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="31" t="s">
-        <v>542</v>
-      </c>
-      <c r="B4" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" s="33" t="s">
-        <v>557</v>
-      </c>
-      <c r="D4" s="31" t="s">
-        <v>558</v>
-      </c>
-      <c r="E4" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="F4" s="31"/>
-    </row>
-    <row r="5" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="31" t="s">
-        <v>542</v>
-      </c>
-      <c r="B5" s="32" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" s="33" t="s">
-        <v>559</v>
-      </c>
-      <c r="D5" s="31" t="s">
-        <v>560</v>
-      </c>
-      <c r="E5" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="F5" s="31"/>
-    </row>
-    <row r="6" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="31" t="s">
-        <v>542</v>
-      </c>
-      <c r="B6" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="C6" s="33" t="s">
-        <v>561</v>
-      </c>
-      <c r="D6" s="31" t="s">
-        <v>562</v>
-      </c>
-      <c r="E6" s="31" t="s">
-        <v>38</v>
-      </c>
-      <c r="F6" s="31"/>
-    </row>
-    <row r="7" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="31" t="s">
-        <v>542</v>
-      </c>
-      <c r="B7" s="32" t="s">
-        <v>39</v>
-      </c>
-      <c r="C7" s="33" t="s">
-        <v>563</v>
-      </c>
-      <c r="D7" s="31" t="s">
-        <v>564</v>
-      </c>
-      <c r="E7" s="31" t="s">
-        <v>41</v>
-      </c>
-      <c r="F7" s="31"/>
-    </row>
-    <row r="8" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="31" t="s">
-        <v>542</v>
-      </c>
-      <c r="B8" s="32" t="s">
-        <v>601</v>
-      </c>
-      <c r="C8" s="33" t="s">
-        <v>565</v>
-      </c>
-      <c r="D8" s="31" t="s">
-        <v>566</v>
-      </c>
-      <c r="E8" s="31" t="s">
-        <v>44</v>
-      </c>
-      <c r="F8" s="31"/>
-    </row>
-    <row r="9" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="31" t="s">
-        <v>542</v>
-      </c>
-      <c r="B9" s="32" t="s">
-        <v>47</v>
-      </c>
-      <c r="C9" s="33" t="s">
-        <v>567</v>
-      </c>
-      <c r="D9" s="31" t="s">
-        <v>568</v>
-      </c>
-      <c r="E9" s="31" t="s">
-        <v>49</v>
-      </c>
-      <c r="F9" s="31"/>
-    </row>
-    <row r="10" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="31" t="s">
-        <v>542</v>
-      </c>
-      <c r="B10" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="C10" s="33" t="s">
-        <v>569</v>
-      </c>
-      <c r="D10" s="31" t="s">
-        <v>570</v>
-      </c>
-      <c r="E10" s="31" t="s">
-        <v>52</v>
-      </c>
-      <c r="F10" s="31"/>
-    </row>
-    <row r="11" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="31" t="s">
-        <v>542</v>
-      </c>
-      <c r="B11" s="32" t="s">
-        <v>571</v>
-      </c>
-      <c r="C11" s="33" t="s">
-        <v>572</v>
-      </c>
-      <c r="D11" s="31" t="s">
-        <v>573</v>
-      </c>
-      <c r="E11" s="31" t="s">
-        <v>56</v>
-      </c>
-      <c r="F11" s="31"/>
-    </row>
-    <row r="12" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="31" t="s">
-        <v>542</v>
-      </c>
-      <c r="B12" s="32" t="s">
-        <v>574</v>
-      </c>
-      <c r="C12" s="33" t="s">
-        <v>575</v>
-      </c>
-      <c r="D12" s="31" t="s">
-        <v>576</v>
-      </c>
-      <c r="E12" s="31" t="s">
-        <v>577</v>
-      </c>
-      <c r="F12" s="31"/>
-    </row>
-    <row r="13" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="31" t="s">
-        <v>542</v>
-      </c>
-      <c r="B13" s="32" t="s">
-        <v>578</v>
-      </c>
-      <c r="C13" s="33" t="s">
-        <v>579</v>
-      </c>
-      <c r="D13" s="31" t="s">
-        <v>580</v>
-      </c>
-      <c r="E13" s="31" t="s">
-        <v>581</v>
-      </c>
-      <c r="F13" s="31"/>
-    </row>
-    <row r="14" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="31" t="s">
-        <v>542</v>
-      </c>
-      <c r="B14" s="32" t="s">
-        <v>582</v>
-      </c>
-      <c r="C14" s="33" t="s">
-        <v>583</v>
-      </c>
-      <c r="D14" s="31" t="s">
-        <v>576</v>
-      </c>
-      <c r="E14" s="31" t="s">
-        <v>584</v>
-      </c>
-      <c r="F14" s="34"/>
-    </row>
-    <row r="15" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="31" t="s">
-        <v>542</v>
-      </c>
-      <c r="B15" s="32" t="s">
-        <v>585</v>
-      </c>
-      <c r="C15" s="33" t="s">
-        <v>586</v>
-      </c>
-      <c r="D15" s="31" t="s">
-        <v>580</v>
-      </c>
-      <c r="E15" s="31" t="s">
-        <v>587</v>
-      </c>
-      <c r="F15" s="34"/>
-    </row>
-    <row r="16" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="31" t="s">
-        <v>542</v>
-      </c>
-      <c r="B16" s="32" t="s">
-        <v>588</v>
-      </c>
-      <c r="C16" s="33" t="s">
-        <v>589</v>
-      </c>
-      <c r="D16" s="31" t="s">
-        <v>590</v>
-      </c>
-      <c r="E16" s="31" t="s">
-        <v>591</v>
-      </c>
-      <c r="F16" s="31"/>
-    </row>
-    <row r="17" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="31" t="s">
-        <v>542</v>
-      </c>
-      <c r="B17" s="32" t="s">
-        <v>592</v>
-      </c>
-      <c r="C17" s="35" t="s">
-        <v>593</v>
-      </c>
-      <c r="D17" s="31" t="s">
-        <v>594</v>
-      </c>
-      <c r="E17" s="31" t="s">
-        <v>595</v>
-      </c>
-      <c r="F17" s="31"/>
-    </row>
-    <row r="18" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="31" t="s">
-        <v>542</v>
-      </c>
-      <c r="B18" s="32" t="s">
-        <v>596</v>
-      </c>
-      <c r="C18" s="33" t="s">
-        <v>597</v>
-      </c>
-      <c r="D18" s="34" t="s">
-        <v>598</v>
-      </c>
-      <c r="E18" s="34" t="s">
-        <v>599</v>
-      </c>
-      <c r="F18" s="31"/>
-    </row>
-    <row r="19" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="36"/>
-      <c r="B19" s="37"/>
-      <c r="C19" s="33"/>
-      <c r="D19" s="37"/>
-      <c r="E19" s="37"/>
-      <c r="F19" s="31"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="1" right="1" top="1" bottom="1" header="0.511811023622047" footer="0.25"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;"Helvetica Neue,Normal"&amp;12&amp;K000000&amp;P</oddFooter>
-  </headerFooter>
-</worksheet>
 </file>
--- a/ref/scTypeDB.xlsx
+++ b/ref/scTypeDB.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1103" uniqueCount="603">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1098" uniqueCount="599">
   <si>
     <t xml:space="preserve">tissueType</t>
   </si>
@@ -1681,55 +1681,55 @@
     <t xml:space="preserve">CD20,MS4A1,TRAC,TRBC1,TRBC2,CD19</t>
   </si>
   <si>
-    <t xml:space="preserve">CCR6, CCR7, CD11B, CD127, CD2, CD27, CD30, CD3D, CD3E, CD3G, CD3Z, CD45, CD45RA, CD52, CD6, CD62L, CD8, CD8A, CD8B, CTLA4, DAPL1, FOXO1, FOXP1, FOXP3, GNLY, IL2RA, IL7R, KLF2, LCK, LEF1, LTB, PTPRC, SELL, SHISA5, TCF7, THY1, TRAC, TRBC1, TRBC2</t>
+    <t xml:space="preserve">TRAC,TRBC1,TRBC2,CCR6, CCR7, CD11B, CD127, CD2, CD27, CD30, CD3D, CD3E, CD3G, CD3Z, CD45, CD45RA, CD52, CD6, CD62L, CD8, CD8A, CD8B, CTLA4, DAPL1, FOXO1, FOXP1, FOXP3, GNLY, IL2RA, IL7R, KLF2, LCK, LEF1, LTB, PTPRC, SELL, SHISA5, TCF7, THY1, TRAC, TRBC1, TRBC2</t>
   </si>
   <si>
     <t xml:space="preserve">GZMB,CD56,NCAM1,CD4</t>
   </si>
   <si>
-    <t xml:space="preserve">ACTN1, CCR6, CCR7, CD11B, CD127, CD2, CD27, CD30, CD3D, CD3E, CD3G, CD3Z, CD4, CD45, CD45RA, CD52, CD6, CD62L, CTLA4, DAPL1, FOXP3, IL2RA, IL7R, KLF2, LCK, LEF1, LTB, PTPRC, SELL, SHISA5, TCF7, THY1, TRAC, TRBC1, TRBC2</t>
+    <t xml:space="preserve">TRAC,TRBC1,TRBC2,ACTN1, CCR6, CCR7, CD11B, CD127, CD2, CD27, CD30, CD3D, CD3E, CD3G, CD3Z, CD4, CD45, CD45RA, CD52, CD6, CD62L, CTLA4, DAPL1, FOXP3, IL2RA, IL7R, KLF2, LCK, LEF1, LTB, PTPRC, SELL, SHISA5, TCF7, THY1, TRAC, TRBC1, TRBC2</t>
   </si>
   <si>
     <t xml:space="preserve">GZMB,CD56,NCAM1,CD8A,CD8B</t>
   </si>
   <si>
-    <t xml:space="preserve">CCR6, CCR7, CD11B, CD127, CD2, CD25, CD27, CD28, CD30, CD3D, CD3E, CD3G, CD3Z, CD45, CD45RA, CD45RO, CD52, CD6, CD62L, CD8, CD8A, CD8B, CTLA4, DAPL1, FOXP3, GNLY, GZMB, IL2RA, IL32, IL7R, LCK, LTB, S100A4, SELL, SHISA5, THY1, TRAC, TRBC1, TRBC2</t>
+    <t xml:space="preserve">TRAC,TRBC1,TRBC2,CCR6, CD11B, CD127, CD2, CD25, CD27, CD28, CD30, CD3D, CD3E, CD3G, CD3Z, CD45, CD45RA, CD45RO, CD52, CD6, CD62L, CD8, CD8A, CD8B, CTLA4, DAPL1, FOXP3, GNLY, GZMB, IL2RA, IL32, IL7R, LCK, LTB, S100A4, SELL, SHISA5, THY1, TRAC, TRBC1, TRBC2</t>
   </si>
   <si>
     <t xml:space="preserve">CCR7,SELL,CD4</t>
   </si>
   <si>
-    <t xml:space="preserve">CCR6, CCR7, CD11B, CD127, CD2, CD25, CD27, CD28, CD30, CD3D, CD3E, CD3G, CD3Z, CD4, CD45, CD45RA, CD45RO, CD52, CD6, CD62L, CTLA4, DAPL1, FOXP3, GZMB, IL2RA, IL32, IL7R, LCK, LTB, S100A4, SELL, SHISA5, THY1, TRAC, TRBC1, TRBC2</t>
+    <t xml:space="preserve">TRAC,TRBC1,TRBC2,CCR6, CD11B, CD127, CD2, CD25, CD27, CD28, CD30, CD3D, CD3E, CD3G, CD3Z, CD4, CD45, CD45RA, CD45RO, CD52, CD6, CD62L, CTLA4, DAPL1, FOXP3, GZMB, IL2RA, IL32, IL7R, LCK, LTB, S100A4, SELL, SHISA5, THY1, TRAC, TRBC1, TRBC2</t>
   </si>
   <si>
     <t xml:space="preserve">CCR7,SELL,CD8A,CD8B</t>
   </si>
   <si>
-    <t xml:space="preserve">CCR6, CCR7, CD11B, CD127, CD2, CD25, CD27, CD30, CD3D, CD3E, CD3G, CD3Z, CD45, CD45RA, CD52, CD6, CD62L, CD8, CD8A, CD8B, CTLA4, DAPL1, FAS, FOXP3, GNLY, GZMB, GZMK, IFNG, IL2RA, JUN, JUNB, JUND, LCK, LTB, NKG7, PTPRC, SHISA5, THY1, TRAC, TRBC1, TRBC2</t>
+    <t xml:space="preserve">TRAC,TRBC1,TRBC2,CCR6, CD11B, CD127, CD2, CD25, CD27, CD30, CD3D, CD3E, CD3G, CD3Z, CD45, CD45RA, CD52, CD6, CD62L, CD8, CD8A, CD8B, CTLA4, DAPL1, FAS, FOXP3, GNLY, GZMB, GZMK, IFNG, IL2RA, JUN, JUNB, JUND, LCK, LTB, NKG7, PTPRC, SHISA5, THY1, TRAC, TRBC1, TRBC2</t>
   </si>
   <si>
     <t xml:space="preserve">SELL,CCR7,CD27,CD4</t>
   </si>
   <si>
-    <t xml:space="preserve">CCR6, CCR7, CD11B, CD127, CD2, CD25, CD27, CD30, CD3D, CD3E, CD3G, CD3Z, CD4, CD45, CD45RA, CD52, CD6, CD62L, CTLA4, DAPL1, FAS, FOS, FOXP3, GNLY, GZMB, GZMK, IFNG, IL2RA, JUN, JUNB, JUND, LCK, LTB, NKG7, PTPRC, SHISA5, THY1, TRAC, TRBC1, TRBC2</t>
+    <t xml:space="preserve">TRAC,TRBC1,TRBC2,CCR6, CD11B, CD127, CD2, CD25, CD27, CD30, CD3D, CD3E, CD3G, CD3Z, CD4, CD45, CD45RA, CD52, CD6, CD62L, CTLA4, DAPL1, FAS, FOS, FOXP3, GNLY, GZMB, GZMK, IFNG, IL2RA, JUN, JUNB, JUND, LCK, LTB, NKG7, PTPRC, SHISA5, THY1, TRAC, TRBC1, TRBC2</t>
   </si>
   <si>
     <t xml:space="preserve">SELL,CCR7,CD27,CD8A,CD8B</t>
   </si>
   <si>
-    <t xml:space="preserve">CCR6, CCR7, CD11B, CD127, CD2, CD25, CD27, CD30, CD3D, CD3E, CD3G, CD3Z, CD45, CD45RA, CD52, CD6, CD62L, CTLA4, DAPL1, FOXP3, GZMB, IL2RA, LCK, LTB, PLZF, PTPRC, RORC, SHISA5, THY1, TRDC, TRDV1, TRDV2, TRGC1, TRGC2, TRGV9, ZBTB16</t>
+    <t xml:space="preserve">CCR6, CD11B, CD127, CD2, CD25, CD27, CD30, CD3D, CD3E, CD3G, CD3Z, CD45, CD45RA, CD52, CD6, CD62L, CTLA4, DAPL1, FOXP3, GZMB, IL2RA, LCK, LTB, PLZF, PTPRC, RORC, SHISA5, THY1, TRDC, TRDV1, TRDV2, TRGC1, TRGC2, TRGV9, ZBTB16</t>
   </si>
   <si>
     <t xml:space="preserve">SELL,CCR7,CD4,CD8A,CD8B,TRAC,TRBC1,TRBC2</t>
   </si>
   <si>
-    <t xml:space="preserve">CD11B, CD122, CD16, CD161, CD2, CD314, CD3D, CD3E, CD3G, CD3Z, CD56, CD69, CD8, CD8A, CD94, COX6A2, GNLY, GZMA, GZMB, GZMM, KIR2DL4, NCAM1, NKG2D, NKG7, NKP46, PTPRC, ZMAT4</t>
+    <t xml:space="preserve">TRAC,TRBC1,TRBC2,CD11B, CD122, CD16, CD161, CD2, CD314, CD3D, CD3E, CD3G, CD3Z, CD56, CD69, CD8, CD8A, CD94, COX6A2, GNLY, GZMA, GZMB, GZMM, KIR2DL4, NCAM1, NKG2D, NKG7, NKP46, PTPRC, ZMAT4</t>
   </si>
   <si>
     <t xml:space="preserve">CCR7,CD27,CD4</t>
   </si>
   <si>
-    <t xml:space="preserve">CD11B, CD122, CD16, CD161, CD2, CD314, CD3D, CD3E, CD3G, CD3Z, CD4, CD56, CD69, CD94, COX6A2, GNLY, GZMA, GZMB, GZMM, KIR2DL4, NCAM1, NKG2D, NKG7, NKP46, PTPRC, ZMAT4</t>
+    <t xml:space="preserve">TRAC,TRBC1,TRBC2,CD11B, CD122, CD16, CD161, CD2, CD314, CD3D, CD3E, CD3G, CD3Z, CD4, CD56, CD69, CD94, COX6A2, GNLY, GZMA, GZMB, GZMM, KIR2DL4, NCAM1, NKG2D, NKG7, NKP46, PTPRC, ZMAT4</t>
   </si>
   <si>
     <t xml:space="preserve">CCR7,CD27,CD8A,CD8B</t>
@@ -1738,7 +1738,7 @@
     <t xml:space="preserve">Natural killer cells</t>
   </si>
   <si>
-    <t xml:space="preserve">CD11B, CD122, CD16, CD161, CD2, CD314, CD56, CD69, CD94, COX6A2, FCGR3A, GNLY, GZMA, GZMB, GZMM, KIR2DL4, KLRD1, KLRF1, NKG2D, NKG7, NKP46, ZMAT4</t>
+    <t xml:space="preserve">TRAC,TRBC1,TRBC2,CD11B, CD122, CD16, CD161, CD2, CD314, CD56, CD69, CD94, COX6A2, FCGR3A, GNLY, GZMA, GZMB, GZMM, KIR2DL4, KLRD1, KLRF1, NKG2D, NKG7, NKP46, ZMAT4</t>
   </si>
   <si>
     <t xml:space="preserve">CD3D,CD3E,CD3G,CD3Z,CD4,CD8,TRAC,TRBC1,TRBC2,TRBC</t>
@@ -1747,7 +1747,7 @@
     <t xml:space="preserve">Proliferating CD8+ T cells</t>
   </si>
   <si>
-    <t xml:space="preserve">CD3D, CD3E, CD3G, CD8A, CD8B, MCM6, MKI67, PCNA, PTPRC, TOP2A, TRAC, TRBC1, TRBC2</t>
+    <t xml:space="preserve">TRAC,TRBC1,TRBC2,CD3D, CD3E, CD3G, CD8A, CD8B, MCM6, MKI67, PCNA, PTPRC, TOP2A, TRAC, TRBC1, TRBC2</t>
   </si>
   <si>
     <t xml:space="preserve">CD4</t>
@@ -1759,7 +1759,7 @@
     <t xml:space="preserve">Proliferating CD4+ T cells</t>
   </si>
   <si>
-    <t xml:space="preserve">CD3D, CD3E, CD3G, CD4, MCM6, MKI67, PCNA, PTPRC, TOP2A, TRAC, TRBC1, TRBC2</t>
+    <t xml:space="preserve">TRAC,TRBC1,TRBC2,CD3D, CD3E, CD3G, CD4, MCM6, MKI67, PCNA, PTPRC, TOP2A, TRAC, TRBC1, TRBC2</t>
   </si>
   <si>
     <t xml:space="preserve">CD8A,CD8B</t>
@@ -1771,7 +1771,7 @@
     <t xml:space="preserve">Exhausted CD8+ T cells</t>
   </si>
   <si>
-    <t xml:space="preserve">CD8A, CD8B, ENTPD1, HAVCR2, LAG3, LAYN, PDCD1, PTPRC, TIGIT, TOX, TRAC, TRBC1, TRBC2</t>
+    <t xml:space="preserve">TRAC,TRBC1,TRBC2,CD8A, CD8B, ENTPD1, HAVCR2, LAG3, LAYN, PDCD1, PTPRC, TIGIT, TOX, TRAC, TRBC1, TRBC2</t>
   </si>
   <si>
     <t xml:space="preserve">Exh CD8+ T</t>
@@ -1780,7 +1780,7 @@
     <t xml:space="preserve">Exhausted CD4+ T cells</t>
   </si>
   <si>
-    <t xml:space="preserve">BTLA, CD4, CTLA4, HAVCR2, PDCD1, PTPRC, TIGIT, TOX, TRAC, TRBC1, TRBC2</t>
+    <t xml:space="preserve">TRAC,TRBC1,TRBC2,BTLA, CD4, CTLA4, HAVCR2, PDCD1, PTPRC, TIGIT, TOX, TRAC, TRBC1, TRBC2</t>
   </si>
   <si>
     <t xml:space="preserve">Exh CD4+ T</t>
@@ -1789,7 +1789,7 @@
     <t xml:space="preserve">Th17-proInfl T cells</t>
   </si>
   <si>
-    <t xml:space="preserve">CCR6, CD3D, CD3E, CD3G, CD4, IL17A, PDCD1, PTPRC, RORC</t>
+    <t xml:space="preserve">TRAC,TRBC1,TRBC2,CCR6, CD3D, CD3E, CD3G, CD4, IL17A, PDCD1, PTPRC, RORC</t>
   </si>
   <si>
     <t xml:space="preserve">CCR7,CD8A,CD8B</t>
@@ -1798,22 +1798,10 @@
     <t xml:space="preserve">Th17_proInfl</t>
   </si>
   <si>
-    <t xml:space="preserve">Regulatory CD8+ T cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CD8A, CD8B, CTLA4, MAF, PDCD1, PRDM1, PTPRC, TIGIT, TRAC, TRBC1, TRBC2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CD4,GZMB,PRF1,GNLY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CD8+ Treg</t>
-  </si>
-  <si>
     <t xml:space="preserve">Regulatory CD4+ T cells</t>
   </si>
   <si>
-    <t xml:space="preserve">CCR4, CD4, CTLA4, ICOS, IL2RA, PDCD1, PTPRC, TIGIT, TRAC, TRBC1, TRBC2</t>
+    <t xml:space="preserve">TRAC,TRBC1,TRBC2,CCR4, CD4, CTLA4, ICOS, IL2RA, PDCD1, PTPRC, TIGIT, TRAC, TRBC1, TRBC2</t>
   </si>
   <si>
     <t xml:space="preserve">CD8A,CD8B,GZMB,PRF1,GNLY</t>
@@ -6091,10 +6079,10 @@
       <c r="C270" s="14" t="s">
         <v>593</v>
       </c>
-      <c r="D270" s="2" t="s">
+      <c r="D270" s="15" t="s">
         <v>594</v>
       </c>
-      <c r="E270" s="2" t="s">
+      <c r="E270" s="16" t="s">
         <v>595</v>
       </c>
     </row>
@@ -6102,17 +6090,17 @@
       <c r="A271" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="B271" s="13" t="s">
-        <v>596</v>
-      </c>
-      <c r="C271" s="14" t="s">
-        <v>597</v>
-      </c>
-      <c r="D271" s="15" t="s">
-        <v>598</v>
-      </c>
-      <c r="E271" s="16" t="s">
-        <v>599</v>
+      <c r="B271" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C271" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D271" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E271" s="2" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="272" customFormat="false" ht="13.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6120,16 +6108,16 @@
         <v>542</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D272" s="2" t="s">
         <v>72</v>
       </c>
       <c r="E272" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="273" customFormat="false" ht="13.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6137,16 +6125,16 @@
         <v>542</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D273" s="2" t="s">
         <v>72</v>
       </c>
       <c r="E273" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="274" customFormat="false" ht="13.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6154,16 +6142,14 @@
         <v>542</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D274" s="2" t="s">
-        <v>72</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="D274" s="3"/>
       <c r="E274" s="2" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
     </row>
     <row r="275" customFormat="false" ht="13.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6171,14 +6157,14 @@
         <v>542</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>87</v>
+        <v>596</v>
       </c>
       <c r="D275" s="3"/>
       <c r="E275" s="2" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
     </row>
     <row r="276" customFormat="false" ht="13.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6186,44 +6172,44 @@
         <v>542</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="D276" s="3"/>
       <c r="E276" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="277" customFormat="false" ht="13.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A277" s="2" t="s">
+      <c r="A277" s="17" t="s">
         <v>542</v>
       </c>
-      <c r="B277" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C277" s="2" t="s">
-        <v>100</v>
+      <c r="B277" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="C277" s="19" t="s">
+        <v>597</v>
       </c>
       <c r="D277" s="3"/>
-      <c r="E277" s="2" t="s">
-        <v>101</v>
+      <c r="E277" s="20" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="278" customFormat="false" ht="13.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A278" s="17" t="s">
+      <c r="A278" s="21" t="s">
         <v>542</v>
       </c>
-      <c r="B278" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="C278" s="19" t="s">
-        <v>601</v>
-      </c>
-      <c r="D278" s="3"/>
-      <c r="E278" s="20" t="s">
-        <v>59</v>
+      <c r="B278" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="C278" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="D278" s="23"/>
+      <c r="E278" s="24" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="279" customFormat="false" ht="13.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6231,14 +6217,14 @@
         <v>542</v>
       </c>
       <c r="B279" s="22" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="C279" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="D279" s="23"/>
+        <v>81</v>
+      </c>
+      <c r="D279" s="25"/>
       <c r="E279" s="24" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
     </row>
     <row r="280" customFormat="false" ht="13.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6246,14 +6232,14 @@
         <v>542</v>
       </c>
       <c r="B280" s="22" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C280" s="22" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D280" s="25"/>
       <c r="E280" s="24" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="281" customFormat="false" ht="13.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6261,14 +6247,16 @@
         <v>542</v>
       </c>
       <c r="B281" s="22" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C281" s="22" t="s">
-        <v>84</v>
-      </c>
-      <c r="D281" s="25"/>
+        <v>598</v>
+      </c>
+      <c r="D281" s="22" t="s">
+        <v>91</v>
+      </c>
       <c r="E281" s="24" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
     </row>
     <row r="282" customFormat="false" ht="13.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6276,16 +6264,14 @@
         <v>542</v>
       </c>
       <c r="B282" s="22" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C282" s="22" t="s">
-        <v>602</v>
-      </c>
-      <c r="D282" s="22" t="s">
-        <v>91</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="D282" s="25"/>
       <c r="E282" s="24" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="283" customFormat="false" ht="13.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6293,14 +6279,14 @@
         <v>542</v>
       </c>
       <c r="B283" s="22" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="C283" s="22" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="D283" s="25"/>
       <c r="E283" s="24" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
     </row>
     <row r="284" customFormat="false" ht="13.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6308,14 +6294,14 @@
         <v>542</v>
       </c>
       <c r="B284" s="22" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C284" s="22" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D284" s="25"/>
       <c r="E284" s="24" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="285" customFormat="false" ht="13.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6323,14 +6309,14 @@
         <v>542</v>
       </c>
       <c r="B285" s="22" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C285" s="22" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D285" s="25"/>
       <c r="E285" s="24" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="286" customFormat="false" ht="13.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6338,61 +6324,47 @@
         <v>542</v>
       </c>
       <c r="B286" s="22" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C286" s="22" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D286" s="25"/>
       <c r="E286" s="24" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="287" customFormat="false" ht="13.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A287" s="21" t="s">
+      <c r="A287" s="26" t="s">
         <v>542</v>
       </c>
       <c r="B287" s="22" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C287" s="22" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D287" s="25"/>
       <c r="E287" s="24" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="288" customFormat="false" ht="13.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A288" s="26" t="s">
+      <c r="A288" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="B288" s="22" t="s">
-        <v>117</v>
-      </c>
-      <c r="C288" s="22" t="s">
-        <v>118</v>
-      </c>
-      <c r="D288" s="25"/>
-      <c r="E288" s="24" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="289" customFormat="false" ht="13.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A289" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="B289" s="26" t="s">
+      <c r="B288" s="26" t="s">
         <v>120</v>
       </c>
-      <c r="C289" s="27" t="s">
+      <c r="C288" s="27" t="s">
         <v>121</v>
       </c>
-      <c r="D289" s="28"/>
-      <c r="E289" s="29" t="s">
+      <c r="D288" s="28"/>
+      <c r="E288" s="29" t="s">
         <v>120</v>
       </c>
     </row>
+    <row r="1046915" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1046916" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1046917" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1046918" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
